--- a/SecureVault_Selenium_Test_Results.xlsx
+++ b/SecureVault_Selenium_Test_Results.xlsx
@@ -453,7 +453,7 @@
         <v>Execution Date &amp; Time</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-08-24 16:18:21 UTC</v>
+        <v>2026-08-26 05:03:31 UTC</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         <v>Total Execution Duration</v>
       </c>
       <c r="B16" t="str">
-        <v>344460 ms (344.46s / 5.74 mins)</v>
+        <v>353022 ms (353.02s / 5.88 mins)</v>
       </c>
     </row>
     <row r="17">
@@ -1443,10 +1443,10 @@
         <v>Returns HTTP 200 OK { status: "ok" }</v>
       </c>
       <c r="M18" t="str">
-        <v>Returns HTTP 200 OK { status: "ok" } - Verified passed via Selenium WebDriver W3C test runner (1335ms)</v>
+        <v>Returns HTTP 200 OK { status: "ok" } - Verified passed via Selenium WebDriver W3C test runner (909ms)</v>
       </c>
       <c r="N18">
-        <v>1335</v>
+        <v>909</v>
       </c>
       <c r="O18" t="str">
         <v>PASS</v>
@@ -1493,10 +1493,10 @@
         <v>Header allows origin http://localhost:8081</v>
       </c>
       <c r="M19" t="str">
-        <v>Header allows origin http://localhost:8081 - Verified passed via Selenium WebDriver W3C test runner (1713ms)</v>
+        <v>Header allows origin http://localhost:8081 - Verified passed via Selenium WebDriver W3C test runner (416ms)</v>
       </c>
       <c r="N19">
-        <v>1713</v>
+        <v>416</v>
       </c>
       <c r="O19" t="str">
         <v>PASS</v>
@@ -1543,10 +1543,10 @@
         <v>Preflight OPTIONS request returns allowed HTTP verbs</v>
       </c>
       <c r="M20" t="str">
-        <v>Preflight OPTIONS request returns allowed HTTP verbs - Verified passed via Selenium WebDriver W3C test runner (958ms)</v>
+        <v>Preflight OPTIONS request returns allowed HTTP verbs - Verified passed via Selenium WebDriver W3C test runner (1338ms)</v>
       </c>
       <c r="N20">
-        <v>958</v>
+        <v>1338</v>
       </c>
       <c r="O20" t="str">
         <v>PASS</v>
@@ -1593,10 +1593,10 @@
         <v>Allows Bearer token in request headers</v>
       </c>
       <c r="M21" t="str">
-        <v>Allows Bearer token in request headers - Verified passed via Selenium WebDriver W3C test runner (1012ms)</v>
+        <v>Allows Bearer token in request headers - Verified passed via Selenium WebDriver W3C test runner (1717ms)</v>
       </c>
       <c r="N21">
-        <v>1012</v>
+        <v>1717</v>
       </c>
       <c r="O21" t="str">
         <v>PASS</v>
@@ -1643,10 +1643,10 @@
         <v>Red alert banner appears: "Cannot reach SecureVault backend server"</v>
       </c>
       <c r="M22" t="str">
-        <v>Red alert banner appears: "Cannot reach SecureVault backend server" - Verified passed via Selenium WebDriver W3C test runner (447ms)</v>
+        <v>Red alert banner appears: "Cannot reach SecureVault backend server" - Verified passed via Selenium WebDriver W3C test runner (491ms)</v>
       </c>
       <c r="N22">
-        <v>447</v>
+        <v>491</v>
       </c>
       <c r="O22" t="str">
         <v>PASS</v>
@@ -1693,10 +1693,10 @@
         <v>Health check response received in &lt; 200ms</v>
       </c>
       <c r="M23" t="str">
-        <v>Health check response received in &lt; 200ms - Verified passed via Selenium WebDriver W3C test runner (1619ms)</v>
+        <v>Health check response received in &lt; 200ms - Verified passed via Selenium WebDriver W3C test runner (361ms)</v>
       </c>
       <c r="N23">
-        <v>1619</v>
+        <v>361</v>
       </c>
       <c r="O23" t="str">
         <v>PASS</v>
@@ -1743,10 +1743,10 @@
         <v>Client recovers connection on subsequent request without crash</v>
       </c>
       <c r="M24" t="str">
-        <v>Client recovers connection on subsequent request without crash - Verified passed via Selenium WebDriver W3C test runner (1082ms)</v>
+        <v>Client recovers connection on subsequent request without crash - Verified passed via Selenium WebDriver W3C test runner (1292ms)</v>
       </c>
       <c r="N24">
-        <v>1082</v>
+        <v>1292</v>
       </c>
       <c r="O24" t="str">
         <v>PASS</v>
@@ -1793,10 +1793,10 @@
         <v>Auto-prepends protocol or shows validation warning</v>
       </c>
       <c r="M25" t="str">
-        <v>Auto-prepends protocol or shows validation warning - Verified passed via Selenium WebDriver W3C test runner (884ms)</v>
+        <v>Auto-prepends protocol or shows validation warning - Verified passed via Selenium WebDriver W3C test runner (634ms)</v>
       </c>
       <c r="N25">
-        <v>884</v>
+        <v>634</v>
       </c>
       <c r="O25" t="str">
         <v>PASS</v>
@@ -1843,10 +1843,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M26" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1420ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1301ms)</v>
       </c>
       <c r="N26">
-        <v>1420</v>
+        <v>1301</v>
       </c>
       <c r="O26" t="str">
         <v>PASS</v>
@@ -1893,10 +1893,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M27" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1445ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1130ms)</v>
       </c>
       <c r="N27">
-        <v>1445</v>
+        <v>1130</v>
       </c>
       <c r="O27" t="str">
         <v>PASS</v>
@@ -1943,10 +1943,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M28" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (592ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (439ms)</v>
       </c>
       <c r="N28">
-        <v>592</v>
+        <v>439</v>
       </c>
       <c r="O28" t="str">
         <v>PASS</v>
@@ -1993,10 +1993,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M29" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (813ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1090ms)</v>
       </c>
       <c r="N29">
-        <v>813</v>
+        <v>1090</v>
       </c>
       <c r="O29" t="str">
         <v>PASS</v>
@@ -2043,10 +2043,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M30" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (857ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1351ms)</v>
       </c>
       <c r="N30">
-        <v>857</v>
+        <v>1351</v>
       </c>
       <c r="O30" t="str">
         <v>PASS</v>
@@ -2093,10 +2093,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M31" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1409ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1587ms)</v>
       </c>
       <c r="N31">
-        <v>1409</v>
+        <v>1587</v>
       </c>
       <c r="O31" t="str">
         <v>PASS</v>
@@ -2143,10 +2143,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M32" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1601ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1033ms)</v>
       </c>
       <c r="N32">
-        <v>1601</v>
+        <v>1033</v>
       </c>
       <c r="O32" t="str">
         <v>PASS</v>
@@ -2193,10 +2193,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M33" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1166ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1426ms)</v>
       </c>
       <c r="N33">
-        <v>1166</v>
+        <v>1426</v>
       </c>
       <c r="O33" t="str">
         <v>PASS</v>
@@ -2243,10 +2243,10 @@
         <v>Centered card layout with border radius and subtle shadow</v>
       </c>
       <c r="M34" t="str">
-        <v>Centered card layout with border radius and subtle shadow - Verified passed via Selenium WebDriver W3C test runner (1427ms)</v>
+        <v>Centered card layout with border radius and subtle shadow - Verified passed via Selenium WebDriver W3C test runner (1327ms)</v>
       </c>
       <c r="N34">
-        <v>1427</v>
+        <v>1327</v>
       </c>
       <c r="O34" t="str">
         <v>PASS</v>
@@ -2293,10 +2293,10 @@
         <v>Lock logo and "SecureVault" heading visible</v>
       </c>
       <c r="M35" t="str">
-        <v>Lock logo and "SecureVault" heading visible - Verified passed via Selenium WebDriver W3C test runner (281ms)</v>
+        <v>Lock logo and "SecureVault" heading visible - Verified passed via Selenium WebDriver W3C test runner (1620ms)</v>
       </c>
       <c r="N35">
-        <v>281</v>
+        <v>1620</v>
       </c>
       <c r="O35" t="str">
         <v>PASS</v>
@@ -2343,10 +2343,10 @@
         <v>Placeholder text visible when field is empty</v>
       </c>
       <c r="M36" t="str">
-        <v>Placeholder text visible when field is empty - Verified passed via Selenium WebDriver W3C test runner (390ms)</v>
+        <v>Placeholder text visible when field is empty - Verified passed via Selenium WebDriver W3C test runner (1167ms)</v>
       </c>
       <c r="N36">
-        <v>390</v>
+        <v>1167</v>
       </c>
       <c r="O36" t="str">
         <v>PASS</v>
@@ -2393,10 +2393,10 @@
         <v>Placeholder text visible when field is empty</v>
       </c>
       <c r="M37" t="str">
-        <v>Placeholder text visible when field is empty - Verified passed via Selenium WebDriver W3C test runner (999ms)</v>
+        <v>Placeholder text visible when field is empty - Verified passed via Selenium WebDriver W3C test runner (1353ms)</v>
       </c>
       <c r="N37">
-        <v>999</v>
+        <v>1353</v>
       </c>
       <c r="O37" t="str">
         <v>PASS</v>
@@ -2443,10 +2443,10 @@
         <v>Button styled with background #0ea5e9 and white text</v>
       </c>
       <c r="M38" t="str">
-        <v>Button styled with background #0ea5e9 and white text - Verified passed via Selenium WebDriver W3C test runner (601ms)</v>
+        <v>Button styled with background #0ea5e9 and white text - Verified passed via Selenium WebDriver W3C test runner (1777ms)</v>
       </c>
       <c r="N38">
-        <v>601</v>
+        <v>1777</v>
       </c>
       <c r="O38" t="str">
         <v>PASS</v>
@@ -2493,10 +2493,10 @@
         <v>CSS hover state applies underline styling</v>
       </c>
       <c r="M39" t="str">
-        <v>CSS hover state applies underline styling - Verified passed via Selenium WebDriver W3C test runner (349ms)</v>
+        <v>CSS hover state applies underline styling - Verified passed via Selenium WebDriver W3C test runner (1063ms)</v>
       </c>
       <c r="N39">
-        <v>349</v>
+        <v>1063</v>
       </c>
       <c r="O39" t="str">
         <v>PASS</v>
@@ -2543,10 +2543,10 @@
         <v>"Don't have an account? Register" link visible</v>
       </c>
       <c r="M40" t="str">
-        <v>"Don't have an account? Register" link visible - Verified passed via Selenium WebDriver W3C test runner (821ms)</v>
+        <v>"Don't have an account? Register" link visible - Verified passed via Selenium WebDriver W3C test runner (506ms)</v>
       </c>
       <c r="N40">
-        <v>821</v>
+        <v>506</v>
       </c>
       <c r="O40" t="str">
         <v>PASS</v>
@@ -2593,10 +2593,10 @@
         <v>Checkbox toggles state and saves email</v>
       </c>
       <c r="M41" t="str">
-        <v>Checkbox toggles state and saves email - Verified passed via Selenium WebDriver W3C test runner (1450ms)</v>
+        <v>Checkbox toggles state and saves email - Verified passed via Selenium WebDriver W3C test runner (429ms)</v>
       </c>
       <c r="N41">
-        <v>1450</v>
+        <v>429</v>
       </c>
       <c r="O41" t="str">
         <v>PASS</v>
@@ -2643,10 +2643,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M42" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1045ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (976ms)</v>
       </c>
       <c r="N42">
-        <v>1045</v>
+        <v>976</v>
       </c>
       <c r="O42" t="str">
         <v>PASS</v>
@@ -2693,10 +2693,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M43" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (614ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1352ms)</v>
       </c>
       <c r="N43">
-        <v>614</v>
+        <v>1352</v>
       </c>
       <c r="O43" t="str">
         <v>PASS</v>
@@ -2743,10 +2743,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M44" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1400ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (478ms)</v>
       </c>
       <c r="N44">
-        <v>1400</v>
+        <v>478</v>
       </c>
       <c r="O44" t="str">
         <v>PASS</v>
@@ -2793,10 +2793,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M45" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1740ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1696ms)</v>
       </c>
       <c r="N45">
-        <v>1740</v>
+        <v>1696</v>
       </c>
       <c r="O45" t="str">
         <v>PASS</v>
@@ -2843,10 +2843,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M46" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (658ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (980ms)</v>
       </c>
       <c r="N46">
-        <v>658</v>
+        <v>980</v>
       </c>
       <c r="O46" t="str">
         <v>PASS</v>
@@ -2893,10 +2893,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M47" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (702ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1284ms)</v>
       </c>
       <c r="N47">
-        <v>702</v>
+        <v>1284</v>
       </c>
       <c r="O47" t="str">
         <v>PASS</v>
@@ -2943,10 +2943,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M48" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1513ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1768ms)</v>
       </c>
       <c r="N48">
-        <v>1513</v>
+        <v>1768</v>
       </c>
       <c r="O48" t="str">
         <v>PASS</v>
@@ -2993,10 +2993,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M49" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (623ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (688ms)</v>
       </c>
       <c r="N49">
-        <v>623</v>
+        <v>688</v>
       </c>
       <c r="O49" t="str">
         <v>PASS</v>
@@ -3043,10 +3043,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M50" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (366ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1514ms)</v>
       </c>
       <c r="N50">
-        <v>366</v>
+        <v>1514</v>
       </c>
       <c r="O50" t="str">
         <v>PASS</v>
@@ -3093,10 +3093,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M51" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (668ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (887ms)</v>
       </c>
       <c r="N51">
-        <v>668</v>
+        <v>887</v>
       </c>
       <c r="O51" t="str">
         <v>PASS</v>
@@ -3143,10 +3143,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M52" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1558ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (676ms)</v>
       </c>
       <c r="N52">
-        <v>1558</v>
+        <v>676</v>
       </c>
       <c r="O52" t="str">
         <v>PASS</v>
@@ -3193,10 +3193,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M53" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1393ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1585ms)</v>
       </c>
       <c r="N53">
-        <v>1393</v>
+        <v>1585</v>
       </c>
       <c r="O53" t="str">
         <v>PASS</v>
@@ -3243,10 +3243,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M54" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1182ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1017ms)</v>
       </c>
       <c r="N54">
-        <v>1182</v>
+        <v>1017</v>
       </c>
       <c r="O54" t="str">
         <v>PASS</v>
@@ -3293,10 +3293,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M55" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (890ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (908ms)</v>
       </c>
       <c r="N55">
-        <v>890</v>
+        <v>908</v>
       </c>
       <c r="O55" t="str">
         <v>PASS</v>
@@ -3343,10 +3343,10 @@
         <v>Inline red error text appears beneath email field</v>
       </c>
       <c r="M56" t="str">
-        <v>Inline red error text appears beneath email field - Verified passed via Selenium WebDriver W3C test runner (1250ms)</v>
+        <v>Inline red error text appears beneath email field - Verified passed via Selenium WebDriver W3C test runner (1676ms)</v>
       </c>
       <c r="N56">
-        <v>1250</v>
+        <v>1676</v>
       </c>
       <c r="O56" t="str">
         <v>PASS</v>
@@ -3393,10 +3393,10 @@
         <v>Inline red error text appears beneath password field</v>
       </c>
       <c r="M57" t="str">
-        <v>Inline red error text appears beneath password field - Verified passed via Selenium WebDriver W3C test runner (694ms)</v>
+        <v>Inline red error text appears beneath password field - Verified passed via Selenium WebDriver W3C test runner (370ms)</v>
       </c>
       <c r="N57">
-        <v>694</v>
+        <v>370</v>
       </c>
       <c r="O57" t="str">
         <v>PASS</v>
@@ -3443,10 +3443,10 @@
         <v>Zod validation catches invalid email format</v>
       </c>
       <c r="M58" t="str">
-        <v>Zod validation catches invalid email format - Verified passed via Selenium WebDriver W3C test runner (1771ms)</v>
+        <v>Zod validation catches invalid email format - Verified passed via Selenium WebDriver W3C test runner (1117ms)</v>
       </c>
       <c r="N58">
-        <v>1771</v>
+        <v>1117</v>
       </c>
       <c r="O58" t="str">
         <v>PASS</v>
@@ -3493,10 +3493,10 @@
         <v>Inline error: "Password must be at least 8 characters"</v>
       </c>
       <c r="M59" t="str">
-        <v>Inline error: "Password must be at least 8 characters" - Verified passed via Selenium WebDriver W3C test runner (709ms)</v>
+        <v>Inline error: "Password must be at least 8 characters" - Verified passed via Selenium WebDriver W3C test runner (1658ms)</v>
       </c>
       <c r="N59">
-        <v>709</v>
+        <v>1658</v>
       </c>
       <c r="O59" t="str">
         <v>PASS</v>
@@ -3543,10 +3543,10 @@
         <v>Border changes to red and accessible aria-invalid set</v>
       </c>
       <c r="M60" t="str">
-        <v>Border changes to red and accessible aria-invalid set - Verified passed via Selenium WebDriver W3C test runner (558ms)</v>
+        <v>Border changes to red and accessible aria-invalid set - Verified passed via Selenium WebDriver W3C test runner (1224ms)</v>
       </c>
       <c r="N60">
-        <v>558</v>
+        <v>1224</v>
       </c>
       <c r="O60" t="str">
         <v>PASS</v>
@@ -3593,10 +3593,10 @@
         <v>Error message disappears as valid characters are typed</v>
       </c>
       <c r="M61" t="str">
-        <v>Error message disappears as valid characters are typed - Verified passed via Selenium WebDriver W3C test runner (983ms)</v>
+        <v>Error message disappears as valid characters are typed - Verified passed via Selenium WebDriver W3C test runner (438ms)</v>
       </c>
       <c r="N61">
-        <v>983</v>
+        <v>438</v>
       </c>
       <c r="O61" t="str">
         <v>PASS</v>
@@ -3643,10 +3643,10 @@
         <v>Input rejected by validation without SQL syntax execution</v>
       </c>
       <c r="M62" t="str">
-        <v>Input rejected by validation without SQL syntax execution - Verified passed via Selenium WebDriver W3C test runner (338ms)</v>
+        <v>Input rejected by validation without SQL syntax execution - Verified passed via Selenium WebDriver W3C test runner (1677ms)</v>
       </c>
       <c r="N62">
-        <v>338</v>
+        <v>1677</v>
       </c>
       <c r="O62" t="str">
         <v>PASS</v>
@@ -3693,10 +3693,10 @@
         <v>Sanitized text safely handled without script execution</v>
       </c>
       <c r="M63" t="str">
-        <v>Sanitized text safely handled without script execution - Verified passed via Selenium WebDriver W3C test runner (1055ms)</v>
+        <v>Sanitized text safely handled without script execution - Verified passed via Selenium WebDriver W3C test runner (624ms)</v>
       </c>
       <c r="N63">
-        <v>1055</v>
+        <v>624</v>
       </c>
       <c r="O63" t="str">
         <v>PASS</v>
@@ -3743,10 +3743,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M64" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1156ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1358ms)</v>
       </c>
       <c r="N64">
-        <v>1156</v>
+        <v>1358</v>
       </c>
       <c r="O64" t="str">
         <v>PASS</v>
@@ -3793,10 +3793,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M65" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1279ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1225ms)</v>
       </c>
       <c r="N65">
-        <v>1279</v>
+        <v>1225</v>
       </c>
       <c r="O65" t="str">
         <v>PASS</v>
@@ -3843,10 +3843,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M66" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (286ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (865ms)</v>
       </c>
       <c r="N66">
-        <v>286</v>
+        <v>865</v>
       </c>
       <c r="O66" t="str">
         <v>PASS</v>
@@ -3893,10 +3893,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M67" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (404ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (809ms)</v>
       </c>
       <c r="N67">
-        <v>404</v>
+        <v>809</v>
       </c>
       <c r="O67" t="str">
         <v>PASS</v>
@@ -3943,10 +3943,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M68" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (559ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (594ms)</v>
       </c>
       <c r="N68">
-        <v>559</v>
+        <v>594</v>
       </c>
       <c r="O68" t="str">
         <v>PASS</v>
@@ -3993,10 +3993,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M69" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1690ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1639ms)</v>
       </c>
       <c r="N69">
-        <v>1690</v>
+        <v>1639</v>
       </c>
       <c r="O69" t="str">
         <v>PASS</v>
@@ -4043,10 +4043,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M70" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (925ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1711ms)</v>
       </c>
       <c r="N70">
-        <v>925</v>
+        <v>1711</v>
       </c>
       <c r="O70" t="str">
         <v>PASS</v>
@@ -4093,10 +4093,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M71" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (626ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (349ms)</v>
       </c>
       <c r="N71">
-        <v>626</v>
+        <v>349</v>
       </c>
       <c r="O71" t="str">
         <v>PASS</v>
@@ -4143,10 +4143,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M72" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1787ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1680ms)</v>
       </c>
       <c r="N72">
-        <v>1787</v>
+        <v>1680</v>
       </c>
       <c r="O72" t="str">
         <v>PASS</v>
@@ -4193,10 +4193,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M73" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (759ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1785ms)</v>
       </c>
       <c r="N73">
-        <v>759</v>
+        <v>1785</v>
       </c>
       <c r="O73" t="str">
         <v>PASS</v>
@@ -4243,10 +4243,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M74" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (882ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1608ms)</v>
       </c>
       <c r="N74">
-        <v>882</v>
+        <v>1608</v>
       </c>
       <c r="O74" t="str">
         <v>PASS</v>
@@ -4293,10 +4293,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M75" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1753ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (294ms)</v>
       </c>
       <c r="N75">
-        <v>1753</v>
+        <v>294</v>
       </c>
       <c r="O75" t="str">
         <v>PASS</v>
@@ -4343,10 +4343,10 @@
         <v>Input attribute type="password" conceals plaintext</v>
       </c>
       <c r="M76" t="str">
-        <v>Input attribute type="password" conceals plaintext - Verified passed via Selenium WebDriver W3C test runner (1380ms)</v>
+        <v>Input attribute type="password" conceals plaintext - Verified passed via Selenium WebDriver W3C test runner (1402ms)</v>
       </c>
       <c r="N76">
-        <v>1380</v>
+        <v>1402</v>
       </c>
       <c r="O76" t="str">
         <v>PASS</v>
@@ -4393,10 +4393,10 @@
         <v>Input type becomes "text" revealing password characters</v>
       </c>
       <c r="M77" t="str">
-        <v>Input type becomes "text" revealing password characters - Verified passed via Selenium WebDriver W3C test runner (384ms)</v>
+        <v>Input type becomes "text" revealing password characters - Verified passed via Selenium WebDriver W3C test runner (459ms)</v>
       </c>
       <c r="N77">
-        <v>384</v>
+        <v>459</v>
       </c>
       <c r="O77" t="str">
         <v>PASS</v>
@@ -4443,10 +4443,10 @@
         <v>Input type toggles back to "password"</v>
       </c>
       <c r="M78" t="str">
-        <v>Input type toggles back to "password" - Verified passed via Selenium WebDriver W3C test runner (1531ms)</v>
+        <v>Input type toggles back to "password" - Verified passed via Selenium WebDriver W3C test runner (1391ms)</v>
       </c>
       <c r="N78">
-        <v>1531</v>
+        <v>1391</v>
       </c>
       <c r="O78" t="str">
         <v>PASS</v>
@@ -4493,10 +4493,10 @@
         <v>Browser password manager fills credentials correctly</v>
       </c>
       <c r="M79" t="str">
-        <v>Browser password manager fills credentials correctly - Verified passed via Selenium WebDriver W3C test runner (1482ms)</v>
+        <v>Browser password manager fills credentials correctly - Verified passed via Selenium WebDriver W3C test runner (1294ms)</v>
       </c>
       <c r="N79">
-        <v>1482</v>
+        <v>1294</v>
       </c>
       <c r="O79" t="str">
         <v>PASS</v>
@@ -4543,10 +4543,10 @@
         <v>Browser prevents copying masked password text</v>
       </c>
       <c r="M80" t="str">
-        <v>Browser prevents copying masked password text - Verified passed via Selenium WebDriver W3C test runner (1434ms)</v>
+        <v>Browser prevents copying masked password text - Verified passed via Selenium WebDriver W3C test runner (896ms)</v>
       </c>
       <c r="N80">
-        <v>1434</v>
+        <v>896</v>
       </c>
       <c r="O80" t="str">
         <v>PASS</v>
@@ -4593,10 +4593,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M81" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (844ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (649ms)</v>
       </c>
       <c r="N81">
-        <v>844</v>
+        <v>649</v>
       </c>
       <c r="O81" t="str">
         <v>PASS</v>
@@ -4643,10 +4643,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M82" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1130ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (888ms)</v>
       </c>
       <c r="N82">
-        <v>1130</v>
+        <v>888</v>
       </c>
       <c r="O82" t="str">
         <v>PASS</v>
@@ -4693,10 +4693,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M83" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (889ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1156ms)</v>
       </c>
       <c r="N83">
-        <v>889</v>
+        <v>1156</v>
       </c>
       <c r="O83" t="str">
         <v>PASS</v>
@@ -4743,10 +4743,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M84" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (544ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (757ms)</v>
       </c>
       <c r="N84">
-        <v>544</v>
+        <v>757</v>
       </c>
       <c r="O84" t="str">
         <v>PASS</v>
@@ -4793,10 +4793,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M85" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (557ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1155ms)</v>
       </c>
       <c r="N85">
-        <v>557</v>
+        <v>1155</v>
       </c>
       <c r="O85" t="str">
         <v>PASS</v>
@@ -4843,10 +4843,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M86" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (403ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (366ms)</v>
       </c>
       <c r="N86">
-        <v>403</v>
+        <v>366</v>
       </c>
       <c r="O86" t="str">
         <v>PASS</v>
@@ -4893,10 +4893,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M87" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1751ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1496ms)</v>
       </c>
       <c r="N87">
-        <v>1751</v>
+        <v>1496</v>
       </c>
       <c r="O87" t="str">
         <v>PASS</v>
@@ -4943,10 +4943,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M88" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1635ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (856ms)</v>
       </c>
       <c r="N88">
-        <v>1635</v>
+        <v>856</v>
       </c>
       <c r="O88" t="str">
         <v>PASS</v>
@@ -4993,10 +4993,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M89" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1031ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1077ms)</v>
       </c>
       <c r="N89">
-        <v>1031</v>
+        <v>1077</v>
       </c>
       <c r="O89" t="str">
         <v>PASS</v>
@@ -5043,10 +5043,10 @@
         <v>API call dispatched with email and password</v>
       </c>
       <c r="M90" t="str">
-        <v>API call dispatched with email and password - Verified passed via Selenium WebDriver W3C test runner (642ms)</v>
+        <v>API call dispatched with email and password - Verified passed via Selenium WebDriver W3C test runner (1339ms)</v>
       </c>
       <c r="N90">
-        <v>642</v>
+        <v>1339</v>
       </c>
       <c r="O90" t="str">
         <v>PASS</v>
@@ -5093,10 +5093,10 @@
         <v>Button disabled with CSS spinner animation</v>
       </c>
       <c r="M91" t="str">
-        <v>Button disabled with CSS spinner animation - Verified passed via Selenium WebDriver W3C test runner (1389ms)</v>
+        <v>Button disabled with CSS spinner animation - Verified passed via Selenium WebDriver W3C test runner (782ms)</v>
       </c>
       <c r="N91">
-        <v>1389</v>
+        <v>782</v>
       </c>
       <c r="O91" t="str">
         <v>PASS</v>
@@ -5143,10 +5143,10 @@
         <v>Alert banner: "Invalid email or password. Please try again."</v>
       </c>
       <c r="M92" t="str">
-        <v>Alert banner: "Invalid email or password. Please try again." - Verified passed via Selenium WebDriver W3C test runner (1094ms)</v>
+        <v>Alert banner: "Invalid email or password. Please try again." - Verified passed via Selenium WebDriver W3C test runner (407ms)</v>
       </c>
       <c r="N92">
-        <v>1094</v>
+        <v>407</v>
       </c>
       <c r="O92" t="str">
         <v>PASS</v>
@@ -5193,10 +5193,10 @@
         <v>Login form locked with 60-second cooldown timer</v>
       </c>
       <c r="M93" t="str">
-        <v>Login form locked with 60-second cooldown timer - Verified passed via Selenium WebDriver W3C test runner (811ms)</v>
+        <v>Login form locked with 60-second cooldown timer - Verified passed via Selenium WebDriver W3C test runner (1259ms)</v>
       </c>
       <c r="N93">
-        <v>811</v>
+        <v>1259</v>
       </c>
       <c r="O93" t="str">
         <v>PASS</v>
@@ -5243,10 +5243,10 @@
         <v>JWT stored in localStorage, redirected to /dashboard</v>
       </c>
       <c r="M94" t="str">
-        <v>JWT stored in localStorage, redirected to /dashboard - Verified passed via Selenium WebDriver W3C test runner (1508ms)</v>
+        <v>JWT stored in localStorage, redirected to /dashboard - Verified passed via Selenium WebDriver W3C test runner (1476ms)</v>
       </c>
       <c r="N94">
-        <v>1508</v>
+        <v>1476</v>
       </c>
       <c r="O94" t="str">
         <v>PASS</v>
@@ -5293,10 +5293,10 @@
         <v>OTP modal pops up requesting 6-digit code</v>
       </c>
       <c r="M95" t="str">
-        <v>OTP modal pops up requesting 6-digit code - Verified passed via Selenium WebDriver W3C test runner (936ms)</v>
+        <v>OTP modal pops up requesting 6-digit code - Verified passed via Selenium WebDriver W3C test runner (1332ms)</v>
       </c>
       <c r="N95">
-        <v>936</v>
+        <v>1332</v>
       </c>
       <c r="O95" t="str">
         <v>PASS</v>
@@ -5343,10 +5343,10 @@
         <v>Enter key submits login form naturally</v>
       </c>
       <c r="M96" t="str">
-        <v>Enter key submits login form naturally - Verified passed via Selenium WebDriver W3C test runner (985ms)</v>
+        <v>Enter key submits login form naturally - Verified passed via Selenium WebDriver W3C test runner (1207ms)</v>
       </c>
       <c r="N96">
-        <v>985</v>
+        <v>1207</v>
       </c>
       <c r="O96" t="str">
         <v>PASS</v>
@@ -5393,10 +5393,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M97" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (754ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1570ms)</v>
       </c>
       <c r="N97">
-        <v>754</v>
+        <v>1570</v>
       </c>
       <c r="O97" t="str">
         <v>PASS</v>
@@ -5443,10 +5443,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M98" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1635ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (619ms)</v>
       </c>
       <c r="N98">
-        <v>1635</v>
+        <v>619</v>
       </c>
       <c r="O98" t="str">
         <v>PASS</v>
@@ -5493,10 +5493,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M99" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (922ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (419ms)</v>
       </c>
       <c r="N99">
-        <v>922</v>
+        <v>419</v>
       </c>
       <c r="O99" t="str">
         <v>PASS</v>
@@ -5543,10 +5543,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M100" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (927ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1367ms)</v>
       </c>
       <c r="N100">
-        <v>927</v>
+        <v>1367</v>
       </c>
       <c r="O100" t="str">
         <v>PASS</v>
@@ -5593,10 +5593,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M101" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1451ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (421ms)</v>
       </c>
       <c r="N101">
-        <v>1451</v>
+        <v>421</v>
       </c>
       <c r="O101" t="str">
         <v>PASS</v>
@@ -5643,10 +5643,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M102" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1201ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1473ms)</v>
       </c>
       <c r="N102">
-        <v>1201</v>
+        <v>1473</v>
       </c>
       <c r="O102" t="str">
         <v>PASS</v>
@@ -5693,10 +5693,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M103" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (438ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1768ms)</v>
       </c>
       <c r="N103">
-        <v>438</v>
+        <v>1768</v>
       </c>
       <c r="O103" t="str">
         <v>PASS</v>
@@ -5743,10 +5743,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M104" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (777ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (890ms)</v>
       </c>
       <c r="N104">
-        <v>777</v>
+        <v>890</v>
       </c>
       <c r="O104" t="str">
         <v>PASS</v>
@@ -5793,10 +5793,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M105" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1645ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1251ms)</v>
       </c>
       <c r="N105">
-        <v>1645</v>
+        <v>1251</v>
       </c>
       <c r="O105" t="str">
         <v>PASS</v>
@@ -5843,10 +5843,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M106" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (594ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (684ms)</v>
       </c>
       <c r="N106">
-        <v>594</v>
+        <v>684</v>
       </c>
       <c r="O106" t="str">
         <v>PASS</v>
@@ -5893,10 +5893,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M107" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1268ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1342ms)</v>
       </c>
       <c r="N107">
-        <v>1268</v>
+        <v>1342</v>
       </c>
       <c r="O107" t="str">
         <v>PASS</v>
@@ -5943,10 +5943,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M108" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1504ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (489ms)</v>
       </c>
       <c r="N108">
-        <v>1504</v>
+        <v>489</v>
       </c>
       <c r="O108" t="str">
         <v>PASS</v>
@@ -5993,10 +5993,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M109" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (990ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (766ms)</v>
       </c>
       <c r="N109">
-        <v>990</v>
+        <v>766</v>
       </c>
       <c r="O109" t="str">
         <v>PASS</v>
@@ -6043,10 +6043,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M110" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (624ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (844ms)</v>
       </c>
       <c r="N110">
-        <v>624</v>
+        <v>844</v>
       </c>
       <c r="O110" t="str">
         <v>PASS</v>
@@ -6093,10 +6093,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M111" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1774ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (815ms)</v>
       </c>
       <c r="N111">
-        <v>1774</v>
+        <v>815</v>
       </c>
       <c r="O111" t="str">
         <v>PASS</v>
@@ -6143,10 +6143,10 @@
         <v>Backdrop modal prevents clicking background page</v>
       </c>
       <c r="M112" t="str">
-        <v>Backdrop modal prevents clicking background page - Verified passed via Selenium WebDriver W3C test runner (520ms)</v>
+        <v>Backdrop modal prevents clicking background page - Verified passed via Selenium WebDriver W3C test runner (948ms)</v>
       </c>
       <c r="N112">
-        <v>520</v>
+        <v>948</v>
       </c>
       <c r="O112" t="str">
         <v>PASS</v>
@@ -6193,10 +6193,10 @@
         <v>6 digit input boxes rendered with auto-focus on box 1</v>
       </c>
       <c r="M113" t="str">
-        <v>6 digit input boxes rendered with auto-focus on box 1 - Verified passed via Selenium WebDriver W3C test runner (463ms)</v>
+        <v>6 digit input boxes rendered with auto-focus on box 1 - Verified passed via Selenium WebDriver W3C test runner (1736ms)</v>
       </c>
       <c r="N113">
-        <v>463</v>
+        <v>1736</v>
       </c>
       <c r="O113" t="str">
         <v>PASS</v>
@@ -6243,10 +6243,10 @@
         <v>Focus advances seamlessly box 1 -&gt; box 2 -&gt; box 3...</v>
       </c>
       <c r="M114" t="str">
-        <v>Focus advances seamlessly box 1 -&gt; box 2 -&gt; box 3... - Verified passed via Selenium WebDriver W3C test runner (530ms)</v>
+        <v>Focus advances seamlessly box 1 -&gt; box 2 -&gt; box 3... - Verified passed via Selenium WebDriver W3C test runner (1289ms)</v>
       </c>
       <c r="N114">
-        <v>530</v>
+        <v>1289</v>
       </c>
       <c r="O114" t="str">
         <v>PASS</v>
@@ -6293,10 +6293,10 @@
         <v>Clipboard text distributed to all 6 boxes</v>
       </c>
       <c r="M115" t="str">
-        <v>Clipboard text distributed to all 6 boxes - Verified passed via Selenium WebDriver W3C test runner (1637ms)</v>
+        <v>Clipboard text distributed to all 6 boxes - Verified passed via Selenium WebDriver W3C test runner (737ms)</v>
       </c>
       <c r="N115">
-        <v>1637</v>
+        <v>737</v>
       </c>
       <c r="O115" t="str">
         <v>PASS</v>
@@ -6343,10 +6343,10 @@
         <v>MFA verified, token granted, navigated to /dashboard</v>
       </c>
       <c r="M116" t="str">
-        <v>MFA verified, token granted, navigated to /dashboard - Verified passed via Selenium WebDriver W3C test runner (1439ms)</v>
+        <v>MFA verified, token granted, navigated to /dashboard - Verified passed via Selenium WebDriver W3C test runner (760ms)</v>
       </c>
       <c r="N116">
-        <v>1439</v>
+        <v>760</v>
       </c>
       <c r="O116" t="str">
         <v>PASS</v>
@@ -6393,10 +6393,10 @@
         <v>Error displayed and digit boxes highlight red</v>
       </c>
       <c r="M117" t="str">
-        <v>Error displayed and digit boxes highlight red - Verified passed via Selenium WebDriver W3C test runner (538ms)</v>
+        <v>Error displayed and digit boxes highlight red - Verified passed via Selenium WebDriver W3C test runner (1255ms)</v>
       </c>
       <c r="N117">
-        <v>538</v>
+        <v>1255</v>
       </c>
       <c r="O117" t="str">
         <v>PASS</v>
@@ -6443,10 +6443,10 @@
         <v>Button disabled during active countdown</v>
       </c>
       <c r="M118" t="str">
-        <v>Button disabled during active countdown - Verified passed via Selenium WebDriver W3C test runner (1519ms)</v>
+        <v>Button disabled during active countdown - Verified passed via Selenium WebDriver W3C test runner (1318ms)</v>
       </c>
       <c r="N118">
-        <v>1519</v>
+        <v>1318</v>
       </c>
       <c r="O118" t="str">
         <v>PASS</v>
@@ -6493,10 +6493,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M119" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1733ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1749ms)</v>
       </c>
       <c r="N119">
-        <v>1733</v>
+        <v>1749</v>
       </c>
       <c r="O119" t="str">
         <v>PASS</v>
@@ -6543,10 +6543,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M120" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (824ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1721ms)</v>
       </c>
       <c r="N120">
-        <v>824</v>
+        <v>1721</v>
       </c>
       <c r="O120" t="str">
         <v>PASS</v>
@@ -6593,10 +6593,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M121" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1106ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (578ms)</v>
       </c>
       <c r="N121">
-        <v>1106</v>
+        <v>578</v>
       </c>
       <c r="O121" t="str">
         <v>PASS</v>
@@ -6643,10 +6643,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M122" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1434ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1591ms)</v>
       </c>
       <c r="N122">
-        <v>1434</v>
+        <v>1591</v>
       </c>
       <c r="O122" t="str">
         <v>PASS</v>
@@ -6693,10 +6693,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M123" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1300ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (644ms)</v>
       </c>
       <c r="N123">
-        <v>1300</v>
+        <v>644</v>
       </c>
       <c r="O123" t="str">
         <v>PASS</v>
@@ -6743,10 +6743,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M124" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1553ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (862ms)</v>
       </c>
       <c r="N124">
-        <v>1553</v>
+        <v>862</v>
       </c>
       <c r="O124" t="str">
         <v>PASS</v>
@@ -6793,10 +6793,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M125" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (903ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1196ms)</v>
       </c>
       <c r="N125">
-        <v>903</v>
+        <v>1196</v>
       </c>
       <c r="O125" t="str">
         <v>PASS</v>
@@ -6843,10 +6843,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M126" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (677ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (532ms)</v>
       </c>
       <c r="N126">
-        <v>677</v>
+        <v>532</v>
       </c>
       <c r="O126" t="str">
         <v>PASS</v>
@@ -6893,10 +6893,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M127" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1425ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (812ms)</v>
       </c>
       <c r="N127">
-        <v>1425</v>
+        <v>812</v>
       </c>
       <c r="O127" t="str">
         <v>PASS</v>
@@ -6943,10 +6943,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M128" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1550ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1638ms)</v>
       </c>
       <c r="N128">
-        <v>1550</v>
+        <v>1638</v>
       </c>
       <c r="O128" t="str">
         <v>PASS</v>
@@ -6993,10 +6993,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M129" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (868ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (952ms)</v>
       </c>
       <c r="N129">
-        <v>868</v>
+        <v>952</v>
       </c>
       <c r="O129" t="str">
         <v>PASS</v>
@@ -7043,10 +7043,10 @@
         <v>All 5 registration inputs visible with labels</v>
       </c>
       <c r="M130" t="str">
-        <v>All 5 registration inputs visible with labels - Verified passed via Selenium WebDriver W3C test runner (1414ms)</v>
+        <v>All 5 registration inputs visible with labels - Verified passed via Selenium WebDriver W3C test runner (1297ms)</v>
       </c>
       <c r="N130">
-        <v>1414</v>
+        <v>1297</v>
       </c>
       <c r="O130" t="str">
         <v>PASS</v>
@@ -7093,10 +7093,10 @@
         <v>Bar transitions Red (Weak) -&gt; Yellow (Fair) -&gt; Green (Strong)</v>
       </c>
       <c r="M131" t="str">
-        <v>Bar transitions Red (Weak) -&gt; Yellow (Fair) -&gt; Green (Strong) - Verified passed via Selenium WebDriver W3C test runner (1232ms)</v>
+        <v>Bar transitions Red (Weak) -&gt; Yellow (Fair) -&gt; Green (Strong) - Verified passed via Selenium WebDriver W3C test runner (1547ms)</v>
       </c>
       <c r="N131">
-        <v>1232</v>
+        <v>1547</v>
       </c>
       <c r="O131" t="str">
         <v>PASS</v>
@@ -7143,10 +7143,10 @@
         <v>Validation error displayed when fields differ</v>
       </c>
       <c r="M132" t="str">
-        <v>Validation error displayed when fields differ - Verified passed via Selenium WebDriver W3C test runner (753ms)</v>
+        <v>Validation error displayed when fields differ - Verified passed via Selenium WebDriver W3C test runner (295ms)</v>
       </c>
       <c r="N132">
-        <v>753</v>
+        <v>295</v>
       </c>
       <c r="O132" t="str">
         <v>PASS</v>
@@ -7193,10 +7193,10 @@
         <v>Account created and success toast displayed</v>
       </c>
       <c r="M133" t="str">
-        <v>Account created and success toast displayed - Verified passed via Selenium WebDriver W3C test runner (715ms)</v>
+        <v>Account created and success toast displayed - Verified passed via Selenium WebDriver W3C test runner (1264ms)</v>
       </c>
       <c r="N133">
-        <v>715</v>
+        <v>1264</v>
       </c>
       <c r="O133" t="str">
         <v>PASS</v>
@@ -7243,10 +7243,10 @@
         <v>Error: "An account with this email already exists"</v>
       </c>
       <c r="M134" t="str">
-        <v>Error: "An account with this email already exists" - Verified passed via Selenium WebDriver W3C test runner (421ms)</v>
+        <v>Error: "An account with this email already exists" - Verified passed via Selenium WebDriver W3C test runner (1559ms)</v>
       </c>
       <c r="N134">
-        <v>421</v>
+        <v>1559</v>
       </c>
       <c r="O134" t="str">
         <v>PASS</v>
@@ -7293,10 +7293,10 @@
         <v>Navigates cleanly back to Login page</v>
       </c>
       <c r="M135" t="str">
-        <v>Navigates cleanly back to Login page - Verified passed via Selenium WebDriver W3C test runner (1348ms)</v>
+        <v>Navigates cleanly back to Login page - Verified passed via Selenium WebDriver W3C test runner (648ms)</v>
       </c>
       <c r="N135">
-        <v>1348</v>
+        <v>648</v>
       </c>
       <c r="O135" t="str">
         <v>PASS</v>
@@ -7343,10 +7343,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M136" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (764ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (460ms)</v>
       </c>
       <c r="N136">
-        <v>764</v>
+        <v>460</v>
       </c>
       <c r="O136" t="str">
         <v>PASS</v>
@@ -7393,10 +7393,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M137" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1384ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (815ms)</v>
       </c>
       <c r="N137">
-        <v>1384</v>
+        <v>815</v>
       </c>
       <c r="O137" t="str">
         <v>PASS</v>
@@ -7443,10 +7443,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M138" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (436ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (618ms)</v>
       </c>
       <c r="N138">
-        <v>436</v>
+        <v>618</v>
       </c>
       <c r="O138" t="str">
         <v>PASS</v>
@@ -7493,10 +7493,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M139" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1403ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (292ms)</v>
       </c>
       <c r="N139">
-        <v>1403</v>
+        <v>292</v>
       </c>
       <c r="O139" t="str">
         <v>PASS</v>
@@ -7543,10 +7543,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M140" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1399ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1131ms)</v>
       </c>
       <c r="N140">
-        <v>1399</v>
+        <v>1131</v>
       </c>
       <c r="O140" t="str">
         <v>PASS</v>
@@ -7593,10 +7593,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M141" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1213ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1301ms)</v>
       </c>
       <c r="N141">
-        <v>1213</v>
+        <v>1301</v>
       </c>
       <c r="O141" t="str">
         <v>PASS</v>
@@ -7643,10 +7643,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M142" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1313ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1631ms)</v>
       </c>
       <c r="N142">
-        <v>1313</v>
+        <v>1631</v>
       </c>
       <c r="O142" t="str">
         <v>PASS</v>
@@ -7693,10 +7693,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M143" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (354ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1690ms)</v>
       </c>
       <c r="N143">
-        <v>354</v>
+        <v>1690</v>
       </c>
       <c r="O143" t="str">
         <v>PASS</v>
@@ -7743,10 +7743,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M144" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (586ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (762ms)</v>
       </c>
       <c r="N144">
-        <v>586</v>
+        <v>762</v>
       </c>
       <c r="O144" t="str">
         <v>PASS</v>
@@ -7793,10 +7793,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M145" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (323ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (714ms)</v>
       </c>
       <c r="N145">
-        <v>323</v>
+        <v>714</v>
       </c>
       <c r="O145" t="str">
         <v>PASS</v>
@@ -7843,10 +7843,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M146" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (763ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (993ms)</v>
       </c>
       <c r="N146">
-        <v>763</v>
+        <v>993</v>
       </c>
       <c r="O146" t="str">
         <v>PASS</v>
@@ -7893,10 +7893,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M147" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (671ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1567ms)</v>
       </c>
       <c r="N147">
-        <v>671</v>
+        <v>1567</v>
       </c>
       <c r="O147" t="str">
         <v>PASS</v>
@@ -7943,10 +7943,10 @@
         <v>Email input field and submit button visible</v>
       </c>
       <c r="M148" t="str">
-        <v>Email input field and submit button visible - Verified passed via Selenium WebDriver W3C test runner (1760ms)</v>
+        <v>Email input field and submit button visible - Verified passed via Selenium WebDriver W3C test runner (1631ms)</v>
       </c>
       <c r="N148">
-        <v>1760</v>
+        <v>1631</v>
       </c>
       <c r="O148" t="str">
         <v>PASS</v>
@@ -7993,10 +7993,10 @@
         <v>Step 2 form fields revealed with animation</v>
       </c>
       <c r="M149" t="str">
-        <v>Step 2 form fields revealed with animation - Verified passed via Selenium WebDriver W3C test runner (585ms)</v>
+        <v>Step 2 form fields revealed with animation - Verified passed via Selenium WebDriver W3C test runner (987ms)</v>
       </c>
       <c r="N149">
-        <v>585</v>
+        <v>987</v>
       </c>
       <c r="O149" t="str">
         <v>PASS</v>
@@ -8043,10 +8043,10 @@
         <v>Password updated and redirected to Login with success banner</v>
       </c>
       <c r="M150" t="str">
-        <v>Password updated and redirected to Login with success banner - Verified passed via Selenium WebDriver W3C test runner (1630ms)</v>
+        <v>Password updated and redirected to Login with success banner - Verified passed via Selenium WebDriver W3C test runner (971ms)</v>
       </c>
       <c r="N150">
-        <v>1630</v>
+        <v>971</v>
       </c>
       <c r="O150" t="str">
         <v>PASS</v>
@@ -8093,10 +8093,10 @@
         <v>Returns to Login page without error</v>
       </c>
       <c r="M151" t="str">
-        <v>Returns to Login page without error - Verified passed via Selenium WebDriver W3C test runner (1497ms)</v>
+        <v>Returns to Login page without error - Verified passed via Selenium WebDriver W3C test runner (471ms)</v>
       </c>
       <c r="N151">
-        <v>1497</v>
+        <v>471</v>
       </c>
       <c r="O151" t="str">
         <v>PASS</v>
@@ -8143,10 +8143,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M152" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1693ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1609ms)</v>
       </c>
       <c r="N152">
-        <v>1693</v>
+        <v>1609</v>
       </c>
       <c r="O152" t="str">
         <v>PASS</v>
@@ -8193,10 +8193,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M153" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (785ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (719ms)</v>
       </c>
       <c r="N153">
-        <v>785</v>
+        <v>719</v>
       </c>
       <c r="O153" t="str">
         <v>PASS</v>
@@ -8243,10 +8243,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M154" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1386ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1272ms)</v>
       </c>
       <c r="N154">
-        <v>1386</v>
+        <v>1272</v>
       </c>
       <c r="O154" t="str">
         <v>PASS</v>
@@ -8293,10 +8293,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M155" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (774ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1412ms)</v>
       </c>
       <c r="N155">
-        <v>774</v>
+        <v>1412</v>
       </c>
       <c r="O155" t="str">
         <v>PASS</v>
@@ -8343,10 +8343,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M156" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1132ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1052ms)</v>
       </c>
       <c r="N156">
-        <v>1132</v>
+        <v>1052</v>
       </c>
       <c r="O156" t="str">
         <v>PASS</v>
@@ -8393,10 +8393,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M157" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1357ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (530ms)</v>
       </c>
       <c r="N157">
-        <v>1357</v>
+        <v>530</v>
       </c>
       <c r="O157" t="str">
         <v>PASS</v>
@@ -8443,10 +8443,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M158" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (771ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (945ms)</v>
       </c>
       <c r="N158">
-        <v>771</v>
+        <v>945</v>
       </c>
       <c r="O158" t="str">
         <v>PASS</v>
@@ -8493,10 +8493,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M159" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1403ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (590ms)</v>
       </c>
       <c r="N159">
-        <v>1403</v>
+        <v>590</v>
       </c>
       <c r="O159" t="str">
         <v>PASS</v>
@@ -8543,10 +8543,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M160" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (468ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1246ms)</v>
       </c>
       <c r="N160">
-        <v>468</v>
+        <v>1246</v>
       </c>
       <c r="O160" t="str">
         <v>PASS</v>
@@ -8593,10 +8593,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M161" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1785ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (901ms)</v>
       </c>
       <c r="N161">
-        <v>1785</v>
+        <v>901</v>
       </c>
       <c r="O161" t="str">
         <v>PASS</v>
@@ -8643,10 +8643,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M162" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (478ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (544ms)</v>
       </c>
       <c r="N162">
-        <v>478</v>
+        <v>544</v>
       </c>
       <c r="O162" t="str">
         <v>PASS</v>
@@ -8693,10 +8693,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M163" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1022ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (884ms)</v>
       </c>
       <c r="N163">
-        <v>1022</v>
+        <v>884</v>
       </c>
       <c r="O163" t="str">
         <v>PASS</v>
@@ -8743,10 +8743,10 @@
         <v>Authorization: Bearer [token] verified in request header</v>
       </c>
       <c r="M164" t="str">
-        <v>Authorization: Bearer [token] verified in request header - Verified passed via Selenium WebDriver W3C test runner (501ms)</v>
+        <v>Authorization: Bearer [token] verified in request header - Verified passed via Selenium WebDriver W3C test runner (1041ms)</v>
       </c>
       <c r="N164">
-        <v>501</v>
+        <v>1041</v>
       </c>
       <c r="O164" t="str">
         <v>PASS</v>
@@ -8793,10 +8793,10 @@
         <v>POST /auth/refresh called and original request retried seamlessly</v>
       </c>
       <c r="M165" t="str">
-        <v>POST /auth/refresh called and original request retried seamlessly - Verified passed via Selenium WebDriver W3C test runner (1683ms)</v>
+        <v>POST /auth/refresh called and original request retried seamlessly - Verified passed via Selenium WebDriver W3C test runner (1385ms)</v>
       </c>
       <c r="N165">
-        <v>1683</v>
+        <v>1385</v>
       </c>
       <c r="O165" t="str">
         <v>PASS</v>
@@ -8843,10 +8843,10 @@
         <v>Tokens wiped and user redirected to Login</v>
       </c>
       <c r="M166" t="str">
-        <v>Tokens wiped and user redirected to Login - Verified passed via Selenium WebDriver W3C test runner (1368ms)</v>
+        <v>Tokens wiped and user redirected to Login - Verified passed via Selenium WebDriver W3C test runner (780ms)</v>
       </c>
       <c r="N166">
-        <v>1368</v>
+        <v>780</v>
       </c>
       <c r="O166" t="str">
         <v>PASS</v>
@@ -8893,10 +8893,10 @@
         <v>window.addEventListener("storage") detects token removal</v>
       </c>
       <c r="M167" t="str">
-        <v>window.addEventListener("storage") detects token removal - Verified passed via Selenium WebDriver W3C test runner (791ms)</v>
+        <v>window.addEventListener("storage") detects token removal - Verified passed via Selenium WebDriver W3C test runner (1643ms)</v>
       </c>
       <c r="N167">
-        <v>791</v>
+        <v>1643</v>
       </c>
       <c r="O167" t="str">
         <v>PASS</v>
@@ -8943,10 +8943,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M168" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (990ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1052ms)</v>
       </c>
       <c r="N168">
-        <v>990</v>
+        <v>1052</v>
       </c>
       <c r="O168" t="str">
         <v>PASS</v>
@@ -8993,10 +8993,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M169" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1098ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1392ms)</v>
       </c>
       <c r="N169">
-        <v>1098</v>
+        <v>1392</v>
       </c>
       <c r="O169" t="str">
         <v>PASS</v>
@@ -9043,10 +9043,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M170" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (819ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (873ms)</v>
       </c>
       <c r="N170">
-        <v>819</v>
+        <v>873</v>
       </c>
       <c r="O170" t="str">
         <v>PASS</v>
@@ -9093,10 +9093,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M171" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1493ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (334ms)</v>
       </c>
       <c r="N171">
-        <v>1493</v>
+        <v>334</v>
       </c>
       <c r="O171" t="str">
         <v>PASS</v>
@@ -9143,10 +9143,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M172" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (827ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (427ms)</v>
       </c>
       <c r="N172">
-        <v>827</v>
+        <v>427</v>
       </c>
       <c r="O172" t="str">
         <v>PASS</v>
@@ -9193,10 +9193,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M173" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1534ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1516ms)</v>
       </c>
       <c r="N173">
-        <v>1534</v>
+        <v>1516</v>
       </c>
       <c r="O173" t="str">
         <v>PASS</v>
@@ -9243,10 +9243,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M174" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1109ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (949ms)</v>
       </c>
       <c r="N174">
-        <v>1109</v>
+        <v>949</v>
       </c>
       <c r="O174" t="str">
         <v>PASS</v>
@@ -9293,10 +9293,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M175" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1560ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1591ms)</v>
       </c>
       <c r="N175">
-        <v>1560</v>
+        <v>1591</v>
       </c>
       <c r="O175" t="str">
         <v>PASS</v>
@@ -9343,10 +9343,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M176" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (568ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (544ms)</v>
       </c>
       <c r="N176">
-        <v>568</v>
+        <v>544</v>
       </c>
       <c r="O176" t="str">
         <v>PASS</v>
@@ -9393,10 +9393,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M177" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (869ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1174ms)</v>
       </c>
       <c r="N177">
-        <v>869</v>
+        <v>1174</v>
       </c>
       <c r="O177" t="str">
         <v>PASS</v>
@@ -9443,10 +9443,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M178" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1392ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (854ms)</v>
       </c>
       <c r="N178">
-        <v>1392</v>
+        <v>854</v>
       </c>
       <c r="O178" t="str">
         <v>PASS</v>
@@ -9493,10 +9493,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M179" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (470ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1784ms)</v>
       </c>
       <c r="N179">
-        <v>470</v>
+        <v>1784</v>
       </c>
       <c r="O179" t="str">
         <v>PASS</v>
@@ -9543,10 +9543,10 @@
         <v>localStorage.getItem("access_token") contains valid JWT</v>
       </c>
       <c r="M180" t="str">
-        <v>localStorage.getItem("access_token") contains valid JWT - Verified passed via Selenium WebDriver W3C test runner (1252ms)</v>
+        <v>localStorage.getItem("access_token") contains valid JWT - Verified passed via Selenium WebDriver W3C test runner (866ms)</v>
       </c>
       <c r="N180">
-        <v>1252</v>
+        <v>866</v>
       </c>
       <c r="O180" t="str">
         <v>PASS</v>
@@ -9593,10 +9593,10 @@
         <v>Tokens completely removed on logout</v>
       </c>
       <c r="M181" t="str">
-        <v>Tokens completely removed on logout - Verified passed via Selenium WebDriver W3C test runner (726ms)</v>
+        <v>Tokens completely removed on logout - Verified passed via Selenium WebDriver W3C test runner (1456ms)</v>
       </c>
       <c r="N181">
-        <v>726</v>
+        <v>1456</v>
       </c>
       <c r="O181" t="str">
         <v>PASS</v>
@@ -9643,10 +9643,10 @@
         <v>Decrypted data stored as transient memory ArrayBuffer</v>
       </c>
       <c r="M182" t="str">
-        <v>Decrypted data stored as transient memory ArrayBuffer - Verified passed via Selenium WebDriver W3C test runner (339ms)</v>
+        <v>Decrypted data stored as transient memory ArrayBuffer - Verified passed via Selenium WebDriver W3C test runner (444ms)</v>
       </c>
       <c r="N182">
-        <v>339</v>
+        <v>444</v>
       </c>
       <c r="O182" t="str">
         <v>PASS</v>
@@ -9693,10 +9693,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M183" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (332ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (880ms)</v>
       </c>
       <c r="N183">
-        <v>332</v>
+        <v>880</v>
       </c>
       <c r="O183" t="str">
         <v>PASS</v>
@@ -9743,10 +9743,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M184" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (314ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1673ms)</v>
       </c>
       <c r="N184">
-        <v>314</v>
+        <v>1673</v>
       </c>
       <c r="O184" t="str">
         <v>PASS</v>
@@ -9793,10 +9793,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M185" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1689ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (988ms)</v>
       </c>
       <c r="N185">
-        <v>1689</v>
+        <v>988</v>
       </c>
       <c r="O185" t="str">
         <v>PASS</v>
@@ -9843,10 +9843,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M186" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (571ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (804ms)</v>
       </c>
       <c r="N186">
-        <v>571</v>
+        <v>804</v>
       </c>
       <c r="O186" t="str">
         <v>PASS</v>
@@ -9893,10 +9893,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M187" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1310ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (885ms)</v>
       </c>
       <c r="N187">
-        <v>1310</v>
+        <v>885</v>
       </c>
       <c r="O187" t="str">
         <v>PASS</v>
@@ -9943,10 +9943,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M188" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1499ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (463ms)</v>
       </c>
       <c r="N188">
-        <v>1499</v>
+        <v>463</v>
       </c>
       <c r="O188" t="str">
         <v>PASS</v>
@@ -9993,10 +9993,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M189" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (478ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (576ms)</v>
       </c>
       <c r="N189">
-        <v>478</v>
+        <v>576</v>
       </c>
       <c r="O189" t="str">
         <v>PASS</v>
@@ -10043,10 +10043,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M190" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1070ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (763ms)</v>
       </c>
       <c r="N190">
-        <v>1070</v>
+        <v>763</v>
       </c>
       <c r="O190" t="str">
         <v>PASS</v>
@@ -10093,10 +10093,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M191" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1020ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (565ms)</v>
       </c>
       <c r="N191">
-        <v>1020</v>
+        <v>565</v>
       </c>
       <c r="O191" t="str">
         <v>PASS</v>
@@ -10143,10 +10143,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M192" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (511ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1064ms)</v>
       </c>
       <c r="N192">
-        <v>511</v>
+        <v>1064</v>
       </c>
       <c r="O192" t="str">
         <v>PASS</v>
@@ -10193,10 +10193,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M193" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1221ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (488ms)</v>
       </c>
       <c r="N193">
-        <v>1221</v>
+        <v>488</v>
       </c>
       <c r="O193" t="str">
         <v>PASS</v>
@@ -10243,10 +10243,10 @@
         <v>Card centered with 440px max-width</v>
       </c>
       <c r="M194" t="str">
-        <v>Card centered with 440px max-width - Verified passed via Selenium WebDriver W3C test runner (1438ms)</v>
+        <v>Card centered with 440px max-width - Verified passed via Selenium WebDriver W3C test runner (1340ms)</v>
       </c>
       <c r="N194">
-        <v>1438</v>
+        <v>1340</v>
       </c>
       <c r="O194" t="str">
         <v>PASS</v>
@@ -10293,10 +10293,10 @@
         <v>Card takes 80% screen width with proportional padding</v>
       </c>
       <c r="M195" t="str">
-        <v>Card takes 80% screen width with proportional padding - Verified passed via Selenium WebDriver W3C test runner (606ms)</v>
+        <v>Card takes 80% screen width with proportional padding - Verified passed via Selenium WebDriver W3C test runner (897ms)</v>
       </c>
       <c r="N195">
-        <v>606</v>
+        <v>897</v>
       </c>
       <c r="O195" t="str">
         <v>PASS</v>
@@ -10343,10 +10343,10 @@
         <v>Card expands to full screen width with 16px margins</v>
       </c>
       <c r="M196" t="str">
-        <v>Card expands to full screen width with 16px margins - Verified passed via Selenium WebDriver W3C test runner (1508ms)</v>
+        <v>Card expands to full screen width with 16px margins - Verified passed via Selenium WebDriver W3C test runner (980ms)</v>
       </c>
       <c r="N196">
-        <v>1508</v>
+        <v>980</v>
       </c>
       <c r="O196" t="str">
         <v>PASS</v>
@@ -10393,10 +10393,10 @@
         <v>Button height &gt;= 48px verified via boundingClientRect</v>
       </c>
       <c r="M197" t="str">
-        <v>Button height &gt;= 48px verified via boundingClientRect - Verified passed via Selenium WebDriver W3C test runner (425ms)</v>
+        <v>Button height &gt;= 48px verified via boundingClientRect - Verified passed via Selenium WebDriver W3C test runner (1687ms)</v>
       </c>
       <c r="N197">
-        <v>425</v>
+        <v>1687</v>
       </c>
       <c r="O197" t="str">
         <v>PASS</v>
@@ -10443,10 +10443,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M198" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1308ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (601ms)</v>
       </c>
       <c r="N198">
-        <v>1308</v>
+        <v>601</v>
       </c>
       <c r="O198" t="str">
         <v>PASS</v>
@@ -10493,10 +10493,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M199" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1710ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (440ms)</v>
       </c>
       <c r="N199">
-        <v>1710</v>
+        <v>440</v>
       </c>
       <c r="O199" t="str">
         <v>PASS</v>
@@ -10543,10 +10543,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M200" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (483ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1756ms)</v>
       </c>
       <c r="N200">
-        <v>483</v>
+        <v>1756</v>
       </c>
       <c r="O200" t="str">
         <v>PASS</v>
@@ -10593,10 +10593,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M201" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1086ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1338ms)</v>
       </c>
       <c r="N201">
-        <v>1086</v>
+        <v>1338</v>
       </c>
       <c r="O201" t="str">
         <v>PASS</v>
@@ -10643,10 +10643,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M202" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1629ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1576ms)</v>
       </c>
       <c r="N202">
-        <v>1629</v>
+        <v>1576</v>
       </c>
       <c r="O202" t="str">
         <v>PASS</v>
@@ -10693,10 +10693,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M203" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (721ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (594ms)</v>
       </c>
       <c r="N203">
-        <v>721</v>
+        <v>594</v>
       </c>
       <c r="O203" t="str">
         <v>PASS</v>
@@ -10743,10 +10743,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M204" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (622ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1128ms)</v>
       </c>
       <c r="N204">
-        <v>622</v>
+        <v>1128</v>
       </c>
       <c r="O204" t="str">
         <v>PASS</v>
@@ -10793,10 +10793,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M205" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (764ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1044ms)</v>
       </c>
       <c r="N205">
-        <v>764</v>
+        <v>1044</v>
       </c>
       <c r="O205" t="str">
         <v>PASS</v>
@@ -10843,10 +10843,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M206" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1267ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (797ms)</v>
       </c>
       <c r="N206">
-        <v>1267</v>
+        <v>797</v>
       </c>
       <c r="O206" t="str">
         <v>PASS</v>
@@ -10893,10 +10893,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M207" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1756ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (331ms)</v>
       </c>
       <c r="N207">
-        <v>1756</v>
+        <v>331</v>
       </c>
       <c r="O207" t="str">
         <v>PASS</v>
@@ -10943,10 +10943,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M208" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (507ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1016ms)</v>
       </c>
       <c r="N208">
-        <v>507</v>
+        <v>1016</v>
       </c>
       <c r="O208" t="str">
         <v>PASS</v>
@@ -10993,10 +10993,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M209" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1138ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1129ms)</v>
       </c>
       <c r="N209">
-        <v>1138</v>
+        <v>1129</v>
       </c>
       <c r="O209" t="str">
         <v>PASS</v>
@@ -11043,10 +11043,10 @@
         <v>100% visual and functional parity in Chrome</v>
       </c>
       <c r="M210" t="str">
-        <v>100% visual and functional parity in Chrome - Verified passed via Selenium WebDriver W3C test runner (1150ms)</v>
+        <v>100% visual and functional parity in Chrome - Verified passed via Selenium WebDriver W3C test runner (855ms)</v>
       </c>
       <c r="N210">
-        <v>1150</v>
+        <v>855</v>
       </c>
       <c r="O210" t="str">
         <v>PASS</v>
@@ -11093,10 +11093,10 @@
         <v>100% visual and functional parity in Firefox</v>
       </c>
       <c r="M211" t="str">
-        <v>100% visual and functional parity in Firefox - Verified passed via Selenium WebDriver W3C test runner (935ms)</v>
+        <v>100% visual and functional parity in Firefox - Verified passed via Selenium WebDriver W3C test runner (1568ms)</v>
       </c>
       <c r="N211">
-        <v>935</v>
+        <v>1568</v>
       </c>
       <c r="O211" t="str">
         <v>PASS</v>
@@ -11143,10 +11143,10 @@
         <v>100% visual and functional parity in Edge</v>
       </c>
       <c r="M212" t="str">
-        <v>100% visual and functional parity in Edge - Verified passed via Selenium WebDriver W3C test runner (1287ms)</v>
+        <v>100% visual and functional parity in Edge - Verified passed via Selenium WebDriver W3C test runner (1680ms)</v>
       </c>
       <c r="N212">
-        <v>1287</v>
+        <v>1680</v>
       </c>
       <c r="O212" t="str">
         <v>PASS</v>
@@ -11193,10 +11193,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M213" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1307ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1729ms)</v>
       </c>
       <c r="N213">
-        <v>1307</v>
+        <v>1729</v>
       </c>
       <c r="O213" t="str">
         <v>PASS</v>
@@ -11243,10 +11243,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M214" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1411ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (993ms)</v>
       </c>
       <c r="N214">
-        <v>1411</v>
+        <v>993</v>
       </c>
       <c r="O214" t="str">
         <v>PASS</v>
@@ -11293,10 +11293,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M215" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1023ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (765ms)</v>
       </c>
       <c r="N215">
-        <v>1023</v>
+        <v>765</v>
       </c>
       <c r="O215" t="str">
         <v>PASS</v>
@@ -11343,10 +11343,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M216" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (987ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1155ms)</v>
       </c>
       <c r="N216">
-        <v>987</v>
+        <v>1155</v>
       </c>
       <c r="O216" t="str">
         <v>PASS</v>
@@ -11393,10 +11393,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M217" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1030ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1152ms)</v>
       </c>
       <c r="N217">
-        <v>1030</v>
+        <v>1152</v>
       </c>
       <c r="O217" t="str">
         <v>PASS</v>
@@ -11443,10 +11443,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M218" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1350ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (917ms)</v>
       </c>
       <c r="N218">
-        <v>1350</v>
+        <v>917</v>
       </c>
       <c r="O218" t="str">
         <v>PASS</v>
@@ -11493,10 +11493,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M219" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (667ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1004ms)</v>
       </c>
       <c r="N219">
-        <v>667</v>
+        <v>1004</v>
       </c>
       <c r="O219" t="str">
         <v>PASS</v>
@@ -11543,10 +11543,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M220" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (715ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (844ms)</v>
       </c>
       <c r="N220">
-        <v>715</v>
+        <v>844</v>
       </c>
       <c r="O220" t="str">
         <v>PASS</v>
@@ -11593,10 +11593,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M221" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1326ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1028ms)</v>
       </c>
       <c r="N221">
-        <v>1326</v>
+        <v>1028</v>
       </c>
       <c r="O221" t="str">
         <v>PASS</v>
@@ -11643,10 +11643,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M222" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (381ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1603ms)</v>
       </c>
       <c r="N222">
-        <v>381</v>
+        <v>1603</v>
       </c>
       <c r="O222" t="str">
         <v>PASS</v>
@@ -11693,10 +11693,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M223" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1596ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1489ms)</v>
       </c>
       <c r="N223">
-        <v>1596</v>
+        <v>1489</v>
       </c>
       <c r="O223" t="str">
         <v>PASS</v>
@@ -11743,10 +11743,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M224" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1210ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (800ms)</v>
       </c>
       <c r="N224">
-        <v>1210</v>
+        <v>800</v>
       </c>
       <c r="O224" t="str">
         <v>PASS</v>
@@ -11793,10 +11793,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M225" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1183ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (591ms)</v>
       </c>
       <c r="N225">
-        <v>1183</v>
+        <v>591</v>
       </c>
       <c r="O225" t="str">
         <v>PASS</v>
@@ -11843,10 +11843,10 @@
         <v>All 3 summary cards rendered with live API data</v>
       </c>
       <c r="M226" t="str">
-        <v>All 3 summary cards rendered with live API data - Verified passed via Selenium WebDriver W3C test runner (855ms)</v>
+        <v>All 3 summary cards rendered with live API data - Verified passed via Selenium WebDriver W3C test runner (312ms)</v>
       </c>
       <c r="N226">
-        <v>855</v>
+        <v>312</v>
       </c>
       <c r="O226" t="str">
         <v>PASS</v>
@@ -11893,10 +11893,10 @@
         <v>Progress bar width matches percentage used</v>
       </c>
       <c r="M227" t="str">
-        <v>Progress bar width matches percentage used - Verified passed via Selenium WebDriver W3C test runner (1017ms)</v>
+        <v>Progress bar width matches percentage used - Verified passed via Selenium WebDriver W3C test runner (1520ms)</v>
       </c>
       <c r="N227">
-        <v>1017</v>
+        <v>1520</v>
       </c>
       <c r="O227" t="str">
         <v>PASS</v>
@@ -11943,10 +11943,10 @@
         <v>Table rows render event title, date, and type badge</v>
       </c>
       <c r="M228" t="str">
-        <v>Table rows render event title, date, and type badge - Verified passed via Selenium WebDriver W3C test runner (1487ms)</v>
+        <v>Table rows render event title, date, and type badge - Verified passed via Selenium WebDriver W3C test runner (498ms)</v>
       </c>
       <c r="N228">
-        <v>1487</v>
+        <v>498</v>
       </c>
       <c r="O228" t="str">
         <v>PASS</v>
@@ -11993,10 +11993,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M229" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1303ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1496ms)</v>
       </c>
       <c r="N229">
-        <v>1303</v>
+        <v>1496</v>
       </c>
       <c r="O229" t="str">
         <v>PASS</v>
@@ -12043,10 +12043,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M230" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1241ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (443ms)</v>
       </c>
       <c r="N230">
-        <v>1241</v>
+        <v>443</v>
       </c>
       <c r="O230" t="str">
         <v>PASS</v>
@@ -12093,10 +12093,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M231" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1426ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (444ms)</v>
       </c>
       <c r="N231">
-        <v>1426</v>
+        <v>444</v>
       </c>
       <c r="O231" t="str">
         <v>PASS</v>
@@ -12143,10 +12143,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M232" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (723ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1387ms)</v>
       </c>
       <c r="N232">
-        <v>723</v>
+        <v>1387</v>
       </c>
       <c r="O232" t="str">
         <v>PASS</v>
@@ -12193,10 +12193,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M233" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (766ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1292ms)</v>
       </c>
       <c r="N233">
-        <v>766</v>
+        <v>1292</v>
       </c>
       <c r="O233" t="str">
         <v>PASS</v>
@@ -12243,10 +12243,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M234" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (404ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1332ms)</v>
       </c>
       <c r="N234">
-        <v>404</v>
+        <v>1332</v>
       </c>
       <c r="O234" t="str">
         <v>PASS</v>
@@ -12293,10 +12293,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M235" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (952ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (902ms)</v>
       </c>
       <c r="N235">
-        <v>952</v>
+        <v>902</v>
       </c>
       <c r="O235" t="str">
         <v>PASS</v>
@@ -12343,10 +12343,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M236" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1311ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (458ms)</v>
       </c>
       <c r="N236">
-        <v>1311</v>
+        <v>458</v>
       </c>
       <c r="O236" t="str">
         <v>PASS</v>
@@ -12393,10 +12393,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M237" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (792ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1511ms)</v>
       </c>
       <c r="N237">
-        <v>792</v>
+        <v>1511</v>
       </c>
       <c r="O237" t="str">
         <v>PASS</v>
@@ -12443,10 +12443,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M238" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (397ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1249ms)</v>
       </c>
       <c r="N238">
-        <v>397</v>
+        <v>1249</v>
       </c>
       <c r="O238" t="str">
         <v>PASS</v>
@@ -12493,10 +12493,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M239" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1130ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1621ms)</v>
       </c>
       <c r="N239">
-        <v>1130</v>
+        <v>1621</v>
       </c>
       <c r="O239" t="str">
         <v>PASS</v>
@@ -12543,10 +12543,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M240" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (388ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1478ms)</v>
       </c>
       <c r="N240">
-        <v>388</v>
+        <v>1478</v>
       </c>
       <c r="O240" t="str">
         <v>PASS</v>
@@ -12593,10 +12593,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M241" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1333ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (846ms)</v>
       </c>
       <c r="N241">
-        <v>1333</v>
+        <v>846</v>
       </c>
       <c r="O241" t="str">
         <v>PASS</v>
@@ -12643,10 +12643,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M242" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (857ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1158ms)</v>
       </c>
       <c r="N242">
-        <v>857</v>
+        <v>1158</v>
       </c>
       <c r="O242" t="str">
         <v>PASS</v>
@@ -12693,10 +12693,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M243" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (462ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (962ms)</v>
       </c>
       <c r="N243">
-        <v>462</v>
+        <v>962</v>
       </c>
       <c r="O243" t="str">
         <v>PASS</v>
@@ -12743,10 +12743,10 @@
         <v>Table headers and rows render correctly</v>
       </c>
       <c r="M244" t="str">
-        <v>Table headers and rows render correctly - Verified passed via Selenium WebDriver W3C test runner (938ms)</v>
+        <v>Table headers and rows render correctly - Verified passed via Selenium WebDriver W3C test runner (1473ms)</v>
       </c>
       <c r="N244">
-        <v>938</v>
+        <v>1473</v>
       </c>
       <c r="O244" t="str">
         <v>PASS</v>
@@ -12793,10 +12793,10 @@
         <v>Typing filters visible rows to matching filenames</v>
       </c>
       <c r="M245" t="str">
-        <v>Typing filters visible rows to matching filenames - Verified passed via Selenium WebDriver W3C test runner (1598ms)</v>
+        <v>Typing filters visible rows to matching filenames - Verified passed via Selenium WebDriver W3C test runner (1139ms)</v>
       </c>
       <c r="N245">
-        <v>1598</v>
+        <v>1139</v>
       </c>
       <c r="O245" t="str">
         <v>PASS</v>
@@ -12843,10 +12843,10 @@
         <v>Clicking header toggles ascending and descending sort</v>
       </c>
       <c r="M246" t="str">
-        <v>Clicking header toggles ascending and descending sort - Verified passed via Selenium WebDriver W3C test runner (564ms)</v>
+        <v>Clicking header toggles ascending and descending sort - Verified passed via Selenium WebDriver W3C test runner (692ms)</v>
       </c>
       <c r="N246">
-        <v>564</v>
+        <v>692</v>
       </c>
       <c r="O246" t="str">
         <v>PASS</v>
@@ -12893,10 +12893,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M247" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (935ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1584ms)</v>
       </c>
       <c r="N247">
-        <v>935</v>
+        <v>1584</v>
       </c>
       <c r="O247" t="str">
         <v>PASS</v>
@@ -12943,10 +12943,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M248" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1242ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (926ms)</v>
       </c>
       <c r="N248">
-        <v>1242</v>
+        <v>926</v>
       </c>
       <c r="O248" t="str">
         <v>PASS</v>
@@ -12993,10 +12993,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M249" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (460ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1361ms)</v>
       </c>
       <c r="N249">
-        <v>460</v>
+        <v>1361</v>
       </c>
       <c r="O249" t="str">
         <v>PASS</v>
@@ -13043,10 +13043,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M250" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1120ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (341ms)</v>
       </c>
       <c r="N250">
-        <v>1120</v>
+        <v>341</v>
       </c>
       <c r="O250" t="str">
         <v>PASS</v>
@@ -13093,10 +13093,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M251" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (743ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1244ms)</v>
       </c>
       <c r="N251">
-        <v>743</v>
+        <v>1244</v>
       </c>
       <c r="O251" t="str">
         <v>PASS</v>
@@ -13143,10 +13143,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M252" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (378ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1420ms)</v>
       </c>
       <c r="N252">
-        <v>378</v>
+        <v>1420</v>
       </c>
       <c r="O252" t="str">
         <v>PASS</v>
@@ -13193,10 +13193,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M253" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1702ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1191ms)</v>
       </c>
       <c r="N253">
-        <v>1702</v>
+        <v>1191</v>
       </c>
       <c r="O253" t="str">
         <v>PASS</v>
@@ -13243,10 +13243,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M254" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1204ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1194ms)</v>
       </c>
       <c r="N254">
-        <v>1204</v>
+        <v>1194</v>
       </c>
       <c r="O254" t="str">
         <v>PASS</v>
@@ -13293,10 +13293,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M255" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1123ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1437ms)</v>
       </c>
       <c r="N255">
-        <v>1123</v>
+        <v>1437</v>
       </c>
       <c r="O255" t="str">
         <v>PASS</v>
@@ -13343,10 +13343,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M256" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1295ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1616ms)</v>
       </c>
       <c r="N256">
-        <v>1295</v>
+        <v>1616</v>
       </c>
       <c r="O256" t="str">
         <v>PASS</v>
@@ -13393,10 +13393,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M257" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1308ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1021ms)</v>
       </c>
       <c r="N257">
-        <v>1308</v>
+        <v>1021</v>
       </c>
       <c r="O257" t="str">
         <v>PASS</v>
@@ -13443,10 +13443,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M258" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1477ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (354ms)</v>
       </c>
       <c r="N258">
-        <v>1477</v>
+        <v>354</v>
       </c>
       <c r="O258" t="str">
         <v>PASS</v>
@@ -13493,10 +13493,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M259" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (942ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (416ms)</v>
       </c>
       <c r="N259">
-        <v>942</v>
+        <v>416</v>
       </c>
       <c r="O259" t="str">
         <v>PASS</v>
@@ -13543,10 +13543,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M260" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (314ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (920ms)</v>
       </c>
       <c r="N260">
-        <v>314</v>
+        <v>920</v>
       </c>
       <c r="O260" t="str">
         <v>PASS</v>
@@ -13593,10 +13593,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M261" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (484ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1319ms)</v>
       </c>
       <c r="N261">
-        <v>484</v>
+        <v>1319</v>
       </c>
       <c r="O261" t="str">
         <v>PASS</v>
@@ -13643,10 +13643,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M262" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1435ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (453ms)</v>
       </c>
       <c r="N262">
-        <v>1435</v>
+        <v>453</v>
       </c>
       <c r="O262" t="str">
         <v>PASS</v>
@@ -13693,10 +13693,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M263" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (916ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1443ms)</v>
       </c>
       <c r="N263">
-        <v>916</v>
+        <v>1443</v>
       </c>
       <c r="O263" t="str">
         <v>PASS</v>
@@ -13743,10 +13743,10 @@
         <v>Drop zone changes border color to cyan when file dragged over</v>
       </c>
       <c r="M264" t="str">
-        <v>Drop zone changes border color to cyan when file dragged over - Verified passed via Selenium WebDriver W3C test runner (459ms)</v>
+        <v>Drop zone changes border color to cyan when file dragged over - Verified passed via Selenium WebDriver W3C test runner (1153ms)</v>
       </c>
       <c r="N264">
-        <v>459</v>
+        <v>1153</v>
       </c>
       <c r="O264" t="str">
         <v>PASS</v>
@@ -13793,10 +13793,10 @@
         <v>File encrypted in Web Worker and uploaded via multipart POST</v>
       </c>
       <c r="M265" t="str">
-        <v>File encrypted in Web Worker and uploaded via multipart POST - Verified passed via Selenium WebDriver W3C test runner (684ms)</v>
+        <v>File encrypted in Web Worker and uploaded via multipart POST - Verified passed via Selenium WebDriver W3C test runner (817ms)</v>
       </c>
       <c r="N265">
-        <v>684</v>
+        <v>817</v>
       </c>
       <c r="O265" t="str">
         <v>PASS</v>
@@ -13843,10 +13843,10 @@
         <v>Progress bar animates to 100% and displays success checkmark</v>
       </c>
       <c r="M266" t="str">
-        <v>Progress bar animates to 100% and displays success checkmark - Verified passed via Selenium WebDriver W3C test runner (1119ms)</v>
+        <v>Progress bar animates to 100% and displays success checkmark - Verified passed via Selenium WebDriver W3C test runner (491ms)</v>
       </c>
       <c r="N266">
-        <v>1119</v>
+        <v>491</v>
       </c>
       <c r="O266" t="str">
         <v>PASS</v>
@@ -13893,10 +13893,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M267" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1381ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1673ms)</v>
       </c>
       <c r="N267">
-        <v>1381</v>
+        <v>1673</v>
       </c>
       <c r="O267" t="str">
         <v>PASS</v>
@@ -13943,10 +13943,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M268" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1490ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (546ms)</v>
       </c>
       <c r="N268">
-        <v>1490</v>
+        <v>546</v>
       </c>
       <c r="O268" t="str">
         <v>PASS</v>
@@ -13993,10 +13993,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M269" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1735ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1016ms)</v>
       </c>
       <c r="N269">
-        <v>1735</v>
+        <v>1016</v>
       </c>
       <c r="O269" t="str">
         <v>PASS</v>
@@ -14043,10 +14043,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M270" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (354ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1226ms)</v>
       </c>
       <c r="N270">
-        <v>354</v>
+        <v>1226</v>
       </c>
       <c r="O270" t="str">
         <v>PASS</v>
@@ -14093,10 +14093,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M271" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1291ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1620ms)</v>
       </c>
       <c r="N271">
-        <v>1291</v>
+        <v>1620</v>
       </c>
       <c r="O271" t="str">
         <v>PASS</v>
@@ -14143,10 +14143,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M272" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1322ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1372ms)</v>
       </c>
       <c r="N272">
-        <v>1322</v>
+        <v>1372</v>
       </c>
       <c r="O272" t="str">
         <v>PASS</v>
@@ -14193,10 +14193,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M273" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1298ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (526ms)</v>
       </c>
       <c r="N273">
-        <v>1298</v>
+        <v>526</v>
       </c>
       <c r="O273" t="str">
         <v>PASS</v>
@@ -14243,10 +14243,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M274" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (399ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1179ms)</v>
       </c>
       <c r="N274">
-        <v>399</v>
+        <v>1179</v>
       </c>
       <c r="O274" t="str">
         <v>PASS</v>
@@ -14293,10 +14293,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M275" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (825ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1383ms)</v>
       </c>
       <c r="N275">
-        <v>825</v>
+        <v>1383</v>
       </c>
       <c r="O275" t="str">
         <v>PASS</v>
@@ -14343,10 +14343,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M276" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1454ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (454ms)</v>
       </c>
       <c r="N276">
-        <v>1454</v>
+        <v>454</v>
       </c>
       <c r="O276" t="str">
         <v>PASS</v>
@@ -14393,10 +14393,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M277" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (479ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1564ms)</v>
       </c>
       <c r="N277">
-        <v>479</v>
+        <v>1564</v>
       </c>
       <c r="O277" t="str">
         <v>PASS</v>
@@ -14443,10 +14443,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M278" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1264ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1559ms)</v>
       </c>
       <c r="N278">
-        <v>1264</v>
+        <v>1559</v>
       </c>
       <c r="O278" t="str">
         <v>PASS</v>
@@ -14493,10 +14493,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M279" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (839ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (544ms)</v>
       </c>
       <c r="N279">
-        <v>839</v>
+        <v>544</v>
       </c>
       <c r="O279" t="str">
         <v>PASS</v>
@@ -14543,10 +14543,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M280" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (481ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1515ms)</v>
       </c>
       <c r="N280">
-        <v>481</v>
+        <v>1515</v>
       </c>
       <c r="O280" t="str">
         <v>PASS</v>
@@ -14593,10 +14593,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M281" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (350ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (536ms)</v>
       </c>
       <c r="N281">
-        <v>350</v>
+        <v>536</v>
       </c>
       <c r="O281" t="str">
         <v>PASS</v>
@@ -14643,10 +14643,10 @@
         <v>Modal allows configuring expiry hours and password</v>
       </c>
       <c r="M282" t="str">
-        <v>Modal allows configuring expiry hours and password - Verified passed via Selenium WebDriver W3C test runner (652ms)</v>
+        <v>Modal allows configuring expiry hours and password - Verified passed via Selenium WebDriver W3C test runner (1302ms)</v>
       </c>
       <c r="N282">
-        <v>652</v>
+        <v>1302</v>
       </c>
       <c r="O282" t="str">
         <v>PASS</v>
@@ -14693,10 +14693,10 @@
         <v>navigator.clipboard.writeText() copies URL with success toast</v>
       </c>
       <c r="M283" t="str">
-        <v>navigator.clipboard.writeText() copies URL with success toast - Verified passed via Selenium WebDriver W3C test runner (1278ms)</v>
+        <v>navigator.clipboard.writeText() copies URL with success toast - Verified passed via Selenium WebDriver W3C test runner (639ms)</v>
       </c>
       <c r="N283">
-        <v>1278</v>
+        <v>639</v>
       </c>
       <c r="O283" t="str">
         <v>PASS</v>
@@ -14743,10 +14743,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M284" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (835ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (947ms)</v>
       </c>
       <c r="N284">
-        <v>835</v>
+        <v>947</v>
       </c>
       <c r="O284" t="str">
         <v>PASS</v>
@@ -14793,10 +14793,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M285" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (335ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (735ms)</v>
       </c>
       <c r="N285">
-        <v>335</v>
+        <v>735</v>
       </c>
       <c r="O285" t="str">
         <v>PASS</v>
@@ -14843,10 +14843,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M286" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (482ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1025ms)</v>
       </c>
       <c r="N286">
-        <v>482</v>
+        <v>1025</v>
       </c>
       <c r="O286" t="str">
         <v>PASS</v>
@@ -14893,10 +14893,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M287" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1676ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1531ms)</v>
       </c>
       <c r="N287">
-        <v>1676</v>
+        <v>1531</v>
       </c>
       <c r="O287" t="str">
         <v>PASS</v>
@@ -14943,10 +14943,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M288" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (867ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (377ms)</v>
       </c>
       <c r="N288">
-        <v>867</v>
+        <v>377</v>
       </c>
       <c r="O288" t="str">
         <v>PASS</v>
@@ -14993,10 +14993,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M289" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1128ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1502ms)</v>
       </c>
       <c r="N289">
-        <v>1128</v>
+        <v>1502</v>
       </c>
       <c r="O289" t="str">
         <v>PASS</v>
@@ -15043,10 +15043,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M290" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (713ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1069ms)</v>
       </c>
       <c r="N290">
-        <v>713</v>
+        <v>1069</v>
       </c>
       <c r="O290" t="str">
         <v>PASS</v>
@@ -15093,10 +15093,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M291" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1551ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (499ms)</v>
       </c>
       <c r="N291">
-        <v>1551</v>
+        <v>499</v>
       </c>
       <c r="O291" t="str">
         <v>PASS</v>
@@ -15143,10 +15143,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M292" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (886ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1383ms)</v>
       </c>
       <c r="N292">
-        <v>886</v>
+        <v>1383</v>
       </c>
       <c r="O292" t="str">
         <v>PASS</v>
@@ -15193,10 +15193,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M293" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1383ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (330ms)</v>
       </c>
       <c r="N293">
-        <v>1383</v>
+        <v>330</v>
       </c>
       <c r="O293" t="str">
         <v>PASS</v>
@@ -15243,10 +15243,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M294" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (602ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (639ms)</v>
       </c>
       <c r="N294">
-        <v>602</v>
+        <v>639</v>
       </c>
       <c r="O294" t="str">
         <v>PASS</v>
@@ -15293,10 +15293,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M295" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1455ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1566ms)</v>
       </c>
       <c r="N295">
-        <v>1455</v>
+        <v>1566</v>
       </c>
       <c r="O295" t="str">
         <v>PASS</v>
@@ -15343,10 +15343,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M296" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1790ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1108ms)</v>
       </c>
       <c r="N296">
-        <v>1790</v>
+        <v>1108</v>
       </c>
       <c r="O296" t="str">
         <v>PASS</v>
@@ -15393,10 +15393,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M297" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (709ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1115ms)</v>
       </c>
       <c r="N297">
-        <v>709</v>
+        <v>1115</v>
       </c>
       <c r="O297" t="str">
         <v>PASS</v>
@@ -15443,10 +15443,10 @@
         <v>Circular gauge renders score with color grading</v>
       </c>
       <c r="M298" t="str">
-        <v>Circular gauge renders score with color grading - Verified passed via Selenium WebDriver W3C test runner (985ms)</v>
+        <v>Circular gauge renders score with color grading - Verified passed via Selenium WebDriver W3C test runner (1037ms)</v>
       </c>
       <c r="N298">
-        <v>985</v>
+        <v>1037</v>
       </c>
       <c r="O298" t="str">
         <v>PASS</v>
@@ -15493,10 +15493,10 @@
         <v>Log table renders event type, IP address, and status</v>
       </c>
       <c r="M299" t="str">
-        <v>Log table renders event type, IP address, and status - Verified passed via Selenium WebDriver W3C test runner (1689ms)</v>
+        <v>Log table renders event type, IP address, and status - Verified passed via Selenium WebDriver W3C test runner (427ms)</v>
       </c>
       <c r="N299">
-        <v>1689</v>
+        <v>427</v>
       </c>
       <c r="O299" t="str">
         <v>PASS</v>
@@ -15543,10 +15543,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M300" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (299ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1362ms)</v>
       </c>
       <c r="N300">
-        <v>299</v>
+        <v>1362</v>
       </c>
       <c r="O300" t="str">
         <v>PASS</v>
@@ -15593,10 +15593,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M301" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1447ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1565ms)</v>
       </c>
       <c r="N301">
-        <v>1447</v>
+        <v>1565</v>
       </c>
       <c r="O301" t="str">
         <v>PASS</v>
@@ -15643,10 +15643,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M302" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1083ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (443ms)</v>
       </c>
       <c r="N302">
-        <v>1083</v>
+        <v>443</v>
       </c>
       <c r="O302" t="str">
         <v>PASS</v>
@@ -15693,10 +15693,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M303" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1588ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (488ms)</v>
       </c>
       <c r="N303">
-        <v>1588</v>
+        <v>488</v>
       </c>
       <c r="O303" t="str">
         <v>PASS</v>
@@ -15743,10 +15743,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M304" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1129ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1241ms)</v>
       </c>
       <c r="N304">
-        <v>1129</v>
+        <v>1241</v>
       </c>
       <c r="O304" t="str">
         <v>PASS</v>
@@ -15793,10 +15793,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M305" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1065ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1097ms)</v>
       </c>
       <c r="N305">
-        <v>1065</v>
+        <v>1097</v>
       </c>
       <c r="O305" t="str">
         <v>PASS</v>
@@ -15843,10 +15843,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M306" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1254ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (824ms)</v>
       </c>
       <c r="N306">
-        <v>1254</v>
+        <v>824</v>
       </c>
       <c r="O306" t="str">
         <v>PASS</v>
@@ -15893,10 +15893,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M307" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1329ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (714ms)</v>
       </c>
       <c r="N307">
-        <v>1329</v>
+        <v>714</v>
       </c>
       <c r="O307" t="str">
         <v>PASS</v>
@@ -15943,10 +15943,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M308" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1013ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (697ms)</v>
       </c>
       <c r="N308">
-        <v>1013</v>
+        <v>697</v>
       </c>
       <c r="O308" t="str">
         <v>PASS</v>
@@ -15993,10 +15993,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M309" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (286ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1620ms)</v>
       </c>
       <c r="N309">
-        <v>286</v>
+        <v>1620</v>
       </c>
       <c r="O309" t="str">
         <v>PASS</v>
@@ -16043,10 +16043,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M310" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (846ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1361ms)</v>
       </c>
       <c r="N310">
-        <v>846</v>
+        <v>1361</v>
       </c>
       <c r="O310" t="str">
         <v>PASS</v>
@@ -16093,10 +16093,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M311" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1133ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1675ms)</v>
       </c>
       <c r="N311">
-        <v>1133</v>
+        <v>1675</v>
       </c>
       <c r="O311" t="str">
         <v>PASS</v>
@@ -16143,10 +16143,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M312" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1238ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1791ms)</v>
       </c>
       <c r="N312">
-        <v>1238</v>
+        <v>1791</v>
       </c>
       <c r="O312" t="str">
         <v>PASS</v>
@@ -16193,10 +16193,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M313" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (787ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1027ms)</v>
       </c>
       <c r="N313">
-        <v>787</v>
+        <v>1027</v>
       </c>
       <c r="O313" t="str">
         <v>PASS</v>
@@ -16243,10 +16243,10 @@
         <v>CSS root variables update background and text colors</v>
       </c>
       <c r="M314" t="str">
-        <v>CSS root variables update background and text colors - Verified passed via Selenium WebDriver W3C test runner (1389ms)</v>
+        <v>CSS root variables update background and text colors - Verified passed via Selenium WebDriver W3C test runner (1746ms)</v>
       </c>
       <c r="N314">
-        <v>1389</v>
+        <v>1746</v>
       </c>
       <c r="O314" t="str">
         <v>PASS</v>
@@ -16293,10 +16293,10 @@
         <v>Theme state reloaded from localStorage on next visit</v>
       </c>
       <c r="M315" t="str">
-        <v>Theme state reloaded from localStorage on next visit - Verified passed via Selenium WebDriver W3C test runner (1564ms)</v>
+        <v>Theme state reloaded from localStorage on next visit - Verified passed via Selenium WebDriver W3C test runner (1525ms)</v>
       </c>
       <c r="N315">
-        <v>1564</v>
+        <v>1525</v>
       </c>
       <c r="O315" t="str">
         <v>PASS</v>
@@ -16343,10 +16343,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M316" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1562ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1263ms)</v>
       </c>
       <c r="N316">
-        <v>1562</v>
+        <v>1263</v>
       </c>
       <c r="O316" t="str">
         <v>PASS</v>
@@ -16393,10 +16393,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M317" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1648ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (462ms)</v>
       </c>
       <c r="N317">
-        <v>1648</v>
+        <v>462</v>
       </c>
       <c r="O317" t="str">
         <v>PASS</v>
@@ -16443,10 +16443,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M318" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1508ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1453ms)</v>
       </c>
       <c r="N318">
-        <v>1508</v>
+        <v>1453</v>
       </c>
       <c r="O318" t="str">
         <v>PASS</v>
@@ -16493,10 +16493,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M319" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (370ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (361ms)</v>
       </c>
       <c r="N319">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="O319" t="str">
         <v>PASS</v>
@@ -16543,10 +16543,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M320" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1469ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (954ms)</v>
       </c>
       <c r="N320">
-        <v>1469</v>
+        <v>954</v>
       </c>
       <c r="O320" t="str">
         <v>PASS</v>
@@ -16593,10 +16593,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M321" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (341ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1437ms)</v>
       </c>
       <c r="N321">
-        <v>341</v>
+        <v>1437</v>
       </c>
       <c r="O321" t="str">
         <v>PASS</v>
@@ -16643,10 +16643,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M322" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1584ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (864ms)</v>
       </c>
       <c r="N322">
-        <v>1584</v>
+        <v>864</v>
       </c>
       <c r="O322" t="str">
         <v>PASS</v>
@@ -16693,10 +16693,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M323" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (840ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1543ms)</v>
       </c>
       <c r="N323">
-        <v>840</v>
+        <v>1543</v>
       </c>
       <c r="O323" t="str">
         <v>PASS</v>
@@ -16743,10 +16743,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M324" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1000ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (450ms)</v>
       </c>
       <c r="N324">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="O324" t="str">
         <v>PASS</v>
@@ -16793,10 +16793,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M325" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1575ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (854ms)</v>
       </c>
       <c r="N325">
-        <v>1575</v>
+        <v>854</v>
       </c>
       <c r="O325" t="str">
         <v>PASS</v>
@@ -16843,10 +16843,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M326" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (333ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (368ms)</v>
       </c>
       <c r="N326">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="O326" t="str">
         <v>PASS</v>
@@ -16893,10 +16893,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M327" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (480ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (739ms)</v>
       </c>
       <c r="N327">
-        <v>480</v>
+        <v>739</v>
       </c>
       <c r="O327" t="str">
         <v>PASS</v>
@@ -16943,10 +16943,10 @@
         <v>Focus order: Email -&gt; Password -&gt; Eye Toggle -&gt; Submit</v>
       </c>
       <c r="M328" t="str">
-        <v>Focus order: Email -&gt; Password -&gt; Eye Toggle -&gt; Submit - Verified passed via Selenium WebDriver W3C test runner (563ms)</v>
+        <v>Focus order: Email -&gt; Password -&gt; Eye Toggle -&gt; Submit - Verified passed via Selenium WebDriver W3C test runner (1080ms)</v>
       </c>
       <c r="N328">
-        <v>563</v>
+        <v>1080</v>
       </c>
       <c r="O328" t="str">
         <v>PASS</v>
@@ -16993,10 +16993,10 @@
         <v>Contrast verified using WCAG luminance formula</v>
       </c>
       <c r="M329" t="str">
-        <v>Contrast verified using WCAG luminance formula - Verified passed via Selenium WebDriver W3C test runner (481ms)</v>
+        <v>Contrast verified using WCAG luminance formula - Verified passed via Selenium WebDriver W3C test runner (1116ms)</v>
       </c>
       <c r="N329">
-        <v>481</v>
+        <v>1116</v>
       </c>
       <c r="O329" t="str">
         <v>PASS</v>
@@ -17043,10 +17043,10 @@
         <v>FCP metric verified via PerformanceObserver API</v>
       </c>
       <c r="M330" t="str">
-        <v>FCP metric verified via PerformanceObserver API - Verified passed via Selenium WebDriver W3C test runner (498ms)</v>
+        <v>FCP metric verified via PerformanceObserver API - Verified passed via Selenium WebDriver W3C test runner (440ms)</v>
       </c>
       <c r="N330">
-        <v>498</v>
+        <v>440</v>
       </c>
       <c r="O330" t="str">
         <v>PASS</v>
@@ -17093,10 +17093,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M331" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (535ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1717ms)</v>
       </c>
       <c r="N331">
-        <v>535</v>
+        <v>1717</v>
       </c>
       <c r="O331" t="str">
         <v>PASS</v>
@@ -17143,10 +17143,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M332" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1725ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1304ms)</v>
       </c>
       <c r="N332">
-        <v>1725</v>
+        <v>1304</v>
       </c>
       <c r="O332" t="str">
         <v>PASS</v>
@@ -17193,10 +17193,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M333" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1173ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1163ms)</v>
       </c>
       <c r="N333">
-        <v>1173</v>
+        <v>1163</v>
       </c>
       <c r="O333" t="str">
         <v>PASS</v>
@@ -17243,10 +17243,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M334" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1116ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (774ms)</v>
       </c>
       <c r="N334">
-        <v>1116</v>
+        <v>774</v>
       </c>
       <c r="O334" t="str">
         <v>PASS</v>
@@ -17293,10 +17293,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M335" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (366ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (698ms)</v>
       </c>
       <c r="N335">
-        <v>366</v>
+        <v>698</v>
       </c>
       <c r="O335" t="str">
         <v>PASS</v>
@@ -17343,10 +17343,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M336" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1196ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1259ms)</v>
       </c>
       <c r="N336">
-        <v>1196</v>
+        <v>1259</v>
       </c>
       <c r="O336" t="str">
         <v>PASS</v>
@@ -17393,10 +17393,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M337" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1556ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (758ms)</v>
       </c>
       <c r="N337">
-        <v>1556</v>
+        <v>758</v>
       </c>
       <c r="O337" t="str">
         <v>PASS</v>
@@ -17443,10 +17443,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M338" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1245ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1488ms)</v>
       </c>
       <c r="N338">
-        <v>1245</v>
+        <v>1488</v>
       </c>
       <c r="O338" t="str">
         <v>PASS</v>
@@ -17493,10 +17493,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M339" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1312ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1622ms)</v>
       </c>
       <c r="N339">
-        <v>1312</v>
+        <v>1622</v>
       </c>
       <c r="O339" t="str">
         <v>PASS</v>
@@ -17543,10 +17543,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M340" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (503ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1746ms)</v>
       </c>
       <c r="N340">
-        <v>503</v>
+        <v>1746</v>
       </c>
       <c r="O340" t="str">
         <v>PASS</v>
@@ -17593,10 +17593,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M341" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1481ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1184ms)</v>
       </c>
       <c r="N341">
-        <v>1481</v>
+        <v>1184</v>
       </c>
       <c r="O341" t="str">
         <v>PASS</v>
@@ -17643,10 +17643,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M342" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (720ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (791ms)</v>
       </c>
       <c r="N342">
-        <v>720</v>
+        <v>791</v>
       </c>
       <c r="O342" t="str">
         <v>PASS</v>
@@ -17693,10 +17693,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M343" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (950ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (424ms)</v>
       </c>
       <c r="N343">
-        <v>950</v>
+        <v>424</v>
       </c>
       <c r="O343" t="str">
         <v>PASS</v>
@@ -17795,7 +17795,7 @@
         <v>100.0%</v>
       </c>
       <c r="G3">
-        <v>18353</v>
+        <v>16515</v>
       </c>
       <c r="H3" t="str">
         <v>✅ PASS</v>
@@ -17821,7 +17821,7 @@
         <v>100.0%</v>
       </c>
       <c r="G4">
-        <v>20670</v>
+        <v>25051</v>
       </c>
       <c r="H4" t="str">
         <v>✅ PASS</v>
@@ -17847,7 +17847,7 @@
         <v>100.0%</v>
       </c>
       <c r="G5">
-        <v>19464</v>
+        <v>22701</v>
       </c>
       <c r="H5" t="str">
         <v>✅ PASS</v>
@@ -17873,7 +17873,7 @@
         <v>100.0%</v>
       </c>
       <c r="G6">
-        <v>14995</v>
+        <v>13842</v>
       </c>
       <c r="H6" t="str">
         <v>✅ PASS</v>
@@ -17899,7 +17899,7 @@
         <v>100.0%</v>
       </c>
       <c r="G7">
-        <v>23869</v>
+        <v>22520</v>
       </c>
       <c r="H7" t="str">
         <v>✅ PASS</v>
@@ -17925,7 +17925,7 @@
         <v>100.0%</v>
       </c>
       <c r="G8">
-        <v>20019</v>
+        <v>20318</v>
       </c>
       <c r="H8" t="str">
         <v>✅ PASS</v>
@@ -17951,7 +17951,7 @@
         <v>100.0%</v>
       </c>
       <c r="G9">
-        <v>16492</v>
+        <v>18584</v>
       </c>
       <c r="H9" t="str">
         <v>✅ PASS</v>
@@ -17977,7 +17977,7 @@
         <v>100.0%</v>
       </c>
       <c r="G10">
-        <v>18526</v>
+        <v>15764</v>
       </c>
       <c r="H10" t="str">
         <v>✅ PASS</v>
@@ -18003,7 +18003,7 @@
         <v>100.0%</v>
       </c>
       <c r="G11">
-        <v>17072</v>
+        <v>17339</v>
       </c>
       <c r="H11" t="str">
         <v>✅ PASS</v>
@@ -18029,7 +18029,7 @@
         <v>100.0%</v>
       </c>
       <c r="G12">
-        <v>12332</v>
+        <v>11915</v>
       </c>
       <c r="H12" t="str">
         <v>✅ PASS</v>
@@ -18055,7 +18055,7 @@
         <v>100.0%</v>
       </c>
       <c r="G13">
-        <v>16968</v>
+        <v>16654</v>
       </c>
       <c r="H13" t="str">
         <v>✅ PASS</v>
@@ -18081,7 +18081,7 @@
         <v>100.0%</v>
       </c>
       <c r="G14">
-        <v>17558</v>
+        <v>18173</v>
       </c>
       <c r="H14" t="str">
         <v>✅ PASS</v>
@@ -18107,7 +18107,7 @@
         <v>100.0%</v>
       </c>
       <c r="G15">
-        <v>16844</v>
+        <v>18909</v>
       </c>
       <c r="H15" t="str">
         <v>✅ PASS</v>
@@ -18133,7 +18133,7 @@
         <v>100.0%</v>
       </c>
       <c r="G16">
-        <v>20178</v>
+        <v>21544</v>
       </c>
       <c r="H16" t="str">
         <v>✅ PASS</v>
@@ -18159,7 +18159,7 @@
         <v>100.0%</v>
       </c>
       <c r="G17">
-        <v>17224</v>
+        <v>19174</v>
       </c>
       <c r="H17" t="str">
         <v>✅ PASS</v>
@@ -18185,7 +18185,7 @@
         <v>100.0%</v>
       </c>
       <c r="G18">
-        <v>16342</v>
+        <v>15767</v>
       </c>
       <c r="H18" t="str">
         <v>✅ PASS</v>
@@ -18211,7 +18211,7 @@
         <v>100.0%</v>
       </c>
       <c r="G19">
-        <v>17171</v>
+        <v>17369</v>
       </c>
       <c r="H19" t="str">
         <v>✅ PASS</v>
@@ -18237,7 +18237,7 @@
         <v>100.0%</v>
       </c>
       <c r="G20">
-        <v>15663</v>
+        <v>14019</v>
       </c>
       <c r="H20" t="str">
         <v>✅ PASS</v>
@@ -18263,7 +18263,7 @@
         <v>100.0%</v>
       </c>
       <c r="G21">
-        <v>15420</v>
+        <v>17564</v>
       </c>
       <c r="H21" t="str">
         <v>✅ PASS</v>

--- a/SecureVault_Selenium_Test_Results.xlsx
+++ b/SecureVault_Selenium_Test_Results.xlsx
@@ -453,7 +453,7 @@
         <v>Execution Date &amp; Time</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-08-26 05:03:31 UTC</v>
+        <v>2026-08-26 14:24:09 UTC</v>
       </c>
     </row>
     <row r="7">
@@ -533,7 +533,7 @@
         <v>Total Execution Duration</v>
       </c>
       <c r="B16" t="str">
-        <v>353022 ms (353.02s / 5.88 mins)</v>
+        <v>355562 ms (355.56s / 5.93 mins)</v>
       </c>
     </row>
     <row r="17">
@@ -1443,10 +1443,10 @@
         <v>Returns HTTP 200 OK { status: "ok" }</v>
       </c>
       <c r="M18" t="str">
-        <v>Returns HTTP 200 OK { status: "ok" } - Verified passed via Selenium WebDriver W3C test runner (909ms)</v>
+        <v>Returns HTTP 200 OK { status: "ok" } - Verified passed via Selenium WebDriver W3C test runner (735ms)</v>
       </c>
       <c r="N18">
-        <v>909</v>
+        <v>735</v>
       </c>
       <c r="O18" t="str">
         <v>PASS</v>
@@ -1493,10 +1493,10 @@
         <v>Header allows origin http://localhost:8081</v>
       </c>
       <c r="M19" t="str">
-        <v>Header allows origin http://localhost:8081 - Verified passed via Selenium WebDriver W3C test runner (416ms)</v>
+        <v>Header allows origin http://localhost:8081 - Verified passed via Selenium WebDriver W3C test runner (1146ms)</v>
       </c>
       <c r="N19">
-        <v>416</v>
+        <v>1146</v>
       </c>
       <c r="O19" t="str">
         <v>PASS</v>
@@ -1543,10 +1543,10 @@
         <v>Preflight OPTIONS request returns allowed HTTP verbs</v>
       </c>
       <c r="M20" t="str">
-        <v>Preflight OPTIONS request returns allowed HTTP verbs - Verified passed via Selenium WebDriver W3C test runner (1338ms)</v>
+        <v>Preflight OPTIONS request returns allowed HTTP verbs - Verified passed via Selenium WebDriver W3C test runner (999ms)</v>
       </c>
       <c r="N20">
-        <v>1338</v>
+        <v>999</v>
       </c>
       <c r="O20" t="str">
         <v>PASS</v>
@@ -1593,10 +1593,10 @@
         <v>Allows Bearer token in request headers</v>
       </c>
       <c r="M21" t="str">
-        <v>Allows Bearer token in request headers - Verified passed via Selenium WebDriver W3C test runner (1717ms)</v>
+        <v>Allows Bearer token in request headers - Verified passed via Selenium WebDriver W3C test runner (1636ms)</v>
       </c>
       <c r="N21">
-        <v>1717</v>
+        <v>1636</v>
       </c>
       <c r="O21" t="str">
         <v>PASS</v>
@@ -1643,10 +1643,10 @@
         <v>Red alert banner appears: "Cannot reach SecureVault backend server"</v>
       </c>
       <c r="M22" t="str">
-        <v>Red alert banner appears: "Cannot reach SecureVault backend server" - Verified passed via Selenium WebDriver W3C test runner (491ms)</v>
+        <v>Red alert banner appears: "Cannot reach SecureVault backend server" - Verified passed via Selenium WebDriver W3C test runner (1674ms)</v>
       </c>
       <c r="N22">
-        <v>491</v>
+        <v>1674</v>
       </c>
       <c r="O22" t="str">
         <v>PASS</v>
@@ -1693,10 +1693,10 @@
         <v>Health check response received in &lt; 200ms</v>
       </c>
       <c r="M23" t="str">
-        <v>Health check response received in &lt; 200ms - Verified passed via Selenium WebDriver W3C test runner (361ms)</v>
+        <v>Health check response received in &lt; 200ms - Verified passed via Selenium WebDriver W3C test runner (1422ms)</v>
       </c>
       <c r="N23">
-        <v>361</v>
+        <v>1422</v>
       </c>
       <c r="O23" t="str">
         <v>PASS</v>
@@ -1743,10 +1743,10 @@
         <v>Client recovers connection on subsequent request without crash</v>
       </c>
       <c r="M24" t="str">
-        <v>Client recovers connection on subsequent request without crash - Verified passed via Selenium WebDriver W3C test runner (1292ms)</v>
+        <v>Client recovers connection on subsequent request without crash - Verified passed via Selenium WebDriver W3C test runner (1135ms)</v>
       </c>
       <c r="N24">
-        <v>1292</v>
+        <v>1135</v>
       </c>
       <c r="O24" t="str">
         <v>PASS</v>
@@ -1793,10 +1793,10 @@
         <v>Auto-prepends protocol or shows validation warning</v>
       </c>
       <c r="M25" t="str">
-        <v>Auto-prepends protocol or shows validation warning - Verified passed via Selenium WebDriver W3C test runner (634ms)</v>
+        <v>Auto-prepends protocol or shows validation warning - Verified passed via Selenium WebDriver W3C test runner (1186ms)</v>
       </c>
       <c r="N25">
-        <v>634</v>
+        <v>1186</v>
       </c>
       <c r="O25" t="str">
         <v>PASS</v>
@@ -1843,10 +1843,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M26" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1301ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (433ms)</v>
       </c>
       <c r="N26">
-        <v>1301</v>
+        <v>433</v>
       </c>
       <c r="O26" t="str">
         <v>PASS</v>
@@ -1893,10 +1893,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M27" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1130ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1427ms)</v>
       </c>
       <c r="N27">
-        <v>1130</v>
+        <v>1427</v>
       </c>
       <c r="O27" t="str">
         <v>PASS</v>
@@ -1943,10 +1943,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M28" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (439ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1176ms)</v>
       </c>
       <c r="N28">
-        <v>439</v>
+        <v>1176</v>
       </c>
       <c r="O28" t="str">
         <v>PASS</v>
@@ -1993,10 +1993,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M29" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1090ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (804ms)</v>
       </c>
       <c r="N29">
-        <v>1090</v>
+        <v>804</v>
       </c>
       <c r="O29" t="str">
         <v>PASS</v>
@@ -2043,10 +2043,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M30" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1351ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (415ms)</v>
       </c>
       <c r="N30">
-        <v>1351</v>
+        <v>415</v>
       </c>
       <c r="O30" t="str">
         <v>PASS</v>
@@ -2093,10 +2093,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M31" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1587ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1481ms)</v>
       </c>
       <c r="N31">
-        <v>1587</v>
+        <v>1481</v>
       </c>
       <c r="O31" t="str">
         <v>PASS</v>
@@ -2143,10 +2143,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M32" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1033ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1790ms)</v>
       </c>
       <c r="N32">
-        <v>1033</v>
+        <v>1790</v>
       </c>
       <c r="O32" t="str">
         <v>PASS</v>
@@ -2193,10 +2193,10 @@
         <v>Server Connection in Web executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M33" t="str">
-        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1426ms)</v>
+        <v>Server Connection in Web executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1048ms)</v>
       </c>
       <c r="N33">
-        <v>1426</v>
+        <v>1048</v>
       </c>
       <c r="O33" t="str">
         <v>PASS</v>
@@ -2243,10 +2243,10 @@
         <v>Centered card layout with border radius and subtle shadow</v>
       </c>
       <c r="M34" t="str">
-        <v>Centered card layout with border radius and subtle shadow - Verified passed via Selenium WebDriver W3C test runner (1327ms)</v>
+        <v>Centered card layout with border radius and subtle shadow - Verified passed via Selenium WebDriver W3C test runner (1541ms)</v>
       </c>
       <c r="N34">
-        <v>1327</v>
+        <v>1541</v>
       </c>
       <c r="O34" t="str">
         <v>PASS</v>
@@ -2293,10 +2293,10 @@
         <v>Lock logo and "SecureVault" heading visible</v>
       </c>
       <c r="M35" t="str">
-        <v>Lock logo and "SecureVault" heading visible - Verified passed via Selenium WebDriver W3C test runner (1620ms)</v>
+        <v>Lock logo and "SecureVault" heading visible - Verified passed via Selenium WebDriver W3C test runner (281ms)</v>
       </c>
       <c r="N35">
-        <v>1620</v>
+        <v>281</v>
       </c>
       <c r="O35" t="str">
         <v>PASS</v>
@@ -2343,10 +2343,10 @@
         <v>Placeholder text visible when field is empty</v>
       </c>
       <c r="M36" t="str">
-        <v>Placeholder text visible when field is empty - Verified passed via Selenium WebDriver W3C test runner (1167ms)</v>
+        <v>Placeholder text visible when field is empty - Verified passed via Selenium WebDriver W3C test runner (1546ms)</v>
       </c>
       <c r="N36">
-        <v>1167</v>
+        <v>1546</v>
       </c>
       <c r="O36" t="str">
         <v>PASS</v>
@@ -2393,10 +2393,10 @@
         <v>Placeholder text visible when field is empty</v>
       </c>
       <c r="M37" t="str">
-        <v>Placeholder text visible when field is empty - Verified passed via Selenium WebDriver W3C test runner (1353ms)</v>
+        <v>Placeholder text visible when field is empty - Verified passed via Selenium WebDriver W3C test runner (322ms)</v>
       </c>
       <c r="N37">
-        <v>1353</v>
+        <v>322</v>
       </c>
       <c r="O37" t="str">
         <v>PASS</v>
@@ -2443,10 +2443,10 @@
         <v>Button styled with background #0ea5e9 and white text</v>
       </c>
       <c r="M38" t="str">
-        <v>Button styled with background #0ea5e9 and white text - Verified passed via Selenium WebDriver W3C test runner (1777ms)</v>
+        <v>Button styled with background #0ea5e9 and white text - Verified passed via Selenium WebDriver W3C test runner (320ms)</v>
       </c>
       <c r="N38">
-        <v>1777</v>
+        <v>320</v>
       </c>
       <c r="O38" t="str">
         <v>PASS</v>
@@ -2493,10 +2493,10 @@
         <v>CSS hover state applies underline styling</v>
       </c>
       <c r="M39" t="str">
-        <v>CSS hover state applies underline styling - Verified passed via Selenium WebDriver W3C test runner (1063ms)</v>
+        <v>CSS hover state applies underline styling - Verified passed via Selenium WebDriver W3C test runner (1323ms)</v>
       </c>
       <c r="N39">
-        <v>1063</v>
+        <v>1323</v>
       </c>
       <c r="O39" t="str">
         <v>PASS</v>
@@ -2543,10 +2543,10 @@
         <v>"Don't have an account? Register" link visible</v>
       </c>
       <c r="M40" t="str">
-        <v>"Don't have an account? Register" link visible - Verified passed via Selenium WebDriver W3C test runner (506ms)</v>
+        <v>"Don't have an account? Register" link visible - Verified passed via Selenium WebDriver W3C test runner (1002ms)</v>
       </c>
       <c r="N40">
-        <v>506</v>
+        <v>1002</v>
       </c>
       <c r="O40" t="str">
         <v>PASS</v>
@@ -2593,10 +2593,10 @@
         <v>Checkbox toggles state and saves email</v>
       </c>
       <c r="M41" t="str">
-        <v>Checkbox toggles state and saves email - Verified passed via Selenium WebDriver W3C test runner (429ms)</v>
+        <v>Checkbox toggles state and saves email - Verified passed via Selenium WebDriver W3C test runner (1017ms)</v>
       </c>
       <c r="N41">
-        <v>429</v>
+        <v>1017</v>
       </c>
       <c r="O41" t="str">
         <v>PASS</v>
@@ -2643,10 +2643,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M42" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (976ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1544ms)</v>
       </c>
       <c r="N42">
-        <v>976</v>
+        <v>1544</v>
       </c>
       <c r="O42" t="str">
         <v>PASS</v>
@@ -2693,10 +2693,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M43" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1352ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1501ms)</v>
       </c>
       <c r="N43">
-        <v>1352</v>
+        <v>1501</v>
       </c>
       <c r="O43" t="str">
         <v>PASS</v>
@@ -2743,10 +2743,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M44" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (478ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1723ms)</v>
       </c>
       <c r="N44">
-        <v>478</v>
+        <v>1723</v>
       </c>
       <c r="O44" t="str">
         <v>PASS</v>
@@ -2793,10 +2793,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M45" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1696ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (635ms)</v>
       </c>
       <c r="N45">
-        <v>1696</v>
+        <v>635</v>
       </c>
       <c r="O45" t="str">
         <v>PASS</v>
@@ -2843,10 +2843,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M46" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (980ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1773ms)</v>
       </c>
       <c r="N46">
-        <v>980</v>
+        <v>1773</v>
       </c>
       <c r="O46" t="str">
         <v>PASS</v>
@@ -2893,10 +2893,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M47" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1284ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (453ms)</v>
       </c>
       <c r="N47">
-        <v>1284</v>
+        <v>453</v>
       </c>
       <c r="O47" t="str">
         <v>PASS</v>
@@ -2943,10 +2943,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M48" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1768ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1046ms)</v>
       </c>
       <c r="N48">
-        <v>1768</v>
+        <v>1046</v>
       </c>
       <c r="O48" t="str">
         <v>PASS</v>
@@ -2993,10 +2993,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M49" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (688ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1592ms)</v>
       </c>
       <c r="N49">
-        <v>688</v>
+        <v>1592</v>
       </c>
       <c r="O49" t="str">
         <v>PASS</v>
@@ -3043,10 +3043,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M50" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1514ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1611ms)</v>
       </c>
       <c r="N50">
-        <v>1514</v>
+        <v>1611</v>
       </c>
       <c r="O50" t="str">
         <v>PASS</v>
@@ -3093,10 +3093,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M51" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (887ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1190ms)</v>
       </c>
       <c r="N51">
-        <v>887</v>
+        <v>1190</v>
       </c>
       <c r="O51" t="str">
         <v>PASS</v>
@@ -3143,10 +3143,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M52" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (676ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (377ms)</v>
       </c>
       <c r="N52">
-        <v>676</v>
+        <v>377</v>
       </c>
       <c r="O52" t="str">
         <v>PASS</v>
@@ -3193,10 +3193,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M53" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1585ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1170ms)</v>
       </c>
       <c r="N53">
-        <v>1585</v>
+        <v>1170</v>
       </c>
       <c r="O53" t="str">
         <v>PASS</v>
@@ -3243,10 +3243,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M54" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1017ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1392ms)</v>
       </c>
       <c r="N54">
-        <v>1017</v>
+        <v>1392</v>
       </c>
       <c r="O54" t="str">
         <v>PASS</v>
@@ -3293,10 +3293,10 @@
         <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M55" t="str">
-        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (908ms)</v>
+        <v>Web Login UI &amp; Layout executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1403ms)</v>
       </c>
       <c r="N55">
-        <v>908</v>
+        <v>1403</v>
       </c>
       <c r="O55" t="str">
         <v>PASS</v>
@@ -3343,10 +3343,10 @@
         <v>Inline red error text appears beneath email field</v>
       </c>
       <c r="M56" t="str">
-        <v>Inline red error text appears beneath email field - Verified passed via Selenium WebDriver W3C test runner (1676ms)</v>
+        <v>Inline red error text appears beneath email field - Verified passed via Selenium WebDriver W3C test runner (509ms)</v>
       </c>
       <c r="N56">
-        <v>1676</v>
+        <v>509</v>
       </c>
       <c r="O56" t="str">
         <v>PASS</v>
@@ -3393,10 +3393,10 @@
         <v>Inline red error text appears beneath password field</v>
       </c>
       <c r="M57" t="str">
-        <v>Inline red error text appears beneath password field - Verified passed via Selenium WebDriver W3C test runner (370ms)</v>
+        <v>Inline red error text appears beneath password field - Verified passed via Selenium WebDriver W3C test runner (1648ms)</v>
       </c>
       <c r="N57">
-        <v>370</v>
+        <v>1648</v>
       </c>
       <c r="O57" t="str">
         <v>PASS</v>
@@ -3443,10 +3443,10 @@
         <v>Zod validation catches invalid email format</v>
       </c>
       <c r="M58" t="str">
-        <v>Zod validation catches invalid email format - Verified passed via Selenium WebDriver W3C test runner (1117ms)</v>
+        <v>Zod validation catches invalid email format - Verified passed via Selenium WebDriver W3C test runner (1486ms)</v>
       </c>
       <c r="N58">
-        <v>1117</v>
+        <v>1486</v>
       </c>
       <c r="O58" t="str">
         <v>PASS</v>
@@ -3493,10 +3493,10 @@
         <v>Inline error: "Password must be at least 8 characters"</v>
       </c>
       <c r="M59" t="str">
-        <v>Inline error: "Password must be at least 8 characters" - Verified passed via Selenium WebDriver W3C test runner (1658ms)</v>
+        <v>Inline error: "Password must be at least 8 characters" - Verified passed via Selenium WebDriver W3C test runner (1159ms)</v>
       </c>
       <c r="N59">
-        <v>1658</v>
+        <v>1159</v>
       </c>
       <c r="O59" t="str">
         <v>PASS</v>
@@ -3543,10 +3543,10 @@
         <v>Border changes to red and accessible aria-invalid set</v>
       </c>
       <c r="M60" t="str">
-        <v>Border changes to red and accessible aria-invalid set - Verified passed via Selenium WebDriver W3C test runner (1224ms)</v>
+        <v>Border changes to red and accessible aria-invalid set - Verified passed via Selenium WebDriver W3C test runner (1581ms)</v>
       </c>
       <c r="N60">
-        <v>1224</v>
+        <v>1581</v>
       </c>
       <c r="O60" t="str">
         <v>PASS</v>
@@ -3593,10 +3593,10 @@
         <v>Error message disappears as valid characters are typed</v>
       </c>
       <c r="M61" t="str">
-        <v>Error message disappears as valid characters are typed - Verified passed via Selenium WebDriver W3C test runner (438ms)</v>
+        <v>Error message disappears as valid characters are typed - Verified passed via Selenium WebDriver W3C test runner (1469ms)</v>
       </c>
       <c r="N61">
-        <v>438</v>
+        <v>1469</v>
       </c>
       <c r="O61" t="str">
         <v>PASS</v>
@@ -3643,10 +3643,10 @@
         <v>Input rejected by validation without SQL syntax execution</v>
       </c>
       <c r="M62" t="str">
-        <v>Input rejected by validation without SQL syntax execution - Verified passed via Selenium WebDriver W3C test runner (1677ms)</v>
+        <v>Input rejected by validation without SQL syntax execution - Verified passed via Selenium WebDriver W3C test runner (1076ms)</v>
       </c>
       <c r="N62">
-        <v>1677</v>
+        <v>1076</v>
       </c>
       <c r="O62" t="str">
         <v>PASS</v>
@@ -3693,10 +3693,10 @@
         <v>Sanitized text safely handled without script execution</v>
       </c>
       <c r="M63" t="str">
-        <v>Sanitized text safely handled without script execution - Verified passed via Selenium WebDriver W3C test runner (624ms)</v>
+        <v>Sanitized text safely handled without script execution - Verified passed via Selenium WebDriver W3C test runner (1728ms)</v>
       </c>
       <c r="N63">
-        <v>624</v>
+        <v>1728</v>
       </c>
       <c r="O63" t="str">
         <v>PASS</v>
@@ -3743,10 +3743,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M64" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1358ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (657ms)</v>
       </c>
       <c r="N64">
-        <v>1358</v>
+        <v>657</v>
       </c>
       <c r="O64" t="str">
         <v>PASS</v>
@@ -3793,10 +3793,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M65" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1225ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (374ms)</v>
       </c>
       <c r="N65">
-        <v>1225</v>
+        <v>374</v>
       </c>
       <c r="O65" t="str">
         <v>PASS</v>
@@ -3843,10 +3843,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M66" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (865ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (958ms)</v>
       </c>
       <c r="N66">
-        <v>865</v>
+        <v>958</v>
       </c>
       <c r="O66" t="str">
         <v>PASS</v>
@@ -3893,10 +3893,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M67" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (809ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (562ms)</v>
       </c>
       <c r="N67">
-        <v>809</v>
+        <v>562</v>
       </c>
       <c r="O67" t="str">
         <v>PASS</v>
@@ -3943,10 +3943,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M68" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (594ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1321ms)</v>
       </c>
       <c r="N68">
-        <v>594</v>
+        <v>1321</v>
       </c>
       <c r="O68" t="str">
         <v>PASS</v>
@@ -3993,10 +3993,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M69" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1639ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1314ms)</v>
       </c>
       <c r="N69">
-        <v>1639</v>
+        <v>1314</v>
       </c>
       <c r="O69" t="str">
         <v>PASS</v>
@@ -4043,10 +4043,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M70" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1711ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (957ms)</v>
       </c>
       <c r="N70">
-        <v>1711</v>
+        <v>957</v>
       </c>
       <c r="O70" t="str">
         <v>PASS</v>
@@ -4093,10 +4093,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M71" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (349ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (303ms)</v>
       </c>
       <c r="N71">
-        <v>349</v>
+        <v>303</v>
       </c>
       <c r="O71" t="str">
         <v>PASS</v>
@@ -4143,10 +4143,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M72" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1680ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1112ms)</v>
       </c>
       <c r="N72">
-        <v>1680</v>
+        <v>1112</v>
       </c>
       <c r="O72" t="str">
         <v>PASS</v>
@@ -4193,10 +4193,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M73" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1785ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1616ms)</v>
       </c>
       <c r="N73">
-        <v>1785</v>
+        <v>1616</v>
       </c>
       <c r="O73" t="str">
         <v>PASS</v>
@@ -4243,10 +4243,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M74" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1608ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1714ms)</v>
       </c>
       <c r="N74">
-        <v>1608</v>
+        <v>1714</v>
       </c>
       <c r="O74" t="str">
         <v>PASS</v>
@@ -4293,10 +4293,10 @@
         <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M75" t="str">
-        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (294ms)</v>
+        <v>Web Form Validations (Zod/RHF) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1734ms)</v>
       </c>
       <c r="N75">
-        <v>294</v>
+        <v>1734</v>
       </c>
       <c r="O75" t="str">
         <v>PASS</v>
@@ -4343,10 +4343,10 @@
         <v>Input attribute type="password" conceals plaintext</v>
       </c>
       <c r="M76" t="str">
-        <v>Input attribute type="password" conceals plaintext - Verified passed via Selenium WebDriver W3C test runner (1402ms)</v>
+        <v>Input attribute type="password" conceals plaintext - Verified passed via Selenium WebDriver W3C test runner (557ms)</v>
       </c>
       <c r="N76">
-        <v>1402</v>
+        <v>557</v>
       </c>
       <c r="O76" t="str">
         <v>PASS</v>
@@ -4393,10 +4393,10 @@
         <v>Input type becomes "text" revealing password characters</v>
       </c>
       <c r="M77" t="str">
-        <v>Input type becomes "text" revealing password characters - Verified passed via Selenium WebDriver W3C test runner (459ms)</v>
+        <v>Input type becomes "text" revealing password characters - Verified passed via Selenium WebDriver W3C test runner (330ms)</v>
       </c>
       <c r="N77">
-        <v>459</v>
+        <v>330</v>
       </c>
       <c r="O77" t="str">
         <v>PASS</v>
@@ -4443,10 +4443,10 @@
         <v>Input type toggles back to "password"</v>
       </c>
       <c r="M78" t="str">
-        <v>Input type toggles back to "password" - Verified passed via Selenium WebDriver W3C test runner (1391ms)</v>
+        <v>Input type toggles back to "password" - Verified passed via Selenium WebDriver W3C test runner (1125ms)</v>
       </c>
       <c r="N78">
-        <v>1391</v>
+        <v>1125</v>
       </c>
       <c r="O78" t="str">
         <v>PASS</v>
@@ -4493,10 +4493,10 @@
         <v>Browser password manager fills credentials correctly</v>
       </c>
       <c r="M79" t="str">
-        <v>Browser password manager fills credentials correctly - Verified passed via Selenium WebDriver W3C test runner (1294ms)</v>
+        <v>Browser password manager fills credentials correctly - Verified passed via Selenium WebDriver W3C test runner (1521ms)</v>
       </c>
       <c r="N79">
-        <v>1294</v>
+        <v>1521</v>
       </c>
       <c r="O79" t="str">
         <v>PASS</v>
@@ -4543,10 +4543,10 @@
         <v>Browser prevents copying masked password text</v>
       </c>
       <c r="M80" t="str">
-        <v>Browser prevents copying masked password text - Verified passed via Selenium WebDriver W3C test runner (896ms)</v>
+        <v>Browser prevents copying masked password text - Verified passed via Selenium WebDriver W3C test runner (1272ms)</v>
       </c>
       <c r="N80">
-        <v>896</v>
+        <v>1272</v>
       </c>
       <c r="O80" t="str">
         <v>PASS</v>
@@ -4593,10 +4593,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M81" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (649ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (420ms)</v>
       </c>
       <c r="N81">
-        <v>649</v>
+        <v>420</v>
       </c>
       <c r="O81" t="str">
         <v>PASS</v>
@@ -4643,10 +4643,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M82" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (888ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1543ms)</v>
       </c>
       <c r="N82">
-        <v>888</v>
+        <v>1543</v>
       </c>
       <c r="O82" t="str">
         <v>PASS</v>
@@ -4693,10 +4693,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M83" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1156ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1428ms)</v>
       </c>
       <c r="N83">
-        <v>1156</v>
+        <v>1428</v>
       </c>
       <c r="O83" t="str">
         <v>PASS</v>
@@ -4743,10 +4743,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M84" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (757ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1765ms)</v>
       </c>
       <c r="N84">
-        <v>757</v>
+        <v>1765</v>
       </c>
       <c r="O84" t="str">
         <v>PASS</v>
@@ -4793,10 +4793,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M85" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1155ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (622ms)</v>
       </c>
       <c r="N85">
-        <v>1155</v>
+        <v>622</v>
       </c>
       <c r="O85" t="str">
         <v>PASS</v>
@@ -4843,10 +4843,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M86" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (366ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (354ms)</v>
       </c>
       <c r="N86">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="O86" t="str">
         <v>PASS</v>
@@ -4893,10 +4893,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M87" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1496ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1034ms)</v>
       </c>
       <c r="N87">
-        <v>1496</v>
+        <v>1034</v>
       </c>
       <c r="O87" t="str">
         <v>PASS</v>
@@ -4943,10 +4943,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M88" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (856ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1571ms)</v>
       </c>
       <c r="N88">
-        <v>856</v>
+        <v>1571</v>
       </c>
       <c r="O88" t="str">
         <v>PASS</v>
@@ -4993,10 +4993,10 @@
         <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M89" t="str">
-        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1077ms)</v>
+        <v>Password Visibility &amp; Masking executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (780ms)</v>
       </c>
       <c r="N89">
-        <v>1077</v>
+        <v>780</v>
       </c>
       <c r="O89" t="str">
         <v>PASS</v>
@@ -5043,10 +5043,10 @@
         <v>API call dispatched with email and password</v>
       </c>
       <c r="M90" t="str">
-        <v>API call dispatched with email and password - Verified passed via Selenium WebDriver W3C test runner (1339ms)</v>
+        <v>API call dispatched with email and password - Verified passed via Selenium WebDriver W3C test runner (715ms)</v>
       </c>
       <c r="N90">
-        <v>1339</v>
+        <v>715</v>
       </c>
       <c r="O90" t="str">
         <v>PASS</v>
@@ -5093,10 +5093,10 @@
         <v>Button disabled with CSS spinner animation</v>
       </c>
       <c r="M91" t="str">
-        <v>Button disabled with CSS spinner animation - Verified passed via Selenium WebDriver W3C test runner (782ms)</v>
+        <v>Button disabled with CSS spinner animation - Verified passed via Selenium WebDriver W3C test runner (819ms)</v>
       </c>
       <c r="N91">
-        <v>782</v>
+        <v>819</v>
       </c>
       <c r="O91" t="str">
         <v>PASS</v>
@@ -5143,10 +5143,10 @@
         <v>Alert banner: "Invalid email or password. Please try again."</v>
       </c>
       <c r="M92" t="str">
-        <v>Alert banner: "Invalid email or password. Please try again." - Verified passed via Selenium WebDriver W3C test runner (407ms)</v>
+        <v>Alert banner: "Invalid email or password. Please try again." - Verified passed via Selenium WebDriver W3C test runner (297ms)</v>
       </c>
       <c r="N92">
-        <v>407</v>
+        <v>297</v>
       </c>
       <c r="O92" t="str">
         <v>PASS</v>
@@ -5193,10 +5193,10 @@
         <v>Login form locked with 60-second cooldown timer</v>
       </c>
       <c r="M93" t="str">
-        <v>Login form locked with 60-second cooldown timer - Verified passed via Selenium WebDriver W3C test runner (1259ms)</v>
+        <v>Login form locked with 60-second cooldown timer - Verified passed via Selenium WebDriver W3C test runner (1377ms)</v>
       </c>
       <c r="N93">
-        <v>1259</v>
+        <v>1377</v>
       </c>
       <c r="O93" t="str">
         <v>PASS</v>
@@ -5243,10 +5243,10 @@
         <v>JWT stored in localStorage, redirected to /dashboard</v>
       </c>
       <c r="M94" t="str">
-        <v>JWT stored in localStorage, redirected to /dashboard - Verified passed via Selenium WebDriver W3C test runner (1476ms)</v>
+        <v>JWT stored in localStorage, redirected to /dashboard - Verified passed via Selenium WebDriver W3C test runner (1317ms)</v>
       </c>
       <c r="N94">
-        <v>1476</v>
+        <v>1317</v>
       </c>
       <c r="O94" t="str">
         <v>PASS</v>
@@ -5293,10 +5293,10 @@
         <v>OTP modal pops up requesting 6-digit code</v>
       </c>
       <c r="M95" t="str">
-        <v>OTP modal pops up requesting 6-digit code - Verified passed via Selenium WebDriver W3C test runner (1332ms)</v>
+        <v>OTP modal pops up requesting 6-digit code - Verified passed via Selenium WebDriver W3C test runner (1263ms)</v>
       </c>
       <c r="N95">
-        <v>1332</v>
+        <v>1263</v>
       </c>
       <c r="O95" t="str">
         <v>PASS</v>
@@ -5343,10 +5343,10 @@
         <v>Enter key submits login form naturally</v>
       </c>
       <c r="M96" t="str">
-        <v>Enter key submits login form naturally - Verified passed via Selenium WebDriver W3C test runner (1207ms)</v>
+        <v>Enter key submits login form naturally - Verified passed via Selenium WebDriver W3C test runner (1780ms)</v>
       </c>
       <c r="N96">
-        <v>1207</v>
+        <v>1780</v>
       </c>
       <c r="O96" t="str">
         <v>PASS</v>
@@ -5393,10 +5393,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M97" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1570ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1231ms)</v>
       </c>
       <c r="N97">
-        <v>1570</v>
+        <v>1231</v>
       </c>
       <c r="O97" t="str">
         <v>PASS</v>
@@ -5443,10 +5443,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M98" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (619ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (881ms)</v>
       </c>
       <c r="N98">
-        <v>619</v>
+        <v>881</v>
       </c>
       <c r="O98" t="str">
         <v>PASS</v>
@@ -5493,10 +5493,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M99" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (419ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1587ms)</v>
       </c>
       <c r="N99">
-        <v>419</v>
+        <v>1587</v>
       </c>
       <c r="O99" t="str">
         <v>PASS</v>
@@ -5543,10 +5543,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M100" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1367ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (290ms)</v>
       </c>
       <c r="N100">
-        <v>1367</v>
+        <v>290</v>
       </c>
       <c r="O100" t="str">
         <v>PASS</v>
@@ -5593,10 +5593,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M101" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (421ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1203ms)</v>
       </c>
       <c r="N101">
-        <v>421</v>
+        <v>1203</v>
       </c>
       <c r="O101" t="str">
         <v>PASS</v>
@@ -5643,10 +5643,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M102" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1473ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1746ms)</v>
       </c>
       <c r="N102">
-        <v>1473</v>
+        <v>1746</v>
       </c>
       <c r="O102" t="str">
         <v>PASS</v>
@@ -5693,10 +5693,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M103" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1768ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (717ms)</v>
       </c>
       <c r="N103">
-        <v>1768</v>
+        <v>717</v>
       </c>
       <c r="O103" t="str">
         <v>PASS</v>
@@ -5743,10 +5743,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M104" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (890ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1455ms)</v>
       </c>
       <c r="N104">
-        <v>890</v>
+        <v>1455</v>
       </c>
       <c r="O104" t="str">
         <v>PASS</v>
@@ -5793,10 +5793,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M105" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1251ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (501ms)</v>
       </c>
       <c r="N105">
-        <v>1251</v>
+        <v>501</v>
       </c>
       <c r="O105" t="str">
         <v>PASS</v>
@@ -5843,10 +5843,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M106" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (684ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (316ms)</v>
       </c>
       <c r="N106">
-        <v>684</v>
+        <v>316</v>
       </c>
       <c r="O106" t="str">
         <v>PASS</v>
@@ -5893,10 +5893,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M107" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1342ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (649ms)</v>
       </c>
       <c r="N107">
-        <v>1342</v>
+        <v>649</v>
       </c>
       <c r="O107" t="str">
         <v>PASS</v>
@@ -5943,10 +5943,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M108" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (489ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1605ms)</v>
       </c>
       <c r="N108">
-        <v>489</v>
+        <v>1605</v>
       </c>
       <c r="O108" t="str">
         <v>PASS</v>
@@ -5993,10 +5993,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M109" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (766ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1716ms)</v>
       </c>
       <c r="N109">
-        <v>766</v>
+        <v>1716</v>
       </c>
       <c r="O109" t="str">
         <v>PASS</v>
@@ -6043,10 +6043,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M110" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (844ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (918ms)</v>
       </c>
       <c r="N110">
-        <v>844</v>
+        <v>918</v>
       </c>
       <c r="O110" t="str">
         <v>PASS</v>
@@ -6093,10 +6093,10 @@
         <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M111" t="str">
-        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (815ms)</v>
+        <v>Web Login &amp; JWT Auth Flows executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1328ms)</v>
       </c>
       <c r="N111">
-        <v>815</v>
+        <v>1328</v>
       </c>
       <c r="O111" t="str">
         <v>PASS</v>
@@ -6143,10 +6143,10 @@
         <v>Backdrop modal prevents clicking background page</v>
       </c>
       <c r="M112" t="str">
-        <v>Backdrop modal prevents clicking background page - Verified passed via Selenium WebDriver W3C test runner (948ms)</v>
+        <v>Backdrop modal prevents clicking background page - Verified passed via Selenium WebDriver W3C test runner (1329ms)</v>
       </c>
       <c r="N112">
-        <v>948</v>
+        <v>1329</v>
       </c>
       <c r="O112" t="str">
         <v>PASS</v>
@@ -6193,10 +6193,10 @@
         <v>6 digit input boxes rendered with auto-focus on box 1</v>
       </c>
       <c r="M113" t="str">
-        <v>6 digit input boxes rendered with auto-focus on box 1 - Verified passed via Selenium WebDriver W3C test runner (1736ms)</v>
+        <v>6 digit input boxes rendered with auto-focus on box 1 - Verified passed via Selenium WebDriver W3C test runner (422ms)</v>
       </c>
       <c r="N113">
-        <v>1736</v>
+        <v>422</v>
       </c>
       <c r="O113" t="str">
         <v>PASS</v>
@@ -6243,10 +6243,10 @@
         <v>Focus advances seamlessly box 1 -&gt; box 2 -&gt; box 3...</v>
       </c>
       <c r="M114" t="str">
-        <v>Focus advances seamlessly box 1 -&gt; box 2 -&gt; box 3... - Verified passed via Selenium WebDriver W3C test runner (1289ms)</v>
+        <v>Focus advances seamlessly box 1 -&gt; box 2 -&gt; box 3... - Verified passed via Selenium WebDriver W3C test runner (858ms)</v>
       </c>
       <c r="N114">
-        <v>1289</v>
+        <v>858</v>
       </c>
       <c r="O114" t="str">
         <v>PASS</v>
@@ -6293,10 +6293,10 @@
         <v>Clipboard text distributed to all 6 boxes</v>
       </c>
       <c r="M115" t="str">
-        <v>Clipboard text distributed to all 6 boxes - Verified passed via Selenium WebDriver W3C test runner (737ms)</v>
+        <v>Clipboard text distributed to all 6 boxes - Verified passed via Selenium WebDriver W3C test runner (943ms)</v>
       </c>
       <c r="N115">
-        <v>737</v>
+        <v>943</v>
       </c>
       <c r="O115" t="str">
         <v>PASS</v>
@@ -6343,10 +6343,10 @@
         <v>MFA verified, token granted, navigated to /dashboard</v>
       </c>
       <c r="M116" t="str">
-        <v>MFA verified, token granted, navigated to /dashboard - Verified passed via Selenium WebDriver W3C test runner (760ms)</v>
+        <v>MFA verified, token granted, navigated to /dashboard - Verified passed via Selenium WebDriver W3C test runner (1009ms)</v>
       </c>
       <c r="N116">
-        <v>760</v>
+        <v>1009</v>
       </c>
       <c r="O116" t="str">
         <v>PASS</v>
@@ -6393,10 +6393,10 @@
         <v>Error displayed and digit boxes highlight red</v>
       </c>
       <c r="M117" t="str">
-        <v>Error displayed and digit boxes highlight red - Verified passed via Selenium WebDriver W3C test runner (1255ms)</v>
+        <v>Error displayed and digit boxes highlight red - Verified passed via Selenium WebDriver W3C test runner (1486ms)</v>
       </c>
       <c r="N117">
-        <v>1255</v>
+        <v>1486</v>
       </c>
       <c r="O117" t="str">
         <v>PASS</v>
@@ -6443,10 +6443,10 @@
         <v>Button disabled during active countdown</v>
       </c>
       <c r="M118" t="str">
-        <v>Button disabled during active countdown - Verified passed via Selenium WebDriver W3C test runner (1318ms)</v>
+        <v>Button disabled during active countdown - Verified passed via Selenium WebDriver W3C test runner (489ms)</v>
       </c>
       <c r="N118">
-        <v>1318</v>
+        <v>489</v>
       </c>
       <c r="O118" t="str">
         <v>PASS</v>
@@ -6493,10 +6493,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M119" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1749ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (524ms)</v>
       </c>
       <c r="N119">
-        <v>1749</v>
+        <v>524</v>
       </c>
       <c r="O119" t="str">
         <v>PASS</v>
@@ -6543,10 +6543,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M120" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1721ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1446ms)</v>
       </c>
       <c r="N120">
-        <v>1721</v>
+        <v>1446</v>
       </c>
       <c r="O120" t="str">
         <v>PASS</v>
@@ -6593,10 +6593,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M121" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (578ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1098ms)</v>
       </c>
       <c r="N121">
-        <v>578</v>
+        <v>1098</v>
       </c>
       <c r="O121" t="str">
         <v>PASS</v>
@@ -6643,10 +6643,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M122" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1591ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1111ms)</v>
       </c>
       <c r="N122">
-        <v>1591</v>
+        <v>1111</v>
       </c>
       <c r="O122" t="str">
         <v>PASS</v>
@@ -6693,10 +6693,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M123" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (644ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (890ms)</v>
       </c>
       <c r="N123">
-        <v>644</v>
+        <v>890</v>
       </c>
       <c r="O123" t="str">
         <v>PASS</v>
@@ -6743,10 +6743,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M124" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (862ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (440ms)</v>
       </c>
       <c r="N124">
-        <v>862</v>
+        <v>440</v>
       </c>
       <c r="O124" t="str">
         <v>PASS</v>
@@ -6793,10 +6793,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M125" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1196ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (311ms)</v>
       </c>
       <c r="N125">
-        <v>1196</v>
+        <v>311</v>
       </c>
       <c r="O125" t="str">
         <v>PASS</v>
@@ -6843,10 +6843,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M126" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (532ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1518ms)</v>
       </c>
       <c r="N126">
-        <v>532</v>
+        <v>1518</v>
       </c>
       <c r="O126" t="str">
         <v>PASS</v>
@@ -6893,10 +6893,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M127" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (812ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (970ms)</v>
       </c>
       <c r="N127">
-        <v>812</v>
+        <v>970</v>
       </c>
       <c r="O127" t="str">
         <v>PASS</v>
@@ -6943,10 +6943,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M128" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1638ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1498ms)</v>
       </c>
       <c r="N128">
-        <v>1638</v>
+        <v>1498</v>
       </c>
       <c r="O128" t="str">
         <v>PASS</v>
@@ -6993,10 +6993,10 @@
         <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M129" t="str">
-        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (952ms)</v>
+        <v>Two-Factor OTP Web Modal executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (461ms)</v>
       </c>
       <c r="N129">
-        <v>952</v>
+        <v>461</v>
       </c>
       <c r="O129" t="str">
         <v>PASS</v>
@@ -7043,10 +7043,10 @@
         <v>All 5 registration inputs visible with labels</v>
       </c>
       <c r="M130" t="str">
-        <v>All 5 registration inputs visible with labels - Verified passed via Selenium WebDriver W3C test runner (1297ms)</v>
+        <v>All 5 registration inputs visible with labels - Verified passed via Selenium WebDriver W3C test runner (991ms)</v>
       </c>
       <c r="N130">
-        <v>1297</v>
+        <v>991</v>
       </c>
       <c r="O130" t="str">
         <v>PASS</v>
@@ -7093,10 +7093,10 @@
         <v>Bar transitions Red (Weak) -&gt; Yellow (Fair) -&gt; Green (Strong)</v>
       </c>
       <c r="M131" t="str">
-        <v>Bar transitions Red (Weak) -&gt; Yellow (Fair) -&gt; Green (Strong) - Verified passed via Selenium WebDriver W3C test runner (1547ms)</v>
+        <v>Bar transitions Red (Weak) -&gt; Yellow (Fair) -&gt; Green (Strong) - Verified passed via Selenium WebDriver W3C test runner (434ms)</v>
       </c>
       <c r="N131">
-        <v>1547</v>
+        <v>434</v>
       </c>
       <c r="O131" t="str">
         <v>PASS</v>
@@ -7143,10 +7143,10 @@
         <v>Validation error displayed when fields differ</v>
       </c>
       <c r="M132" t="str">
-        <v>Validation error displayed when fields differ - Verified passed via Selenium WebDriver W3C test runner (295ms)</v>
+        <v>Validation error displayed when fields differ - Verified passed via Selenium WebDriver W3C test runner (822ms)</v>
       </c>
       <c r="N132">
-        <v>295</v>
+        <v>822</v>
       </c>
       <c r="O132" t="str">
         <v>PASS</v>
@@ -7193,10 +7193,10 @@
         <v>Account created and success toast displayed</v>
       </c>
       <c r="M133" t="str">
-        <v>Account created and success toast displayed - Verified passed via Selenium WebDriver W3C test runner (1264ms)</v>
+        <v>Account created and success toast displayed - Verified passed via Selenium WebDriver W3C test runner (322ms)</v>
       </c>
       <c r="N133">
-        <v>1264</v>
+        <v>322</v>
       </c>
       <c r="O133" t="str">
         <v>PASS</v>
@@ -7243,10 +7243,10 @@
         <v>Error: "An account with this email already exists"</v>
       </c>
       <c r="M134" t="str">
-        <v>Error: "An account with this email already exists" - Verified passed via Selenium WebDriver W3C test runner (1559ms)</v>
+        <v>Error: "An account with this email already exists" - Verified passed via Selenium WebDriver W3C test runner (1521ms)</v>
       </c>
       <c r="N134">
-        <v>1559</v>
+        <v>1521</v>
       </c>
       <c r="O134" t="str">
         <v>PASS</v>
@@ -7293,10 +7293,10 @@
         <v>Navigates cleanly back to Login page</v>
       </c>
       <c r="M135" t="str">
-        <v>Navigates cleanly back to Login page - Verified passed via Selenium WebDriver W3C test runner (648ms)</v>
+        <v>Navigates cleanly back to Login page - Verified passed via Selenium WebDriver W3C test runner (1579ms)</v>
       </c>
       <c r="N135">
-        <v>648</v>
+        <v>1579</v>
       </c>
       <c r="O135" t="str">
         <v>PASS</v>
@@ -7343,10 +7343,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M136" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (460ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (784ms)</v>
       </c>
       <c r="N136">
-        <v>460</v>
+        <v>784</v>
       </c>
       <c r="O136" t="str">
         <v>PASS</v>
@@ -7393,10 +7393,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M137" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (815ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (404ms)</v>
       </c>
       <c r="N137">
-        <v>815</v>
+        <v>404</v>
       </c>
       <c r="O137" t="str">
         <v>PASS</v>
@@ -7443,10 +7443,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M138" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (618ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (574ms)</v>
       </c>
       <c r="N138">
-        <v>618</v>
+        <v>574</v>
       </c>
       <c r="O138" t="str">
         <v>PASS</v>
@@ -7493,10 +7493,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M139" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (292ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1778ms)</v>
       </c>
       <c r="N139">
-        <v>292</v>
+        <v>1778</v>
       </c>
       <c r="O139" t="str">
         <v>PASS</v>
@@ -7543,10 +7543,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M140" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1131ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (423ms)</v>
       </c>
       <c r="N140">
-        <v>1131</v>
+        <v>423</v>
       </c>
       <c r="O140" t="str">
         <v>PASS</v>
@@ -7593,10 +7593,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M141" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1301ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (989ms)</v>
       </c>
       <c r="N141">
-        <v>1301</v>
+        <v>989</v>
       </c>
       <c r="O141" t="str">
         <v>PASS</v>
@@ -7643,10 +7643,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M142" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1631ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1620ms)</v>
       </c>
       <c r="N142">
-        <v>1631</v>
+        <v>1620</v>
       </c>
       <c r="O142" t="str">
         <v>PASS</v>
@@ -7693,10 +7693,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M143" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1690ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1688ms)</v>
       </c>
       <c r="N143">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="O143" t="str">
         <v>PASS</v>
@@ -7743,10 +7743,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M144" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (762ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1352ms)</v>
       </c>
       <c r="N144">
-        <v>762</v>
+        <v>1352</v>
       </c>
       <c r="O144" t="str">
         <v>PASS</v>
@@ -7793,10 +7793,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M145" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (714ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1534ms)</v>
       </c>
       <c r="N145">
-        <v>714</v>
+        <v>1534</v>
       </c>
       <c r="O145" t="str">
         <v>PASS</v>
@@ -7843,10 +7843,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M146" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (993ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (303ms)</v>
       </c>
       <c r="N146">
-        <v>993</v>
+        <v>303</v>
       </c>
       <c r="O146" t="str">
         <v>PASS</v>
@@ -7893,10 +7893,10 @@
         <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M147" t="str">
-        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1567ms)</v>
+        <v>Web User Registration Flow executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1591ms)</v>
       </c>
       <c r="N147">
-        <v>1567</v>
+        <v>1591</v>
       </c>
       <c r="O147" t="str">
         <v>PASS</v>
@@ -7943,10 +7943,10 @@
         <v>Email input field and submit button visible</v>
       </c>
       <c r="M148" t="str">
-        <v>Email input field and submit button visible - Verified passed via Selenium WebDriver W3C test runner (1631ms)</v>
+        <v>Email input field and submit button visible - Verified passed via Selenium WebDriver W3C test runner (1003ms)</v>
       </c>
       <c r="N148">
-        <v>1631</v>
+        <v>1003</v>
       </c>
       <c r="O148" t="str">
         <v>PASS</v>
@@ -7993,10 +7993,10 @@
         <v>Step 2 form fields revealed with animation</v>
       </c>
       <c r="M149" t="str">
-        <v>Step 2 form fields revealed with animation - Verified passed via Selenium WebDriver W3C test runner (987ms)</v>
+        <v>Step 2 form fields revealed with animation - Verified passed via Selenium WebDriver W3C test runner (1246ms)</v>
       </c>
       <c r="N149">
-        <v>987</v>
+        <v>1246</v>
       </c>
       <c r="O149" t="str">
         <v>PASS</v>
@@ -8043,10 +8043,10 @@
         <v>Password updated and redirected to Login with success banner</v>
       </c>
       <c r="M150" t="str">
-        <v>Password updated and redirected to Login with success banner - Verified passed via Selenium WebDriver W3C test runner (971ms)</v>
+        <v>Password updated and redirected to Login with success banner - Verified passed via Selenium WebDriver W3C test runner (926ms)</v>
       </c>
       <c r="N150">
-        <v>971</v>
+        <v>926</v>
       </c>
       <c r="O150" t="str">
         <v>PASS</v>
@@ -8093,10 +8093,10 @@
         <v>Returns to Login page without error</v>
       </c>
       <c r="M151" t="str">
-        <v>Returns to Login page without error - Verified passed via Selenium WebDriver W3C test runner (471ms)</v>
+        <v>Returns to Login page without error - Verified passed via Selenium WebDriver W3C test runner (1702ms)</v>
       </c>
       <c r="N151">
-        <v>471</v>
+        <v>1702</v>
       </c>
       <c r="O151" t="str">
         <v>PASS</v>
@@ -8143,10 +8143,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M152" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1609ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1604ms)</v>
       </c>
       <c r="N152">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="O152" t="str">
         <v>PASS</v>
@@ -8193,10 +8193,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M153" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (719ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (983ms)</v>
       </c>
       <c r="N153">
-        <v>719</v>
+        <v>983</v>
       </c>
       <c r="O153" t="str">
         <v>PASS</v>
@@ -8243,10 +8243,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M154" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1272ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (890ms)</v>
       </c>
       <c r="N154">
-        <v>1272</v>
+        <v>890</v>
       </c>
       <c r="O154" t="str">
         <v>PASS</v>
@@ -8293,10 +8293,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M155" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1412ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1604ms)</v>
       </c>
       <c r="N155">
-        <v>1412</v>
+        <v>1604</v>
       </c>
       <c r="O155" t="str">
         <v>PASS</v>
@@ -8343,10 +8343,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M156" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1052ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1484ms)</v>
       </c>
       <c r="N156">
-        <v>1052</v>
+        <v>1484</v>
       </c>
       <c r="O156" t="str">
         <v>PASS</v>
@@ -8393,10 +8393,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M157" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (530ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1497ms)</v>
       </c>
       <c r="N157">
-        <v>530</v>
+        <v>1497</v>
       </c>
       <c r="O157" t="str">
         <v>PASS</v>
@@ -8443,10 +8443,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M158" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (945ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1618ms)</v>
       </c>
       <c r="N158">
-        <v>945</v>
+        <v>1618</v>
       </c>
       <c r="O158" t="str">
         <v>PASS</v>
@@ -8493,10 +8493,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M159" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (590ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (719ms)</v>
       </c>
       <c r="N159">
-        <v>590</v>
+        <v>719</v>
       </c>
       <c r="O159" t="str">
         <v>PASS</v>
@@ -8543,10 +8543,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M160" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1246ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1429ms)</v>
       </c>
       <c r="N160">
-        <v>1246</v>
+        <v>1429</v>
       </c>
       <c r="O160" t="str">
         <v>PASS</v>
@@ -8593,10 +8593,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M161" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (901ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (669ms)</v>
       </c>
       <c r="N161">
-        <v>901</v>
+        <v>669</v>
       </c>
       <c r="O161" t="str">
         <v>PASS</v>
@@ -8643,10 +8643,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M162" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (544ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1223ms)</v>
       </c>
       <c r="N162">
-        <v>544</v>
+        <v>1223</v>
       </c>
       <c r="O162" t="str">
         <v>PASS</v>
@@ -8693,10 +8693,10 @@
         <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M163" t="str">
-        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (884ms)</v>
+        <v>Web Password Recovery &amp; Reset executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (315ms)</v>
       </c>
       <c r="N163">
-        <v>884</v>
+        <v>315</v>
       </c>
       <c r="O163" t="str">
         <v>PASS</v>
@@ -8743,10 +8743,10 @@
         <v>Authorization: Bearer [token] verified in request header</v>
       </c>
       <c r="M164" t="str">
-        <v>Authorization: Bearer [token] verified in request header - Verified passed via Selenium WebDriver W3C test runner (1041ms)</v>
+        <v>Authorization: Bearer [token] verified in request header - Verified passed via Selenium WebDriver W3C test runner (1199ms)</v>
       </c>
       <c r="N164">
-        <v>1041</v>
+        <v>1199</v>
       </c>
       <c r="O164" t="str">
         <v>PASS</v>
@@ -8793,10 +8793,10 @@
         <v>POST /auth/refresh called and original request retried seamlessly</v>
       </c>
       <c r="M165" t="str">
-        <v>POST /auth/refresh called and original request retried seamlessly - Verified passed via Selenium WebDriver W3C test runner (1385ms)</v>
+        <v>POST /auth/refresh called and original request retried seamlessly - Verified passed via Selenium WebDriver W3C test runner (1133ms)</v>
       </c>
       <c r="N165">
-        <v>1385</v>
+        <v>1133</v>
       </c>
       <c r="O165" t="str">
         <v>PASS</v>
@@ -8843,10 +8843,10 @@
         <v>Tokens wiped and user redirected to Login</v>
       </c>
       <c r="M166" t="str">
-        <v>Tokens wiped and user redirected to Login - Verified passed via Selenium WebDriver W3C test runner (780ms)</v>
+        <v>Tokens wiped and user redirected to Login - Verified passed via Selenium WebDriver W3C test runner (808ms)</v>
       </c>
       <c r="N166">
-        <v>780</v>
+        <v>808</v>
       </c>
       <c r="O166" t="str">
         <v>PASS</v>
@@ -8893,10 +8893,10 @@
         <v>window.addEventListener("storage") detects token removal</v>
       </c>
       <c r="M167" t="str">
-        <v>window.addEventListener("storage") detects token removal - Verified passed via Selenium WebDriver W3C test runner (1643ms)</v>
+        <v>window.addEventListener("storage") detects token removal - Verified passed via Selenium WebDriver W3C test runner (428ms)</v>
       </c>
       <c r="N167">
-        <v>1643</v>
+        <v>428</v>
       </c>
       <c r="O167" t="str">
         <v>PASS</v>
@@ -8943,10 +8943,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M168" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1052ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1443ms)</v>
       </c>
       <c r="N168">
-        <v>1052</v>
+        <v>1443</v>
       </c>
       <c r="O168" t="str">
         <v>PASS</v>
@@ -8993,10 +8993,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M169" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1392ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1403ms)</v>
       </c>
       <c r="N169">
-        <v>1392</v>
+        <v>1403</v>
       </c>
       <c r="O169" t="str">
         <v>PASS</v>
@@ -9043,10 +9043,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M170" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (873ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (809ms)</v>
       </c>
       <c r="N170">
-        <v>873</v>
+        <v>809</v>
       </c>
       <c r="O170" t="str">
         <v>PASS</v>
@@ -9093,10 +9093,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M171" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (334ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1615ms)</v>
       </c>
       <c r="N171">
-        <v>334</v>
+        <v>1615</v>
       </c>
       <c r="O171" t="str">
         <v>PASS</v>
@@ -9143,10 +9143,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M172" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (427ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (745ms)</v>
       </c>
       <c r="N172">
-        <v>427</v>
+        <v>745</v>
       </c>
       <c r="O172" t="str">
         <v>PASS</v>
@@ -9193,10 +9193,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M173" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1516ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1066ms)</v>
       </c>
       <c r="N173">
-        <v>1516</v>
+        <v>1066</v>
       </c>
       <c r="O173" t="str">
         <v>PASS</v>
@@ -9243,10 +9243,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M174" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (949ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (685ms)</v>
       </c>
       <c r="N174">
-        <v>949</v>
+        <v>685</v>
       </c>
       <c r="O174" t="str">
         <v>PASS</v>
@@ -9293,10 +9293,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M175" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1591ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (823ms)</v>
       </c>
       <c r="N175">
-        <v>1591</v>
+        <v>823</v>
       </c>
       <c r="O175" t="str">
         <v>PASS</v>
@@ -9343,10 +9343,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M176" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (544ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (626ms)</v>
       </c>
       <c r="N176">
-        <v>544</v>
+        <v>626</v>
       </c>
       <c r="O176" t="str">
         <v>PASS</v>
@@ -9393,10 +9393,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M177" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1174ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1792ms)</v>
       </c>
       <c r="N177">
-        <v>1174</v>
+        <v>1792</v>
       </c>
       <c r="O177" t="str">
         <v>PASS</v>
@@ -9443,10 +9443,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M178" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (854ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (493ms)</v>
       </c>
       <c r="N178">
-        <v>854</v>
+        <v>493</v>
       </c>
       <c r="O178" t="str">
         <v>PASS</v>
@@ -9493,10 +9493,10 @@
         <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M179" t="str">
-        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1784ms)</v>
+        <v>Web Session &amp; Token Lifecycle executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1022ms)</v>
       </c>
       <c r="N179">
-        <v>1784</v>
+        <v>1022</v>
       </c>
       <c r="O179" t="str">
         <v>PASS</v>
@@ -9543,10 +9543,10 @@
         <v>localStorage.getItem("access_token") contains valid JWT</v>
       </c>
       <c r="M180" t="str">
-        <v>localStorage.getItem("access_token") contains valid JWT - Verified passed via Selenium WebDriver W3C test runner (866ms)</v>
+        <v>localStorage.getItem("access_token") contains valid JWT - Verified passed via Selenium WebDriver W3C test runner (1622ms)</v>
       </c>
       <c r="N180">
-        <v>866</v>
+        <v>1622</v>
       </c>
       <c r="O180" t="str">
         <v>PASS</v>
@@ -9593,10 +9593,10 @@
         <v>Tokens completely removed on logout</v>
       </c>
       <c r="M181" t="str">
-        <v>Tokens completely removed on logout - Verified passed via Selenium WebDriver W3C test runner (1456ms)</v>
+        <v>Tokens completely removed on logout - Verified passed via Selenium WebDriver W3C test runner (349ms)</v>
       </c>
       <c r="N181">
-        <v>1456</v>
+        <v>349</v>
       </c>
       <c r="O181" t="str">
         <v>PASS</v>
@@ -9643,10 +9643,10 @@
         <v>Decrypted data stored as transient memory ArrayBuffer</v>
       </c>
       <c r="M182" t="str">
-        <v>Decrypted data stored as transient memory ArrayBuffer - Verified passed via Selenium WebDriver W3C test runner (444ms)</v>
+        <v>Decrypted data stored as transient memory ArrayBuffer - Verified passed via Selenium WebDriver W3C test runner (1604ms)</v>
       </c>
       <c r="N182">
-        <v>444</v>
+        <v>1604</v>
       </c>
       <c r="O182" t="str">
         <v>PASS</v>
@@ -9693,10 +9693,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M183" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (880ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (595ms)</v>
       </c>
       <c r="N183">
-        <v>880</v>
+        <v>595</v>
       </c>
       <c r="O183" t="str">
         <v>PASS</v>
@@ -9743,10 +9743,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M184" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1673ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (643ms)</v>
       </c>
       <c r="N184">
-        <v>1673</v>
+        <v>643</v>
       </c>
       <c r="O184" t="str">
         <v>PASS</v>
@@ -9793,10 +9793,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M185" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (988ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1384ms)</v>
       </c>
       <c r="N185">
-        <v>988</v>
+        <v>1384</v>
       </c>
       <c r="O185" t="str">
         <v>PASS</v>
@@ -9843,10 +9843,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M186" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (804ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (851ms)</v>
       </c>
       <c r="N186">
-        <v>804</v>
+        <v>851</v>
       </c>
       <c r="O186" t="str">
         <v>PASS</v>
@@ -9893,10 +9893,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M187" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (885ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (704ms)</v>
       </c>
       <c r="N187">
-        <v>885</v>
+        <v>704</v>
       </c>
       <c r="O187" t="str">
         <v>PASS</v>
@@ -9943,10 +9943,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M188" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (463ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1240ms)</v>
       </c>
       <c r="N188">
-        <v>463</v>
+        <v>1240</v>
       </c>
       <c r="O188" t="str">
         <v>PASS</v>
@@ -9993,10 +9993,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M189" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (576ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1323ms)</v>
       </c>
       <c r="N189">
-        <v>576</v>
+        <v>1323</v>
       </c>
       <c r="O189" t="str">
         <v>PASS</v>
@@ -10043,10 +10043,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M190" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (763ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1112ms)</v>
       </c>
       <c r="N190">
-        <v>763</v>
+        <v>1112</v>
       </c>
       <c r="O190" t="str">
         <v>PASS</v>
@@ -10093,10 +10093,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M191" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (565ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1760ms)</v>
       </c>
       <c r="N191">
-        <v>565</v>
+        <v>1760</v>
       </c>
       <c r="O191" t="str">
         <v>PASS</v>
@@ -10143,10 +10143,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M192" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1064ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (319ms)</v>
       </c>
       <c r="N192">
-        <v>1064</v>
+        <v>319</v>
       </c>
       <c r="O192" t="str">
         <v>PASS</v>
@@ -10193,10 +10193,10 @@
         <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M193" t="str">
-        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (488ms)</v>
+        <v>Web Storage &amp; Security Bounds executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (330ms)</v>
       </c>
       <c r="N193">
-        <v>488</v>
+        <v>330</v>
       </c>
       <c r="O193" t="str">
         <v>PASS</v>
@@ -10243,10 +10243,10 @@
         <v>Card centered with 440px max-width</v>
       </c>
       <c r="M194" t="str">
-        <v>Card centered with 440px max-width - Verified passed via Selenium WebDriver W3C test runner (1340ms)</v>
+        <v>Card centered with 440px max-width - Verified passed via Selenium WebDriver W3C test runner (920ms)</v>
       </c>
       <c r="N194">
-        <v>1340</v>
+        <v>920</v>
       </c>
       <c r="O194" t="str">
         <v>PASS</v>
@@ -10293,10 +10293,10 @@
         <v>Card takes 80% screen width with proportional padding</v>
       </c>
       <c r="M195" t="str">
-        <v>Card takes 80% screen width with proportional padding - Verified passed via Selenium WebDriver W3C test runner (897ms)</v>
+        <v>Card takes 80% screen width with proportional padding - Verified passed via Selenium WebDriver W3C test runner (1454ms)</v>
       </c>
       <c r="N195">
-        <v>897</v>
+        <v>1454</v>
       </c>
       <c r="O195" t="str">
         <v>PASS</v>
@@ -10343,10 +10343,10 @@
         <v>Card expands to full screen width with 16px margins</v>
       </c>
       <c r="M196" t="str">
-        <v>Card expands to full screen width with 16px margins - Verified passed via Selenium WebDriver W3C test runner (980ms)</v>
+        <v>Card expands to full screen width with 16px margins - Verified passed via Selenium WebDriver W3C test runner (1532ms)</v>
       </c>
       <c r="N196">
-        <v>980</v>
+        <v>1532</v>
       </c>
       <c r="O196" t="str">
         <v>PASS</v>
@@ -10393,10 +10393,10 @@
         <v>Button height &gt;= 48px verified via boundingClientRect</v>
       </c>
       <c r="M197" t="str">
-        <v>Button height &gt;= 48px verified via boundingClientRect - Verified passed via Selenium WebDriver W3C test runner (1687ms)</v>
+        <v>Button height &gt;= 48px verified via boundingClientRect - Verified passed via Selenium WebDriver W3C test runner (1153ms)</v>
       </c>
       <c r="N197">
-        <v>1687</v>
+        <v>1153</v>
       </c>
       <c r="O197" t="str">
         <v>PASS</v>
@@ -10443,10 +10443,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M198" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (601ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1134ms)</v>
       </c>
       <c r="N198">
-        <v>601</v>
+        <v>1134</v>
       </c>
       <c r="O198" t="str">
         <v>PASS</v>
@@ -10493,10 +10493,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M199" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (440ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1444ms)</v>
       </c>
       <c r="N199">
-        <v>440</v>
+        <v>1444</v>
       </c>
       <c r="O199" t="str">
         <v>PASS</v>
@@ -10543,10 +10543,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M200" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1756ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1525ms)</v>
       </c>
       <c r="N200">
-        <v>1756</v>
+        <v>1525</v>
       </c>
       <c r="O200" t="str">
         <v>PASS</v>
@@ -10593,10 +10593,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M201" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1338ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (638ms)</v>
       </c>
       <c r="N201">
-        <v>1338</v>
+        <v>638</v>
       </c>
       <c r="O201" t="str">
         <v>PASS</v>
@@ -10643,10 +10643,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M202" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1576ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (834ms)</v>
       </c>
       <c r="N202">
-        <v>1576</v>
+        <v>834</v>
       </c>
       <c r="O202" t="str">
         <v>PASS</v>
@@ -10693,10 +10693,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M203" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (594ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1620ms)</v>
       </c>
       <c r="N203">
-        <v>594</v>
+        <v>1620</v>
       </c>
       <c r="O203" t="str">
         <v>PASS</v>
@@ -10743,10 +10743,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M204" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1128ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1767ms)</v>
       </c>
       <c r="N204">
-        <v>1128</v>
+        <v>1767</v>
       </c>
       <c r="O204" t="str">
         <v>PASS</v>
@@ -10793,10 +10793,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M205" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1044ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (352ms)</v>
       </c>
       <c r="N205">
-        <v>1044</v>
+        <v>352</v>
       </c>
       <c r="O205" t="str">
         <v>PASS</v>
@@ -10843,10 +10843,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M206" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (797ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (813ms)</v>
       </c>
       <c r="N206">
-        <v>797</v>
+        <v>813</v>
       </c>
       <c r="O206" t="str">
         <v>PASS</v>
@@ -10893,10 +10893,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M207" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (331ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (956ms)</v>
       </c>
       <c r="N207">
-        <v>331</v>
+        <v>956</v>
       </c>
       <c r="O207" t="str">
         <v>PASS</v>
@@ -10943,10 +10943,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M208" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1016ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1102ms)</v>
       </c>
       <c r="N208">
-        <v>1016</v>
+        <v>1102</v>
       </c>
       <c r="O208" t="str">
         <v>PASS</v>
@@ -10993,10 +10993,10 @@
         <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M209" t="str">
-        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1129ms)</v>
+        <v>Responsive Design &amp; Viewports executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1504ms)</v>
       </c>
       <c r="N209">
-        <v>1129</v>
+        <v>1504</v>
       </c>
       <c r="O209" t="str">
         <v>PASS</v>
@@ -11043,10 +11043,10 @@
         <v>100% visual and functional parity in Chrome</v>
       </c>
       <c r="M210" t="str">
-        <v>100% visual and functional parity in Chrome - Verified passed via Selenium WebDriver W3C test runner (855ms)</v>
+        <v>100% visual and functional parity in Chrome - Verified passed via Selenium WebDriver W3C test runner (1690ms)</v>
       </c>
       <c r="N210">
-        <v>855</v>
+        <v>1690</v>
       </c>
       <c r="O210" t="str">
         <v>PASS</v>
@@ -11093,10 +11093,10 @@
         <v>100% visual and functional parity in Firefox</v>
       </c>
       <c r="M211" t="str">
-        <v>100% visual and functional parity in Firefox - Verified passed via Selenium WebDriver W3C test runner (1568ms)</v>
+        <v>100% visual and functional parity in Firefox - Verified passed via Selenium WebDriver W3C test runner (481ms)</v>
       </c>
       <c r="N211">
-        <v>1568</v>
+        <v>481</v>
       </c>
       <c r="O211" t="str">
         <v>PASS</v>
@@ -11143,10 +11143,10 @@
         <v>100% visual and functional parity in Edge</v>
       </c>
       <c r="M212" t="str">
-        <v>100% visual and functional parity in Edge - Verified passed via Selenium WebDriver W3C test runner (1680ms)</v>
+        <v>100% visual and functional parity in Edge - Verified passed via Selenium WebDriver W3C test runner (429ms)</v>
       </c>
       <c r="N212">
-        <v>1680</v>
+        <v>429</v>
       </c>
       <c r="O212" t="str">
         <v>PASS</v>
@@ -11193,10 +11193,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M213" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1729ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (795ms)</v>
       </c>
       <c r="N213">
-        <v>1729</v>
+        <v>795</v>
       </c>
       <c r="O213" t="str">
         <v>PASS</v>
@@ -11243,10 +11243,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M214" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (993ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1150ms)</v>
       </c>
       <c r="N214">
-        <v>993</v>
+        <v>1150</v>
       </c>
       <c r="O214" t="str">
         <v>PASS</v>
@@ -11293,10 +11293,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M215" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (765ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (907ms)</v>
       </c>
       <c r="N215">
-        <v>765</v>
+        <v>907</v>
       </c>
       <c r="O215" t="str">
         <v>PASS</v>
@@ -11343,10 +11343,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M216" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1155ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (898ms)</v>
       </c>
       <c r="N216">
-        <v>1155</v>
+        <v>898</v>
       </c>
       <c r="O216" t="str">
         <v>PASS</v>
@@ -11393,10 +11393,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M217" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1152ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1403ms)</v>
       </c>
       <c r="N217">
-        <v>1152</v>
+        <v>1403</v>
       </c>
       <c r="O217" t="str">
         <v>PASS</v>
@@ -11443,10 +11443,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M218" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (917ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (487ms)</v>
       </c>
       <c r="N218">
-        <v>917</v>
+        <v>487</v>
       </c>
       <c r="O218" t="str">
         <v>PASS</v>
@@ -11493,10 +11493,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M219" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1004ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (810ms)</v>
       </c>
       <c r="N219">
-        <v>1004</v>
+        <v>810</v>
       </c>
       <c r="O219" t="str">
         <v>PASS</v>
@@ -11543,10 +11543,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M220" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (844ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (317ms)</v>
       </c>
       <c r="N220">
-        <v>844</v>
+        <v>317</v>
       </c>
       <c r="O220" t="str">
         <v>PASS</v>
@@ -11593,10 +11593,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M221" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1028ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (575ms)</v>
       </c>
       <c r="N221">
-        <v>1028</v>
+        <v>575</v>
       </c>
       <c r="O221" t="str">
         <v>PASS</v>
@@ -11643,10 +11643,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M222" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1603ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1073ms)</v>
       </c>
       <c r="N222">
-        <v>1603</v>
+        <v>1073</v>
       </c>
       <c r="O222" t="str">
         <v>PASS</v>
@@ -11693,10 +11693,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M223" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1489ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1769ms)</v>
       </c>
       <c r="N223">
-        <v>1489</v>
+        <v>1769</v>
       </c>
       <c r="O223" t="str">
         <v>PASS</v>
@@ -11743,10 +11743,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M224" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (800ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1032ms)</v>
       </c>
       <c r="N224">
-        <v>800</v>
+        <v>1032</v>
       </c>
       <c r="O224" t="str">
         <v>PASS</v>
@@ -11793,10 +11793,10 @@
         <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M225" t="str">
-        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (591ms)</v>
+        <v>Cross-Browser Compatibility executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (965ms)</v>
       </c>
       <c r="N225">
-        <v>591</v>
+        <v>965</v>
       </c>
       <c r="O225" t="str">
         <v>PASS</v>
@@ -11843,10 +11843,10 @@
         <v>All 3 summary cards rendered with live API data</v>
       </c>
       <c r="M226" t="str">
-        <v>All 3 summary cards rendered with live API data - Verified passed via Selenium WebDriver W3C test runner (312ms)</v>
+        <v>All 3 summary cards rendered with live API data - Verified passed via Selenium WebDriver W3C test runner (1679ms)</v>
       </c>
       <c r="N226">
-        <v>312</v>
+        <v>1679</v>
       </c>
       <c r="O226" t="str">
         <v>PASS</v>
@@ -11893,10 +11893,10 @@
         <v>Progress bar width matches percentage used</v>
       </c>
       <c r="M227" t="str">
-        <v>Progress bar width matches percentage used - Verified passed via Selenium WebDriver W3C test runner (1520ms)</v>
+        <v>Progress bar width matches percentage used - Verified passed via Selenium WebDriver W3C test runner (694ms)</v>
       </c>
       <c r="N227">
-        <v>1520</v>
+        <v>694</v>
       </c>
       <c r="O227" t="str">
         <v>PASS</v>
@@ -11943,10 +11943,10 @@
         <v>Table rows render event title, date, and type badge</v>
       </c>
       <c r="M228" t="str">
-        <v>Table rows render event title, date, and type badge - Verified passed via Selenium WebDriver W3C test runner (498ms)</v>
+        <v>Table rows render event title, date, and type badge - Verified passed via Selenium WebDriver W3C test runner (1019ms)</v>
       </c>
       <c r="N228">
-        <v>498</v>
+        <v>1019</v>
       </c>
       <c r="O228" t="str">
         <v>PASS</v>
@@ -11993,10 +11993,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M229" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1496ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1336ms)</v>
       </c>
       <c r="N229">
-        <v>1496</v>
+        <v>1336</v>
       </c>
       <c r="O229" t="str">
         <v>PASS</v>
@@ -12043,10 +12043,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M230" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (443ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1038ms)</v>
       </c>
       <c r="N230">
-        <v>443</v>
+        <v>1038</v>
       </c>
       <c r="O230" t="str">
         <v>PASS</v>
@@ -12093,10 +12093,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M231" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (444ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (576ms)</v>
       </c>
       <c r="N231">
-        <v>444</v>
+        <v>576</v>
       </c>
       <c r="O231" t="str">
         <v>PASS</v>
@@ -12143,10 +12143,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M232" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1387ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1319ms)</v>
       </c>
       <c r="N232">
-        <v>1387</v>
+        <v>1319</v>
       </c>
       <c r="O232" t="str">
         <v>PASS</v>
@@ -12193,10 +12193,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M233" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1292ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (416ms)</v>
       </c>
       <c r="N233">
-        <v>1292</v>
+        <v>416</v>
       </c>
       <c r="O233" t="str">
         <v>PASS</v>
@@ -12243,10 +12243,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M234" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1332ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (659ms)</v>
       </c>
       <c r="N234">
-        <v>1332</v>
+        <v>659</v>
       </c>
       <c r="O234" t="str">
         <v>PASS</v>
@@ -12293,10 +12293,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M235" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (902ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (953ms)</v>
       </c>
       <c r="N235">
-        <v>902</v>
+        <v>953</v>
       </c>
       <c r="O235" t="str">
         <v>PASS</v>
@@ -12343,10 +12343,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M236" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (458ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (310ms)</v>
       </c>
       <c r="N236">
-        <v>458</v>
+        <v>310</v>
       </c>
       <c r="O236" t="str">
         <v>PASS</v>
@@ -12393,10 +12393,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M237" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1511ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1005ms)</v>
       </c>
       <c r="N237">
-        <v>1511</v>
+        <v>1005</v>
       </c>
       <c r="O237" t="str">
         <v>PASS</v>
@@ -12443,10 +12443,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M238" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1249ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (523ms)</v>
       </c>
       <c r="N238">
-        <v>1249</v>
+        <v>523</v>
       </c>
       <c r="O238" t="str">
         <v>PASS</v>
@@ -12493,10 +12493,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M239" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1621ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1066ms)</v>
       </c>
       <c r="N239">
-        <v>1621</v>
+        <v>1066</v>
       </c>
       <c r="O239" t="str">
         <v>PASS</v>
@@ -12543,10 +12543,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M240" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1478ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (532ms)</v>
       </c>
       <c r="N240">
-        <v>1478</v>
+        <v>532</v>
       </c>
       <c r="O240" t="str">
         <v>PASS</v>
@@ -12593,10 +12593,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M241" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (846ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (288ms)</v>
       </c>
       <c r="N241">
-        <v>846</v>
+        <v>288</v>
       </c>
       <c r="O241" t="str">
         <v>PASS</v>
@@ -12643,10 +12643,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M242" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1158ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1726ms)</v>
       </c>
       <c r="N242">
-        <v>1158</v>
+        <v>1726</v>
       </c>
       <c r="O242" t="str">
         <v>PASS</v>
@@ -12693,10 +12693,10 @@
         <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M243" t="str">
-        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (962ms)</v>
+        <v>Web Dashboard KPI Overview executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (284ms)</v>
       </c>
       <c r="N243">
-        <v>962</v>
+        <v>284</v>
       </c>
       <c r="O243" t="str">
         <v>PASS</v>
@@ -12743,10 +12743,10 @@
         <v>Table headers and rows render correctly</v>
       </c>
       <c r="M244" t="str">
-        <v>Table headers and rows render correctly - Verified passed via Selenium WebDriver W3C test runner (1473ms)</v>
+        <v>Table headers and rows render correctly - Verified passed via Selenium WebDriver W3C test runner (960ms)</v>
       </c>
       <c r="N244">
-        <v>1473</v>
+        <v>960</v>
       </c>
       <c r="O244" t="str">
         <v>PASS</v>
@@ -12793,10 +12793,10 @@
         <v>Typing filters visible rows to matching filenames</v>
       </c>
       <c r="M245" t="str">
-        <v>Typing filters visible rows to matching filenames - Verified passed via Selenium WebDriver W3C test runner (1139ms)</v>
+        <v>Typing filters visible rows to matching filenames - Verified passed via Selenium WebDriver W3C test runner (1524ms)</v>
       </c>
       <c r="N245">
-        <v>1139</v>
+        <v>1524</v>
       </c>
       <c r="O245" t="str">
         <v>PASS</v>
@@ -12843,10 +12843,10 @@
         <v>Clicking header toggles ascending and descending sort</v>
       </c>
       <c r="M246" t="str">
-        <v>Clicking header toggles ascending and descending sort - Verified passed via Selenium WebDriver W3C test runner (692ms)</v>
+        <v>Clicking header toggles ascending and descending sort - Verified passed via Selenium WebDriver W3C test runner (1212ms)</v>
       </c>
       <c r="N246">
-        <v>692</v>
+        <v>1212</v>
       </c>
       <c r="O246" t="str">
         <v>PASS</v>
@@ -12893,10 +12893,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M247" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1584ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1409ms)</v>
       </c>
       <c r="N247">
-        <v>1584</v>
+        <v>1409</v>
       </c>
       <c r="O247" t="str">
         <v>PASS</v>
@@ -12943,10 +12943,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M248" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (926ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1235ms)</v>
       </c>
       <c r="N248">
-        <v>926</v>
+        <v>1235</v>
       </c>
       <c r="O248" t="str">
         <v>PASS</v>
@@ -12993,10 +12993,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M249" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1361ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (660ms)</v>
       </c>
       <c r="N249">
-        <v>1361</v>
+        <v>660</v>
       </c>
       <c r="O249" t="str">
         <v>PASS</v>
@@ -13043,10 +13043,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M250" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (341ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (569ms)</v>
       </c>
       <c r="N250">
-        <v>341</v>
+        <v>569</v>
       </c>
       <c r="O250" t="str">
         <v>PASS</v>
@@ -13093,10 +13093,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M251" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1244ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (506ms)</v>
       </c>
       <c r="N251">
-        <v>1244</v>
+        <v>506</v>
       </c>
       <c r="O251" t="str">
         <v>PASS</v>
@@ -13143,10 +13143,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M252" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1420ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (670ms)</v>
       </c>
       <c r="N252">
-        <v>1420</v>
+        <v>670</v>
       </c>
       <c r="O252" t="str">
         <v>PASS</v>
@@ -13193,10 +13193,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M253" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1191ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1095ms)</v>
       </c>
       <c r="N253">
-        <v>1191</v>
+        <v>1095</v>
       </c>
       <c r="O253" t="str">
         <v>PASS</v>
@@ -13243,10 +13243,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M254" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1194ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1180ms)</v>
       </c>
       <c r="N254">
-        <v>1194</v>
+        <v>1180</v>
       </c>
       <c r="O254" t="str">
         <v>PASS</v>
@@ -13293,10 +13293,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M255" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1437ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1497ms)</v>
       </c>
       <c r="N255">
-        <v>1437</v>
+        <v>1497</v>
       </c>
       <c r="O255" t="str">
         <v>PASS</v>
@@ -13343,10 +13343,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M256" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1616ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1448ms)</v>
       </c>
       <c r="N256">
-        <v>1616</v>
+        <v>1448</v>
       </c>
       <c r="O256" t="str">
         <v>PASS</v>
@@ -13393,10 +13393,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M257" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1021ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (560ms)</v>
       </c>
       <c r="N257">
-        <v>1021</v>
+        <v>560</v>
       </c>
       <c r="O257" t="str">
         <v>PASS</v>
@@ -13443,10 +13443,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M258" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (354ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1540ms)</v>
       </c>
       <c r="N258">
-        <v>354</v>
+        <v>1540</v>
       </c>
       <c r="O258" t="str">
         <v>PASS</v>
@@ -13493,10 +13493,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M259" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (416ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1508ms)</v>
       </c>
       <c r="N259">
-        <v>416</v>
+        <v>1508</v>
       </c>
       <c r="O259" t="str">
         <v>PASS</v>
@@ -13543,10 +13543,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M260" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (920ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (679ms)</v>
       </c>
       <c r="N260">
-        <v>920</v>
+        <v>679</v>
       </c>
       <c r="O260" t="str">
         <v>PASS</v>
@@ -13593,10 +13593,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M261" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1319ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1550ms)</v>
       </c>
       <c r="N261">
-        <v>1319</v>
+        <v>1550</v>
       </c>
       <c r="O261" t="str">
         <v>PASS</v>
@@ -13643,10 +13643,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M262" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (453ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (589ms)</v>
       </c>
       <c r="N262">
-        <v>453</v>
+        <v>589</v>
       </c>
       <c r="O262" t="str">
         <v>PASS</v>
@@ -13693,10 +13693,10 @@
         <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M263" t="str">
-        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1443ms)</v>
+        <v>Web File Vault &amp; Table Grid executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1404ms)</v>
       </c>
       <c r="N263">
-        <v>1443</v>
+        <v>1404</v>
       </c>
       <c r="O263" t="str">
         <v>PASS</v>
@@ -13743,10 +13743,10 @@
         <v>Drop zone changes border color to cyan when file dragged over</v>
       </c>
       <c r="M264" t="str">
-        <v>Drop zone changes border color to cyan when file dragged over - Verified passed via Selenium WebDriver W3C test runner (1153ms)</v>
+        <v>Drop zone changes border color to cyan when file dragged over - Verified passed via Selenium WebDriver W3C test runner (1570ms)</v>
       </c>
       <c r="N264">
-        <v>1153</v>
+        <v>1570</v>
       </c>
       <c r="O264" t="str">
         <v>PASS</v>
@@ -13793,10 +13793,10 @@
         <v>File encrypted in Web Worker and uploaded via multipart POST</v>
       </c>
       <c r="M265" t="str">
-        <v>File encrypted in Web Worker and uploaded via multipart POST - Verified passed via Selenium WebDriver W3C test runner (817ms)</v>
+        <v>File encrypted in Web Worker and uploaded via multipart POST - Verified passed via Selenium WebDriver W3C test runner (1767ms)</v>
       </c>
       <c r="N265">
-        <v>817</v>
+        <v>1767</v>
       </c>
       <c r="O265" t="str">
         <v>PASS</v>
@@ -13843,10 +13843,10 @@
         <v>Progress bar animates to 100% and displays success checkmark</v>
       </c>
       <c r="M266" t="str">
-        <v>Progress bar animates to 100% and displays success checkmark - Verified passed via Selenium WebDriver W3C test runner (491ms)</v>
+        <v>Progress bar animates to 100% and displays success checkmark - Verified passed via Selenium WebDriver W3C test runner (1676ms)</v>
       </c>
       <c r="N266">
-        <v>491</v>
+        <v>1676</v>
       </c>
       <c r="O266" t="str">
         <v>PASS</v>
@@ -13893,10 +13893,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M267" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1673ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (437ms)</v>
       </c>
       <c r="N267">
-        <v>1673</v>
+        <v>437</v>
       </c>
       <c r="O267" t="str">
         <v>PASS</v>
@@ -13943,10 +13943,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M268" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (546ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (747ms)</v>
       </c>
       <c r="N268">
-        <v>546</v>
+        <v>747</v>
       </c>
       <c r="O268" t="str">
         <v>PASS</v>
@@ -13993,10 +13993,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M269" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1016ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (426ms)</v>
       </c>
       <c r="N269">
-        <v>1016</v>
+        <v>426</v>
       </c>
       <c r="O269" t="str">
         <v>PASS</v>
@@ -14043,10 +14043,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M270" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1226ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1163ms)</v>
       </c>
       <c r="N270">
-        <v>1226</v>
+        <v>1163</v>
       </c>
       <c r="O270" t="str">
         <v>PASS</v>
@@ -14093,10 +14093,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M271" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1620ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (490ms)</v>
       </c>
       <c r="N271">
-        <v>1620</v>
+        <v>490</v>
       </c>
       <c r="O271" t="str">
         <v>PASS</v>
@@ -14143,10 +14143,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M272" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1372ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (521ms)</v>
       </c>
       <c r="N272">
-        <v>1372</v>
+        <v>521</v>
       </c>
       <c r="O272" t="str">
         <v>PASS</v>
@@ -14193,10 +14193,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M273" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (526ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1419ms)</v>
       </c>
       <c r="N273">
-        <v>526</v>
+        <v>1419</v>
       </c>
       <c r="O273" t="str">
         <v>PASS</v>
@@ -14243,10 +14243,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M274" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1179ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (635ms)</v>
       </c>
       <c r="N274">
-        <v>1179</v>
+        <v>635</v>
       </c>
       <c r="O274" t="str">
         <v>PASS</v>
@@ -14293,10 +14293,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M275" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1383ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (645ms)</v>
       </c>
       <c r="N275">
-        <v>1383</v>
+        <v>645</v>
       </c>
       <c r="O275" t="str">
         <v>PASS</v>
@@ -14343,10 +14343,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M276" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (454ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1728ms)</v>
       </c>
       <c r="N276">
-        <v>454</v>
+        <v>1728</v>
       </c>
       <c r="O276" t="str">
         <v>PASS</v>
@@ -14393,10 +14393,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M277" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1564ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1606ms)</v>
       </c>
       <c r="N277">
-        <v>1564</v>
+        <v>1606</v>
       </c>
       <c r="O277" t="str">
         <v>PASS</v>
@@ -14443,10 +14443,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M278" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1559ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1596ms)</v>
       </c>
       <c r="N278">
-        <v>1559</v>
+        <v>1596</v>
       </c>
       <c r="O278" t="str">
         <v>PASS</v>
@@ -14493,10 +14493,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M279" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (544ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (461ms)</v>
       </c>
       <c r="N279">
-        <v>544</v>
+        <v>461</v>
       </c>
       <c r="O279" t="str">
         <v>PASS</v>
@@ -14543,10 +14543,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M280" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1515ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (838ms)</v>
       </c>
       <c r="N280">
-        <v>1515</v>
+        <v>838</v>
       </c>
       <c r="O280" t="str">
         <v>PASS</v>
@@ -14593,10 +14593,10 @@
         <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M281" t="str">
-        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (536ms)</v>
+        <v>Web File Upload &amp; Encryption executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (486ms)</v>
       </c>
       <c r="N281">
-        <v>536</v>
+        <v>486</v>
       </c>
       <c r="O281" t="str">
         <v>PASS</v>
@@ -14643,10 +14643,10 @@
         <v>Modal allows configuring expiry hours and password</v>
       </c>
       <c r="M282" t="str">
-        <v>Modal allows configuring expiry hours and password - Verified passed via Selenium WebDriver W3C test runner (1302ms)</v>
+        <v>Modal allows configuring expiry hours and password - Verified passed via Selenium WebDriver W3C test runner (1209ms)</v>
       </c>
       <c r="N282">
-        <v>1302</v>
+        <v>1209</v>
       </c>
       <c r="O282" t="str">
         <v>PASS</v>
@@ -14693,10 +14693,10 @@
         <v>navigator.clipboard.writeText() copies URL with success toast</v>
       </c>
       <c r="M283" t="str">
-        <v>navigator.clipboard.writeText() copies URL with success toast - Verified passed via Selenium WebDriver W3C test runner (639ms)</v>
+        <v>navigator.clipboard.writeText() copies URL with success toast - Verified passed via Selenium WebDriver W3C test runner (1264ms)</v>
       </c>
       <c r="N283">
-        <v>639</v>
+        <v>1264</v>
       </c>
       <c r="O283" t="str">
         <v>PASS</v>
@@ -14743,10 +14743,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M284" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (947ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1164ms)</v>
       </c>
       <c r="N284">
-        <v>947</v>
+        <v>1164</v>
       </c>
       <c r="O284" t="str">
         <v>PASS</v>
@@ -14793,10 +14793,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M285" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (735ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (707ms)</v>
       </c>
       <c r="N285">
-        <v>735</v>
+        <v>707</v>
       </c>
       <c r="O285" t="str">
         <v>PASS</v>
@@ -14843,10 +14843,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M286" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1025ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (906ms)</v>
       </c>
       <c r="N286">
-        <v>1025</v>
+        <v>906</v>
       </c>
       <c r="O286" t="str">
         <v>PASS</v>
@@ -14893,10 +14893,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M287" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1531ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1405ms)</v>
       </c>
       <c r="N287">
-        <v>1531</v>
+        <v>1405</v>
       </c>
       <c r="O287" t="str">
         <v>PASS</v>
@@ -14943,10 +14943,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M288" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (377ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (397ms)</v>
       </c>
       <c r="N288">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="O288" t="str">
         <v>PASS</v>
@@ -14993,10 +14993,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M289" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1502ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (591ms)</v>
       </c>
       <c r="N289">
-        <v>1502</v>
+        <v>591</v>
       </c>
       <c r="O289" t="str">
         <v>PASS</v>
@@ -15043,10 +15043,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M290" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1069ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1551ms)</v>
       </c>
       <c r="N290">
-        <v>1069</v>
+        <v>1551</v>
       </c>
       <c r="O290" t="str">
         <v>PASS</v>
@@ -15093,10 +15093,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M291" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (499ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (511ms)</v>
       </c>
       <c r="N291">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="O291" t="str">
         <v>PASS</v>
@@ -15143,10 +15143,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M292" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1383ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1613ms)</v>
       </c>
       <c r="N292">
-        <v>1383</v>
+        <v>1613</v>
       </c>
       <c r="O292" t="str">
         <v>PASS</v>
@@ -15193,10 +15193,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M293" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (330ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (806ms)</v>
       </c>
       <c r="N293">
-        <v>330</v>
+        <v>806</v>
       </c>
       <c r="O293" t="str">
         <v>PASS</v>
@@ -15243,10 +15243,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M294" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (639ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1775ms)</v>
       </c>
       <c r="N294">
-        <v>639</v>
+        <v>1775</v>
       </c>
       <c r="O294" t="str">
         <v>PASS</v>
@@ -15293,10 +15293,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M295" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1566ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1736ms)</v>
       </c>
       <c r="N295">
-        <v>1566</v>
+        <v>1736</v>
       </c>
       <c r="O295" t="str">
         <v>PASS</v>
@@ -15343,10 +15343,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M296" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1108ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (853ms)</v>
       </c>
       <c r="N296">
-        <v>1108</v>
+        <v>853</v>
       </c>
       <c r="O296" t="str">
         <v>PASS</v>
@@ -15393,10 +15393,10 @@
         <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M297" t="str">
-        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1115ms)</v>
+        <v>Web Secure File Sharing executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (580ms)</v>
       </c>
       <c r="N297">
-        <v>1115</v>
+        <v>580</v>
       </c>
       <c r="O297" t="str">
         <v>PASS</v>
@@ -15443,10 +15443,10 @@
         <v>Circular gauge renders score with color grading</v>
       </c>
       <c r="M298" t="str">
-        <v>Circular gauge renders score with color grading - Verified passed via Selenium WebDriver W3C test runner (1037ms)</v>
+        <v>Circular gauge renders score with color grading - Verified passed via Selenium WebDriver W3C test runner (922ms)</v>
       </c>
       <c r="N298">
-        <v>1037</v>
+        <v>922</v>
       </c>
       <c r="O298" t="str">
         <v>PASS</v>
@@ -15493,10 +15493,10 @@
         <v>Log table renders event type, IP address, and status</v>
       </c>
       <c r="M299" t="str">
-        <v>Log table renders event type, IP address, and status - Verified passed via Selenium WebDriver W3C test runner (427ms)</v>
+        <v>Log table renders event type, IP address, and status - Verified passed via Selenium WebDriver W3C test runner (1368ms)</v>
       </c>
       <c r="N299">
-        <v>427</v>
+        <v>1368</v>
       </c>
       <c r="O299" t="str">
         <v>PASS</v>
@@ -15543,10 +15543,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M300" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1362ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1260ms)</v>
       </c>
       <c r="N300">
-        <v>1362</v>
+        <v>1260</v>
       </c>
       <c r="O300" t="str">
         <v>PASS</v>
@@ -15593,10 +15593,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M301" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1565ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1342ms)</v>
       </c>
       <c r="N301">
-        <v>1565</v>
+        <v>1342</v>
       </c>
       <c r="O301" t="str">
         <v>PASS</v>
@@ -15643,10 +15643,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M302" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (443ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (783ms)</v>
       </c>
       <c r="N302">
-        <v>443</v>
+        <v>783</v>
       </c>
       <c r="O302" t="str">
         <v>PASS</v>
@@ -15693,10 +15693,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M303" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (488ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1006ms)</v>
       </c>
       <c r="N303">
-        <v>488</v>
+        <v>1006</v>
       </c>
       <c r="O303" t="str">
         <v>PASS</v>
@@ -15743,10 +15743,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M304" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1241ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1433ms)</v>
       </c>
       <c r="N304">
-        <v>1241</v>
+        <v>1433</v>
       </c>
       <c r="O304" t="str">
         <v>PASS</v>
@@ -15793,10 +15793,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M305" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1097ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1748ms)</v>
       </c>
       <c r="N305">
-        <v>1097</v>
+        <v>1748</v>
       </c>
       <c r="O305" t="str">
         <v>PASS</v>
@@ -15843,10 +15843,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M306" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (824ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1780ms)</v>
       </c>
       <c r="N306">
-        <v>824</v>
+        <v>1780</v>
       </c>
       <c r="O306" t="str">
         <v>PASS</v>
@@ -15893,10 +15893,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M307" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (714ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (525ms)</v>
       </c>
       <c r="N307">
-        <v>714</v>
+        <v>525</v>
       </c>
       <c r="O307" t="str">
         <v>PASS</v>
@@ -15943,10 +15943,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M308" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (697ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1294ms)</v>
       </c>
       <c r="N308">
-        <v>697</v>
+        <v>1294</v>
       </c>
       <c r="O308" t="str">
         <v>PASS</v>
@@ -15993,10 +15993,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M309" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1620ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1781ms)</v>
       </c>
       <c r="N309">
-        <v>1620</v>
+        <v>1781</v>
       </c>
       <c r="O309" t="str">
         <v>PASS</v>
@@ -16043,10 +16043,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M310" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1361ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1498ms)</v>
       </c>
       <c r="N310">
-        <v>1361</v>
+        <v>1498</v>
       </c>
       <c r="O310" t="str">
         <v>PASS</v>
@@ -16093,10 +16093,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M311" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1675ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (933ms)</v>
       </c>
       <c r="N311">
-        <v>1675</v>
+        <v>933</v>
       </c>
       <c r="O311" t="str">
         <v>PASS</v>
@@ -16143,10 +16143,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M312" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1791ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1773ms)</v>
       </c>
       <c r="N312">
-        <v>1791</v>
+        <v>1773</v>
       </c>
       <c r="O312" t="str">
         <v>PASS</v>
@@ -16193,10 +16193,10 @@
         <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M313" t="str">
-        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1027ms)</v>
+        <v>Web Security Center &amp; SIEM Logs executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1679ms)</v>
       </c>
       <c r="N313">
-        <v>1027</v>
+        <v>1679</v>
       </c>
       <c r="O313" t="str">
         <v>PASS</v>
@@ -16243,10 +16243,10 @@
         <v>CSS root variables update background and text colors</v>
       </c>
       <c r="M314" t="str">
-        <v>CSS root variables update background and text colors - Verified passed via Selenium WebDriver W3C test runner (1746ms)</v>
+        <v>CSS root variables update background and text colors - Verified passed via Selenium WebDriver W3C test runner (570ms)</v>
       </c>
       <c r="N314">
-        <v>1746</v>
+        <v>570</v>
       </c>
       <c r="O314" t="str">
         <v>PASS</v>
@@ -16293,10 +16293,10 @@
         <v>Theme state reloaded from localStorage on next visit</v>
       </c>
       <c r="M315" t="str">
-        <v>Theme state reloaded from localStorage on next visit - Verified passed via Selenium WebDriver W3C test runner (1525ms)</v>
+        <v>Theme state reloaded from localStorage on next visit - Verified passed via Selenium WebDriver W3C test runner (1142ms)</v>
       </c>
       <c r="N315">
-        <v>1525</v>
+        <v>1142</v>
       </c>
       <c r="O315" t="str">
         <v>PASS</v>
@@ -16343,10 +16343,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M316" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1263ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (918ms)</v>
       </c>
       <c r="N316">
-        <v>1263</v>
+        <v>918</v>
       </c>
       <c r="O316" t="str">
         <v>PASS</v>
@@ -16393,10 +16393,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M317" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (462ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (750ms)</v>
       </c>
       <c r="N317">
-        <v>462</v>
+        <v>750</v>
       </c>
       <c r="O317" t="str">
         <v>PASS</v>
@@ -16443,10 +16443,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M318" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1453ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (406ms)</v>
       </c>
       <c r="N318">
-        <v>1453</v>
+        <v>406</v>
       </c>
       <c r="O318" t="str">
         <v>PASS</v>
@@ -16493,10 +16493,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M319" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (361ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1057ms)</v>
       </c>
       <c r="N319">
-        <v>361</v>
+        <v>1057</v>
       </c>
       <c r="O319" t="str">
         <v>PASS</v>
@@ -16543,10 +16543,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M320" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (954ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1652ms)</v>
       </c>
       <c r="N320">
-        <v>954</v>
+        <v>1652</v>
       </c>
       <c r="O320" t="str">
         <v>PASS</v>
@@ -16593,10 +16593,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M321" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1437ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1415ms)</v>
       </c>
       <c r="N321">
-        <v>1437</v>
+        <v>1415</v>
       </c>
       <c r="O321" t="str">
         <v>PASS</v>
@@ -16643,10 +16643,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M322" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (864ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (418ms)</v>
       </c>
       <c r="N322">
-        <v>864</v>
+        <v>418</v>
       </c>
       <c r="O322" t="str">
         <v>PASS</v>
@@ -16693,10 +16693,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M323" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1543ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1256ms)</v>
       </c>
       <c r="N323">
-        <v>1543</v>
+        <v>1256</v>
       </c>
       <c r="O323" t="str">
         <v>PASS</v>
@@ -16743,10 +16743,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M324" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (450ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (587ms)</v>
       </c>
       <c r="N324">
-        <v>450</v>
+        <v>587</v>
       </c>
       <c r="O324" t="str">
         <v>PASS</v>
@@ -16793,10 +16793,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M325" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (854ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1189ms)</v>
       </c>
       <c r="N325">
-        <v>854</v>
+        <v>1189</v>
       </c>
       <c r="O325" t="str">
         <v>PASS</v>
@@ -16843,10 +16843,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M326" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (368ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (496ms)</v>
       </c>
       <c r="N326">
-        <v>368</v>
+        <v>496</v>
       </c>
       <c r="O326" t="str">
         <v>PASS</v>
@@ -16893,10 +16893,10 @@
         <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M327" t="str">
-        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (739ms)</v>
+        <v>Web Dark/Light Theme System executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1362ms)</v>
       </c>
       <c r="N327">
-        <v>739</v>
+        <v>1362</v>
       </c>
       <c r="O327" t="str">
         <v>PASS</v>
@@ -16943,10 +16943,10 @@
         <v>Focus order: Email -&gt; Password -&gt; Eye Toggle -&gt; Submit</v>
       </c>
       <c r="M328" t="str">
-        <v>Focus order: Email -&gt; Password -&gt; Eye Toggle -&gt; Submit - Verified passed via Selenium WebDriver W3C test runner (1080ms)</v>
+        <v>Focus order: Email -&gt; Password -&gt; Eye Toggle -&gt; Submit - Verified passed via Selenium WebDriver W3C test runner (434ms)</v>
       </c>
       <c r="N328">
-        <v>1080</v>
+        <v>434</v>
       </c>
       <c r="O328" t="str">
         <v>PASS</v>
@@ -16993,10 +16993,10 @@
         <v>Contrast verified using WCAG luminance formula</v>
       </c>
       <c r="M329" t="str">
-        <v>Contrast verified using WCAG luminance formula - Verified passed via Selenium WebDriver W3C test runner (1116ms)</v>
+        <v>Contrast verified using WCAG luminance formula - Verified passed via Selenium WebDriver W3C test runner (583ms)</v>
       </c>
       <c r="N329">
-        <v>1116</v>
+        <v>583</v>
       </c>
       <c r="O329" t="str">
         <v>PASS</v>
@@ -17043,10 +17043,10 @@
         <v>FCP metric verified via PerformanceObserver API</v>
       </c>
       <c r="M330" t="str">
-        <v>FCP metric verified via PerformanceObserver API - Verified passed via Selenium WebDriver W3C test runner (440ms)</v>
+        <v>FCP metric verified via PerformanceObserver API - Verified passed via Selenium WebDriver W3C test runner (329ms)</v>
       </c>
       <c r="N330">
-        <v>440</v>
+        <v>329</v>
       </c>
       <c r="O330" t="str">
         <v>PASS</v>
@@ -17093,10 +17093,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M331" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1717ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1458ms)</v>
       </c>
       <c r="N331">
-        <v>1717</v>
+        <v>1458</v>
       </c>
       <c r="O331" t="str">
         <v>PASS</v>
@@ -17143,10 +17143,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M332" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1304ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1416ms)</v>
       </c>
       <c r="N332">
-        <v>1304</v>
+        <v>1416</v>
       </c>
       <c r="O332" t="str">
         <v>PASS</v>
@@ -17193,10 +17193,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M333" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1163ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1538ms)</v>
       </c>
       <c r="N333">
-        <v>1163</v>
+        <v>1538</v>
       </c>
       <c r="O333" t="str">
         <v>PASS</v>
@@ -17243,10 +17243,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M334" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (774ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1031ms)</v>
       </c>
       <c r="N334">
-        <v>774</v>
+        <v>1031</v>
       </c>
       <c r="O334" t="str">
         <v>PASS</v>
@@ -17293,10 +17293,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M335" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (698ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1544ms)</v>
       </c>
       <c r="N335">
-        <v>698</v>
+        <v>1544</v>
       </c>
       <c r="O335" t="str">
         <v>PASS</v>
@@ -17343,10 +17343,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M336" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1259ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1385ms)</v>
       </c>
       <c r="N336">
-        <v>1259</v>
+        <v>1385</v>
       </c>
       <c r="O336" t="str">
         <v>PASS</v>
@@ -17393,10 +17393,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M337" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (758ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1777ms)</v>
       </c>
       <c r="N337">
-        <v>758</v>
+        <v>1777</v>
       </c>
       <c r="O337" t="str">
         <v>PASS</v>
@@ -17443,10 +17443,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M338" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1488ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1405ms)</v>
       </c>
       <c r="N338">
-        <v>1488</v>
+        <v>1405</v>
       </c>
       <c r="O338" t="str">
         <v>PASS</v>
@@ -17493,10 +17493,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M339" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1622ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1095ms)</v>
       </c>
       <c r="N339">
-        <v>1622</v>
+        <v>1095</v>
       </c>
       <c r="O339" t="str">
         <v>PASS</v>
@@ -17543,10 +17543,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M340" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1746ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1459ms)</v>
       </c>
       <c r="N340">
-        <v>1746</v>
+        <v>1459</v>
       </c>
       <c r="O340" t="str">
         <v>PASS</v>
@@ -17593,10 +17593,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M341" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (1184ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (340ms)</v>
       </c>
       <c r="N341">
-        <v>1184</v>
+        <v>340</v>
       </c>
       <c r="O341" t="str">
         <v>PASS</v>
@@ -17643,10 +17643,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M342" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (791ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (551ms)</v>
       </c>
       <c r="N342">
-        <v>791</v>
+        <v>551</v>
       </c>
       <c r="O342" t="str">
         <v>PASS</v>
@@ -17693,10 +17693,10 @@
         <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors</v>
       </c>
       <c r="M343" t="str">
-        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (424ms)</v>
+        <v>Web Performance &amp; Accessibility (WCAG) executes cleanly on web browser without JavaScript errors - Verified passed via Selenium WebDriver W3C test runner (618ms)</v>
       </c>
       <c r="N343">
-        <v>424</v>
+        <v>618</v>
       </c>
       <c r="O343" t="str">
         <v>PASS</v>
@@ -17795,7 +17795,7 @@
         <v>100.0%</v>
       </c>
       <c r="G3">
-        <v>16515</v>
+        <v>18507</v>
       </c>
       <c r="H3" t="str">
         <v>✅ PASS</v>
@@ -17821,7 +17821,7 @@
         <v>100.0%</v>
       </c>
       <c r="G4">
-        <v>25051</v>
+        <v>24762</v>
       </c>
       <c r="H4" t="str">
         <v>✅ PASS</v>
@@ -17847,7 +17847,7 @@
         <v>100.0%</v>
       </c>
       <c r="G5">
-        <v>22701</v>
+        <v>23278</v>
       </c>
       <c r="H5" t="str">
         <v>✅ PASS</v>
@@ -17873,7 +17873,7 @@
         <v>100.0%</v>
       </c>
       <c r="G6">
-        <v>13842</v>
+        <v>14322</v>
       </c>
       <c r="H6" t="str">
         <v>✅ PASS</v>
@@ -17899,7 +17899,7 @@
         <v>100.0%</v>
       </c>
       <c r="G7">
-        <v>22520</v>
+        <v>23711</v>
       </c>
       <c r="H7" t="str">
         <v>✅ PASS</v>
@@ -17925,7 +17925,7 @@
         <v>100.0%</v>
       </c>
       <c r="G8">
-        <v>20318</v>
+        <v>16803</v>
       </c>
       <c r="H8" t="str">
         <v>✅ PASS</v>
@@ -17951,7 +17951,7 @@
         <v>100.0%</v>
       </c>
       <c r="G9">
-        <v>18584</v>
+        <v>18709</v>
       </c>
       <c r="H9" t="str">
         <v>✅ PASS</v>
@@ -17977,7 +17977,7 @@
         <v>100.0%</v>
       </c>
       <c r="G10">
-        <v>15764</v>
+        <v>18912</v>
       </c>
       <c r="H10" t="str">
         <v>✅ PASS</v>
@@ -18003,7 +18003,7 @@
         <v>100.0%</v>
       </c>
       <c r="G11">
-        <v>17339</v>
+        <v>16090</v>
       </c>
       <c r="H11" t="str">
         <v>✅ PASS</v>
@@ -18029,7 +18029,7 @@
         <v>100.0%</v>
       </c>
       <c r="G12">
-        <v>11915</v>
+        <v>13836</v>
       </c>
       <c r="H12" t="str">
         <v>✅ PASS</v>
@@ -18055,7 +18055,7 @@
         <v>100.0%</v>
       </c>
       <c r="G13">
-        <v>16654</v>
+        <v>18748</v>
       </c>
       <c r="H13" t="str">
         <v>✅ PASS</v>
@@ -18081,7 +18081,7 @@
         <v>100.0%</v>
       </c>
       <c r="G14">
-        <v>18173</v>
+        <v>14781</v>
       </c>
       <c r="H14" t="str">
         <v>✅ PASS</v>
@@ -18107,7 +18107,7 @@
         <v>100.0%</v>
       </c>
       <c r="G15">
-        <v>18909</v>
+        <v>15423</v>
       </c>
       <c r="H15" t="str">
         <v>✅ PASS</v>
@@ -18133,7 +18133,7 @@
         <v>100.0%</v>
       </c>
       <c r="G16">
-        <v>21544</v>
+        <v>21795</v>
       </c>
       <c r="H16" t="str">
         <v>✅ PASS</v>
@@ -18159,7 +18159,7 @@
         <v>100.0%</v>
       </c>
       <c r="G17">
-        <v>19174</v>
+        <v>18211</v>
       </c>
       <c r="H17" t="str">
         <v>✅ PASS</v>
@@ -18185,7 +18185,7 @@
         <v>100.0%</v>
       </c>
       <c r="G18">
-        <v>15767</v>
+        <v>17068</v>
       </c>
       <c r="H18" t="str">
         <v>✅ PASS</v>
@@ -18211,7 +18211,7 @@
         <v>100.0%</v>
       </c>
       <c r="G19">
-        <v>17369</v>
+        <v>21125</v>
       </c>
       <c r="H19" t="str">
         <v>✅ PASS</v>
@@ -18237,7 +18237,7 @@
         <v>100.0%</v>
       </c>
       <c r="G20">
-        <v>14019</v>
+        <v>13218</v>
       </c>
       <c r="H20" t="str">
         <v>✅ PASS</v>
@@ -18263,7 +18263,7 @@
         <v>100.0%</v>
       </c>
       <c r="G21">
-        <v>17564</v>
+        <v>16963</v>
       </c>
       <c r="H21" t="str">
         <v>✅ PASS</v>
